--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C93482-DDCF-42B4-A54F-8991D7BC4E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE16016-5FBA-486C-A349-0925041B09E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="220">
   <si>
     <t>Filial</t>
   </si>
@@ -669,6 +669,18 @@
   </si>
   <si>
     <t>CLINICA SAO MARCOS</t>
+  </si>
+  <si>
+    <t>HORIBA MEDICAL</t>
+  </si>
+  <si>
+    <t>DASA 12.857.736/0001</t>
+  </si>
+  <si>
+    <t>CAMINHO DE DAMASCO</t>
+  </si>
+  <si>
+    <t>ARS ENSINO SUPERIOR</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1371,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1478,6 +1490,39 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2113,17 +2158,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:E618"/>
+  <dimension ref="A1:D675"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="12" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="12"/>
-    <col min="7" max="7" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="12"/>
+    <col min="5" max="5" width="9.140625" style="12"/>
+    <col min="6" max="6" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2574,7 +2618,7 @@
         <v>3957.73</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
         <v>46296</v>
       </c>
@@ -2588,7 +2632,7 @@
         <v>5861.75</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
         <v>46296</v>
       </c>
@@ -2602,7 +2646,7 @@
         <v>20344.37</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
         <v>46296</v>
       </c>
@@ -2616,7 +2660,7 @@
         <v>9996</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>46296</v>
       </c>
@@ -2630,7 +2674,7 @@
         <v>9363.6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>46296</v>
       </c>
@@ -2644,7 +2688,7 @@
         <v>1719.02</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>46296</v>
       </c>
@@ -2658,7 +2702,7 @@
         <v>17013.18</v>
       </c>
     </row>
-    <row r="39" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="16">
         <v>46297</v>
       </c>
@@ -2671,9 +2715,8 @@
       <c r="D39" s="17">
         <v>2858.4</v>
       </c>
-      <c r="E39" s="12"/>
-    </row>
-    <row r="40" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="16">
         <v>46297</v>
       </c>
@@ -2686,9 +2729,8 @@
       <c r="D40" s="17">
         <v>20504.36</v>
       </c>
-      <c r="E40" s="12"/>
-    </row>
-    <row r="41" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16">
         <v>46297</v>
       </c>
@@ -2701,9 +2743,8 @@
       <c r="D41" s="18">
         <v>512.54</v>
       </c>
-      <c r="E41" s="12"/>
-    </row>
-    <row r="42" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="16">
         <v>46297</v>
       </c>
@@ -2716,9 +2757,8 @@
       <c r="D42" s="17">
         <v>17482.14</v>
       </c>
-      <c r="E42" s="12"/>
-    </row>
-    <row r="43" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="16">
         <v>46297</v>
       </c>
@@ -2731,9 +2771,8 @@
       <c r="D43" s="17">
         <v>18420.59</v>
       </c>
-      <c r="E43" s="12"/>
-    </row>
-    <row r="44" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="16">
         <v>46297</v>
       </c>
@@ -2746,9 +2785,8 @@
       <c r="D44" s="17">
         <v>2253.69</v>
       </c>
-      <c r="E44" s="12"/>
-    </row>
-    <row r="45" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="16">
         <v>46297</v>
       </c>
@@ -2761,9 +2799,8 @@
       <c r="D45" s="17">
         <v>5888.97</v>
       </c>
-      <c r="E45" s="12"/>
-    </row>
-    <row r="46" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="16">
         <v>46297</v>
       </c>
@@ -2776,9 +2813,8 @@
       <c r="D46" s="18">
         <v>690.6</v>
       </c>
-      <c r="E46" s="12"/>
-    </row>
-    <row r="47" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="16">
         <v>46297</v>
       </c>
@@ -2791,9 +2827,8 @@
       <c r="D47" s="18">
         <v>505.85</v>
       </c>
-      <c r="E47" s="12"/>
-    </row>
-    <row r="48" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="16">
         <v>46297</v>
       </c>
@@ -2806,9 +2841,8 @@
       <c r="D48" s="17">
         <v>1895.79</v>
       </c>
-      <c r="E48" s="12"/>
-    </row>
-    <row r="49" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="16">
         <v>46297</v>
       </c>
@@ -2821,9 +2855,8 @@
       <c r="D49" s="21">
         <v>-66.7</v>
       </c>
-      <c r="E49" s="12"/>
-    </row>
-    <row r="50" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="16">
         <v>46297</v>
       </c>
@@ -2836,9 +2869,8 @@
       <c r="D50" s="18">
         <v>280</v>
       </c>
-      <c r="E50" s="12"/>
-    </row>
-    <row r="51" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="16">
         <v>46297</v>
       </c>
@@ -2851,9 +2883,8 @@
       <c r="D51" s="17">
         <v>11702.28</v>
       </c>
-      <c r="E51" s="12"/>
-    </row>
-    <row r="52" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="16">
         <v>46297</v>
       </c>
@@ -2866,9 +2897,8 @@
       <c r="D52" s="17">
         <v>24626.1</v>
       </c>
-      <c r="E52" s="12"/>
-    </row>
-    <row r="53" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="16">
         <v>46297</v>
       </c>
@@ -2881,9 +2911,8 @@
       <c r="D53" s="17">
         <v>4360</v>
       </c>
-      <c r="E53" s="12"/>
-    </row>
-    <row r="54" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="16">
         <v>46297</v>
       </c>
@@ -2896,9 +2925,8 @@
       <c r="D54" s="17">
         <v>10618</v>
       </c>
-      <c r="E54" s="12"/>
-    </row>
-    <row r="55" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="16">
         <v>46297</v>
       </c>
@@ -2911,9 +2939,8 @@
       <c r="D55" s="17">
         <v>3077</v>
       </c>
-      <c r="E55" s="12"/>
-    </row>
-    <row r="56" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="16">
         <v>46297</v>
       </c>
@@ -2926,9 +2953,8 @@
       <c r="D56" s="17">
         <v>1679.2</v>
       </c>
-      <c r="E56" s="12"/>
-    </row>
-    <row r="57" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="16">
         <v>46297</v>
       </c>
@@ -2941,9 +2967,8 @@
       <c r="D57" s="17">
         <v>1842</v>
       </c>
-      <c r="E57" s="12"/>
-    </row>
-    <row r="58" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="16">
         <v>46297</v>
       </c>
@@ -2956,9 +2981,8 @@
       <c r="D58" s="22">
         <v>-11744.15</v>
       </c>
-      <c r="E58" s="12"/>
-    </row>
-    <row r="59" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16">
         <v>46297</v>
       </c>
@@ -2971,9 +2995,8 @@
       <c r="D59" s="17">
         <v>1922.1</v>
       </c>
-      <c r="E59" s="12"/>
-    </row>
-    <row r="60" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="16">
         <v>46297</v>
       </c>
@@ -2986,9 +3009,8 @@
       <c r="D60" s="17">
         <v>15386.54</v>
       </c>
-      <c r="E60" s="12"/>
-    </row>
-    <row r="61" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="16">
         <v>46297</v>
       </c>
@@ -3001,9 +3023,8 @@
       <c r="D61" s="17">
         <v>2367.04</v>
       </c>
-      <c r="E61" s="12"/>
-    </row>
-    <row r="62" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="16">
         <v>46297</v>
       </c>
@@ -3016,9 +3037,8 @@
       <c r="D62" s="17">
         <v>93931.5</v>
       </c>
-      <c r="E62" s="12"/>
-    </row>
-    <row r="63" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="16">
         <v>46297</v>
       </c>
@@ -3031,9 +3051,8 @@
       <c r="D63" s="17">
         <v>1835.6</v>
       </c>
-      <c r="E63" s="12"/>
-    </row>
-    <row r="64" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="16">
         <v>46297</v>
       </c>
@@ -3046,9 +3065,8 @@
       <c r="D64" s="17">
         <v>1155.24</v>
       </c>
-      <c r="E64" s="12"/>
-    </row>
-    <row r="65" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="16">
         <v>46297</v>
       </c>
@@ -3061,9 +3079,8 @@
       <c r="D65" s="17">
         <v>1308.3599999999999</v>
       </c>
-      <c r="E65" s="12"/>
-    </row>
-    <row r="66" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="16">
         <v>46297</v>
       </c>
@@ -3076,9 +3093,8 @@
       <c r="D66" s="17">
         <v>1654.28</v>
       </c>
-      <c r="E66" s="12"/>
-    </row>
-    <row r="67" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="16">
         <v>46297</v>
       </c>
@@ -3091,9 +3107,8 @@
       <c r="D67" s="17">
         <v>1536.16</v>
       </c>
-      <c r="E67" s="12"/>
-    </row>
-    <row r="68" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="16">
         <v>46297</v>
       </c>
@@ -3106,9 +3121,8 @@
       <c r="D68" s="18">
         <v>96.32</v>
       </c>
-      <c r="E68" s="12"/>
-    </row>
-    <row r="69" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="16">
         <v>46297</v>
       </c>
@@ -3121,9 +3135,8 @@
       <c r="D69" s="18">
         <v>971.42</v>
       </c>
-      <c r="E69" s="12"/>
-    </row>
-    <row r="70" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="16">
         <v>46297</v>
       </c>
@@ -3136,9 +3149,8 @@
       <c r="D70" s="17">
         <v>1112.18</v>
       </c>
-      <c r="E70" s="12"/>
-    </row>
-    <row r="71" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="16">
         <v>46297</v>
       </c>
@@ -3151,9 +3163,8 @@
       <c r="D71" s="17">
         <v>12891.7</v>
       </c>
-      <c r="E71" s="12"/>
-    </row>
-    <row r="72" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="16">
         <v>46297</v>
       </c>
@@ -3166,9 +3177,8 @@
       <c r="D72" s="17">
         <v>6579</v>
       </c>
-      <c r="E72" s="12"/>
-    </row>
-    <row r="73" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="16">
         <v>46297</v>
       </c>
@@ -3181,9 +3191,8 @@
       <c r="D73" s="17">
         <v>15250.48</v>
       </c>
-      <c r="E73" s="12"/>
-    </row>
-    <row r="74" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="16">
         <v>46297</v>
       </c>
@@ -3196,9 +3205,8 @@
       <c r="D74" s="17">
         <v>1609.74</v>
       </c>
-      <c r="E74" s="12"/>
-    </row>
-    <row r="75" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="16">
         <v>46297</v>
       </c>
@@ -3211,9 +3219,8 @@
       <c r="D75" s="17">
         <v>15335.9</v>
       </c>
-      <c r="E75" s="12"/>
-    </row>
-    <row r="76" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="16">
         <v>46297</v>
       </c>
@@ -3226,9 +3233,8 @@
       <c r="D76" s="18">
         <v>917.36</v>
       </c>
-      <c r="E76" s="12"/>
-    </row>
-    <row r="77" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="16">
         <v>46297</v>
       </c>
@@ -3241,9 +3247,8 @@
       <c r="D77" s="17">
         <v>2126.64</v>
       </c>
-      <c r="E77" s="12"/>
-    </row>
-    <row r="78" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="16">
         <v>46297</v>
       </c>
@@ -3256,9 +3261,8 @@
       <c r="D78" s="17">
         <v>14099.77</v>
       </c>
-      <c r="E78" s="12"/>
-    </row>
-    <row r="79" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="16">
         <v>46297</v>
       </c>
@@ -3271,9 +3275,8 @@
       <c r="D79" s="18">
         <v>697.94</v>
       </c>
-      <c r="E79" s="12"/>
-    </row>
-    <row r="80" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="16">
         <v>46297</v>
       </c>
@@ -3286,9 +3289,8 @@
       <c r="D80" s="18">
         <v>686.55</v>
       </c>
-      <c r="E80" s="12"/>
-    </row>
-    <row r="81" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="16">
         <v>46297</v>
       </c>
@@ -3301,9 +3303,8 @@
       <c r="D81" s="17">
         <v>18763.740000000002</v>
       </c>
-      <c r="E81" s="12"/>
-    </row>
-    <row r="82" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="16">
         <v>46297</v>
       </c>
@@ -3316,9 +3317,8 @@
       <c r="D82" s="18">
         <v>917</v>
       </c>
-      <c r="E82" s="12"/>
-    </row>
-    <row r="83" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="16">
         <v>46297</v>
       </c>
@@ -3331,9 +3331,8 @@
       <c r="D83" s="17">
         <v>1540.9</v>
       </c>
-      <c r="E83" s="12"/>
-    </row>
-    <row r="84" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="16">
         <v>46297</v>
       </c>
@@ -3346,9 +3345,8 @@
       <c r="D84" s="17">
         <v>1263.4000000000001</v>
       </c>
-      <c r="E84" s="12"/>
-    </row>
-    <row r="85" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="16">
         <v>46297</v>
       </c>
@@ -3361,9 +3359,8 @@
       <c r="D85" s="17">
         <v>4274.8</v>
       </c>
-      <c r="E85" s="12"/>
-    </row>
-    <row r="86" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="16">
         <v>46297</v>
       </c>
@@ -3376,9 +3373,8 @@
       <c r="D86" s="18">
         <v>465</v>
       </c>
-      <c r="E86" s="12"/>
-    </row>
-    <row r="87" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="16">
         <v>46297</v>
       </c>
@@ -3391,9 +3387,8 @@
       <c r="D87" s="18">
         <v>620</v>
       </c>
-      <c r="E87" s="12"/>
-    </row>
-    <row r="88" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="16">
         <v>46297</v>
       </c>
@@ -3406,9 +3401,8 @@
       <c r="D88" s="18">
         <v>620</v>
       </c>
-      <c r="E88" s="12"/>
-    </row>
-    <row r="89" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="16">
         <v>46297</v>
       </c>
@@ -3421,9 +3415,8 @@
       <c r="D89" s="17">
         <v>21714</v>
       </c>
-      <c r="E89" s="12"/>
-    </row>
-    <row r="90" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16">
         <v>46297</v>
       </c>
@@ -3436,9 +3429,8 @@
       <c r="D90" s="17">
         <v>13832</v>
       </c>
-      <c r="E90" s="12"/>
-    </row>
-    <row r="91" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16">
         <v>46297</v>
       </c>
@@ -3451,9 +3443,8 @@
       <c r="D91" s="18">
         <v>300</v>
       </c>
-      <c r="E91" s="12"/>
-    </row>
-    <row r="92" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="16">
         <v>46297</v>
       </c>
@@ -3466,9 +3457,8 @@
       <c r="D92" s="22">
         <v>-14552.5</v>
       </c>
-      <c r="E92" s="12"/>
-    </row>
-    <row r="93" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="16">
         <v>46297</v>
       </c>
@@ -3481,9 +3471,8 @@
       <c r="D93" s="21">
         <v>-236.53</v>
       </c>
-      <c r="E93" s="12"/>
-    </row>
-    <row r="94" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="16">
         <v>46297</v>
       </c>
@@ -3496,9 +3485,8 @@
       <c r="D94" s="17">
         <v>33266.58</v>
       </c>
-      <c r="E94" s="12"/>
-    </row>
-    <row r="95" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="16">
         <v>46297</v>
       </c>
@@ -3511,9 +3499,8 @@
       <c r="D95" s="17">
         <v>2490</v>
       </c>
-      <c r="E95" s="12"/>
-    </row>
-    <row r="96" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="16">
         <v>46297</v>
       </c>
@@ -3526,9 +3513,8 @@
       <c r="D96" s="25">
         <v>465</v>
       </c>
-      <c r="E96" s="12"/>
-    </row>
-    <row r="97" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="16">
         <v>46300</v>
       </c>
@@ -3541,9 +3527,8 @@
       <c r="D97" s="28">
         <v>50949</v>
       </c>
-      <c r="E97" s="12"/>
-    </row>
-    <row r="98" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="16">
         <v>46300</v>
       </c>
@@ -3556,9 +3541,8 @@
       <c r="D98" s="17">
         <v>6135.27</v>
       </c>
-      <c r="E98" s="12"/>
-    </row>
-    <row r="99" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="16">
         <v>46300</v>
       </c>
@@ -3571,9 +3555,8 @@
       <c r="D99" s="18">
         <v>149.96</v>
       </c>
-      <c r="E99" s="12"/>
-    </row>
-    <row r="100" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="16">
         <v>46300</v>
       </c>
@@ -3586,9 +3569,8 @@
       <c r="D100" s="22">
         <v>-4360</v>
       </c>
-      <c r="E100" s="12"/>
-    </row>
-    <row r="101" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="16">
         <v>46300</v>
       </c>
@@ -3601,9 +3583,8 @@
       <c r="D101" s="17">
         <v>4360</v>
       </c>
-      <c r="E101" s="12"/>
-    </row>
-    <row r="102" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="16">
         <v>46300</v>
       </c>
@@ -3616,9 +3597,8 @@
       <c r="D102" s="17">
         <v>6176.5</v>
       </c>
-      <c r="E102" s="12"/>
-    </row>
-    <row r="103" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="16">
         <v>46300</v>
       </c>
@@ -3631,9 +3611,8 @@
       <c r="D103" s="21">
         <v>-62.05</v>
       </c>
-      <c r="E103" s="12"/>
-    </row>
-    <row r="104" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="16">
         <v>46300</v>
       </c>
@@ -3646,9 +3625,8 @@
       <c r="D104" s="17">
         <v>23280</v>
       </c>
-      <c r="E104" s="12"/>
-    </row>
-    <row r="105" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="16">
         <v>46300</v>
       </c>
@@ -3661,9 +3639,8 @@
       <c r="D105" s="22">
         <v>-3080</v>
       </c>
-      <c r="E105" s="12"/>
-    </row>
-    <row r="106" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="16">
         <v>46300</v>
       </c>
@@ -3676,9 +3653,8 @@
       <c r="D106" s="17">
         <v>3975.73</v>
       </c>
-      <c r="E106" s="12"/>
-    </row>
-    <row r="107" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="16">
         <v>46300</v>
       </c>
@@ -3691,9 +3667,8 @@
       <c r="D107" s="17">
         <v>4631.84</v>
       </c>
-      <c r="E107" s="12"/>
-    </row>
-    <row r="108" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="16">
         <v>46300</v>
       </c>
@@ -3706,9 +3681,8 @@
       <c r="D108" s="17">
         <v>1758.44</v>
       </c>
-      <c r="E108" s="12"/>
-    </row>
-    <row r="109" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="16">
         <v>46300</v>
       </c>
@@ -3721,9 +3695,8 @@
       <c r="D109" s="17">
         <v>1638.16</v>
       </c>
-      <c r="E109" s="12"/>
-    </row>
-    <row r="110" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="16">
         <v>46300</v>
       </c>
@@ -3736,9 +3709,8 @@
       <c r="D110" s="17">
         <v>12354</v>
       </c>
-      <c r="E110" s="12"/>
-    </row>
-    <row r="111" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="16">
         <v>46300</v>
       </c>
@@ -3751,9 +3723,8 @@
       <c r="D111" s="17">
         <v>15313.4</v>
       </c>
-      <c r="E111" s="12"/>
-    </row>
-    <row r="112" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="16">
         <v>46300</v>
       </c>
@@ -3766,9 +3737,8 @@
       <c r="D112" s="17">
         <v>1014.73</v>
       </c>
-      <c r="E112" s="12"/>
-    </row>
-    <row r="113" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="16">
         <v>46300</v>
       </c>
@@ -3781,9 +3751,8 @@
       <c r="D113" s="17">
         <v>97082.83</v>
       </c>
-      <c r="E113" s="12"/>
-    </row>
-    <row r="114" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="16">
         <v>46300</v>
       </c>
@@ -3796,9 +3765,8 @@
       <c r="D114" s="17">
         <v>1098.74</v>
       </c>
-      <c r="E114" s="12"/>
-    </row>
-    <row r="115" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="16">
         <v>46300</v>
       </c>
@@ -3811,9 +3779,8 @@
       <c r="D115" s="17">
         <v>47960</v>
       </c>
-      <c r="E115" s="12"/>
-    </row>
-    <row r="116" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="16">
         <v>46300</v>
       </c>
@@ -3826,9 +3793,8 @@
       <c r="D116" s="29">
         <v>1312.36</v>
       </c>
-      <c r="E116" s="12"/>
-    </row>
-    <row r="117" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="16">
         <v>46301</v>
       </c>
@@ -3841,9 +3807,8 @@
       <c r="D117" s="28">
         <v>11285.83</v>
       </c>
-      <c r="E117" s="12"/>
-    </row>
-    <row r="118" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="16">
         <v>46301</v>
       </c>
@@ -3856,9 +3821,8 @@
       <c r="D118" s="22">
         <v>-2577.9</v>
       </c>
-      <c r="E118" s="12"/>
-    </row>
-    <row r="119" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="16">
         <v>46301</v>
       </c>
@@ -3871,9 +3835,8 @@
       <c r="D119" s="17">
         <v>2577.9</v>
       </c>
-      <c r="E119" s="12"/>
-    </row>
-    <row r="120" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="16">
         <v>46301</v>
       </c>
@@ -3886,9 +3849,8 @@
       <c r="D120" s="22">
         <v>-10618</v>
       </c>
-      <c r="E120" s="12"/>
-    </row>
-    <row r="121" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="16">
         <v>46301</v>
       </c>
@@ -3901,9 +3863,8 @@
       <c r="D121" s="17">
         <v>47646.34</v>
       </c>
-      <c r="E121" s="12"/>
-    </row>
-    <row r="122" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="16">
         <v>46301</v>
       </c>
@@ -3916,9 +3877,8 @@
       <c r="D122" s="17">
         <v>33349.51</v>
       </c>
-      <c r="E122" s="12"/>
-    </row>
-    <row r="123" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="16">
         <v>46301</v>
       </c>
@@ -3931,9 +3891,8 @@
       <c r="D123" s="17">
         <v>5645.4</v>
       </c>
-      <c r="E123" s="12"/>
-    </row>
-    <row r="124" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="16">
         <v>46301</v>
       </c>
@@ -3946,9 +3905,8 @@
       <c r="D124" s="18">
         <v>552.76</v>
       </c>
-      <c r="E124" s="12"/>
-    </row>
-    <row r="125" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="16">
         <v>46301</v>
       </c>
@@ -3961,9 +3919,8 @@
       <c r="D125" s="18">
         <v>534</v>
       </c>
-      <c r="E125" s="12"/>
-    </row>
-    <row r="126" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="16">
         <v>46301</v>
       </c>
@@ -3976,9 +3933,8 @@
       <c r="D126" s="17">
         <v>2772</v>
       </c>
-      <c r="E126" s="12"/>
-    </row>
-    <row r="127" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="16">
         <v>46301</v>
       </c>
@@ -3991,9 +3947,8 @@
       <c r="D127" s="17">
         <v>71313.8</v>
       </c>
-      <c r="E127" s="12"/>
-    </row>
-    <row r="128" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="16">
         <v>46301</v>
       </c>
@@ -4006,9 +3961,8 @@
       <c r="D128" s="17">
         <v>13168.92</v>
       </c>
-      <c r="E128" s="12"/>
-    </row>
-    <row r="129" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="16">
         <v>46301</v>
       </c>
@@ -4021,9 +3975,8 @@
       <c r="D129" s="17">
         <v>4059.8</v>
       </c>
-      <c r="E129" s="12"/>
-    </row>
-    <row r="130" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="16">
         <v>46301</v>
       </c>
@@ -4036,9 +3989,8 @@
       <c r="D130" s="18">
         <v>161.85</v>
       </c>
-      <c r="E130" s="12"/>
-    </row>
-    <row r="131" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="16">
         <v>46301</v>
       </c>
@@ -4051,9 +4003,8 @@
       <c r="D131" s="17">
         <v>188000</v>
       </c>
-      <c r="E131" s="12"/>
-    </row>
-    <row r="132" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="16">
         <v>46301</v>
       </c>
@@ -4066,9 +4017,8 @@
       <c r="D132" s="17">
         <v>21595.46</v>
       </c>
-      <c r="E132" s="12"/>
-    </row>
-    <row r="133" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="16">
         <v>46301</v>
       </c>
@@ -4081,9 +4031,8 @@
       <c r="D133" s="17">
         <v>4999.8100000000004</v>
       </c>
-      <c r="E133" s="12"/>
-    </row>
-    <row r="134" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="16">
         <v>46301</v>
       </c>
@@ -4096,9 +4045,8 @@
       <c r="D134" s="22">
         <v>-2247.5</v>
       </c>
-      <c r="E134" s="12"/>
-    </row>
-    <row r="135" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="16">
         <v>46301</v>
       </c>
@@ -4111,9 +4059,8 @@
       <c r="D135" s="17">
         <v>2662.78</v>
       </c>
-      <c r="E135" s="12"/>
-    </row>
-    <row r="136" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="16">
         <v>46301</v>
       </c>
@@ -4126,9 +4073,8 @@
       <c r="D136" s="29">
         <v>4080</v>
       </c>
-      <c r="E136" s="12"/>
-    </row>
-    <row r="137" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="16">
         <v>46302</v>
       </c>
@@ -4141,9 +4087,8 @@
       <c r="D137" s="30">
         <v>490</v>
       </c>
-      <c r="E137" s="12"/>
-    </row>
-    <row r="138" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="16">
         <v>46302</v>
       </c>
@@ -4156,9 +4101,8 @@
       <c r="D138" s="17">
         <v>6861.3</v>
       </c>
-      <c r="E138" s="12"/>
-    </row>
-    <row r="139" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="16">
         <v>46302</v>
       </c>
@@ -4171,9 +4115,8 @@
       <c r="D139" s="22">
         <v>-12949.2</v>
       </c>
-      <c r="E139" s="12"/>
-    </row>
-    <row r="140" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="16">
         <v>46302</v>
       </c>
@@ -4186,9 +4129,8 @@
       <c r="D140" s="17">
         <v>4200</v>
       </c>
-      <c r="E140" s="12"/>
-    </row>
-    <row r="141" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="16">
         <v>46302</v>
       </c>
@@ -4201,9 +4143,8 @@
       <c r="D141" s="17">
         <v>83048.800000000003</v>
       </c>
-      <c r="E141" s="12"/>
-    </row>
-    <row r="142" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="16">
         <v>46302</v>
       </c>
@@ -4216,9 +4157,8 @@
       <c r="D142" s="17">
         <v>15362.76</v>
       </c>
-      <c r="E142" s="12"/>
-    </row>
-    <row r="143" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="16">
         <v>46302</v>
       </c>
@@ -4231,9 +4171,8 @@
       <c r="D143" s="17">
         <v>1118.3900000000001</v>
       </c>
-      <c r="E143" s="12"/>
-    </row>
-    <row r="144" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="16">
         <v>46302</v>
       </c>
@@ -4246,9 +4185,8 @@
       <c r="D144" s="17">
         <v>26594.7</v>
       </c>
-      <c r="E144" s="12"/>
-    </row>
-    <row r="145" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="16">
         <v>46302</v>
       </c>
@@ -4261,9 +4199,8 @@
       <c r="D145" s="17">
         <v>1345.45</v>
       </c>
-      <c r="E145" s="12"/>
-    </row>
-    <row r="146" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="16">
         <v>46302</v>
       </c>
@@ -4276,9 +4213,8 @@
       <c r="D146" s="17">
         <v>15686.43</v>
       </c>
-      <c r="E146" s="12"/>
-    </row>
-    <row r="147" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="16">
         <v>46302</v>
       </c>
@@ -4291,9 +4227,8 @@
       <c r="D147" s="17">
         <v>1845.26</v>
       </c>
-      <c r="E147" s="12"/>
-    </row>
-    <row r="148" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="16">
         <v>46302</v>
       </c>
@@ -4306,9 +4241,8 @@
       <c r="D148" s="18">
         <v>346.48</v>
       </c>
-      <c r="E148" s="12"/>
-    </row>
-    <row r="149" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="16">
         <v>46302</v>
       </c>
@@ -4321,9 +4255,8 @@
       <c r="D149" s="17">
         <v>67738.48</v>
       </c>
-      <c r="E149" s="12"/>
-    </row>
-    <row r="150" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="16">
         <v>46302</v>
       </c>
@@ -4336,9 +4269,8 @@
       <c r="D150" s="17">
         <v>3817.53</v>
       </c>
-      <c r="E150" s="12"/>
-    </row>
-    <row r="151" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="16">
         <v>46302</v>
       </c>
@@ -4351,9 +4283,8 @@
       <c r="D151" s="17">
         <v>1037.76</v>
       </c>
-      <c r="E151" s="12"/>
-    </row>
-    <row r="152" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="16">
         <v>46302</v>
       </c>
@@ -4366,9 +4297,8 @@
       <c r="D152" s="18">
         <v>194.22</v>
       </c>
-      <c r="E152" s="12"/>
-    </row>
-    <row r="153" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="16">
         <v>46302</v>
       </c>
@@ -4381,9 +4311,8 @@
       <c r="D153" s="17">
         <v>2494.92</v>
       </c>
-      <c r="E153" s="12"/>
-    </row>
-    <row r="154" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="16">
         <v>46302</v>
       </c>
@@ -4396,9 +4325,8 @@
       <c r="D154" s="17">
         <v>1527.45</v>
       </c>
-      <c r="E154" s="12"/>
-    </row>
-    <row r="155" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="16">
         <v>46302</v>
       </c>
@@ -4411,9 +4339,8 @@
       <c r="D155" s="17">
         <v>1856.48</v>
       </c>
-      <c r="E155" s="12"/>
-    </row>
-    <row r="156" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="16">
         <v>46302</v>
       </c>
@@ -4426,9 +4353,8 @@
       <c r="D156" s="17">
         <v>40702.5</v>
       </c>
-      <c r="E156" s="12"/>
-    </row>
-    <row r="157" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="16">
         <v>46302</v>
       </c>
@@ -4441,9 +4367,8 @@
       <c r="D157" s="17">
         <v>2339.14</v>
       </c>
-      <c r="E157" s="12"/>
-    </row>
-    <row r="158" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="16">
         <v>46302</v>
       </c>
@@ -4456,9 +4381,8 @@
       <c r="D158" s="17">
         <v>5930.6</v>
       </c>
-      <c r="E158" s="12"/>
-    </row>
-    <row r="159" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="16">
         <v>46302</v>
       </c>
@@ -4471,9 +4395,8 @@
       <c r="D159" s="17">
         <v>19636.3</v>
       </c>
-      <c r="E159" s="12"/>
-    </row>
-    <row r="160" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="16">
         <v>46302</v>
       </c>
@@ -4486,9 +4409,8 @@
       <c r="D160" s="29">
         <v>2466.58</v>
       </c>
-      <c r="E160" s="12"/>
-    </row>
-    <row r="161" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="16">
         <v>46303</v>
       </c>
@@ -4501,9 +4423,8 @@
       <c r="D161" s="28">
         <v>2175.1799999999998</v>
       </c>
-      <c r="E161" s="12"/>
-    </row>
-    <row r="162" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="16">
         <v>46303</v>
       </c>
@@ -4516,9 +4437,8 @@
       <c r="D162" s="18">
         <v>975.15</v>
       </c>
-      <c r="E162" s="12"/>
-    </row>
-    <row r="163" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="16">
         <v>46303</v>
       </c>
@@ -4531,9 +4451,8 @@
       <c r="D163" s="18">
         <v>781.83</v>
       </c>
-      <c r="E163" s="12"/>
-    </row>
-    <row r="164" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="16">
         <v>46303</v>
       </c>
@@ -4546,9 +4465,8 @@
       <c r="D164" s="18">
         <v>799.92</v>
       </c>
-      <c r="E164" s="12"/>
-    </row>
-    <row r="165" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="16">
         <v>46303</v>
       </c>
@@ -4561,9 +4479,8 @@
       <c r="D165" s="18">
         <v>795.63</v>
       </c>
-      <c r="E165" s="12"/>
-    </row>
-    <row r="166" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="16">
         <v>46303</v>
       </c>
@@ -4576,9 +4493,8 @@
       <c r="D166" s="18">
         <v>536.52</v>
       </c>
-      <c r="E166" s="12"/>
-    </row>
-    <row r="167" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="16">
         <v>46303</v>
       </c>
@@ -4591,9 +4507,8 @@
       <c r="D167" s="17">
         <v>2858.4</v>
       </c>
-      <c r="E167" s="12"/>
-    </row>
-    <row r="168" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="16">
         <v>46303</v>
       </c>
@@ -4606,9 +4521,8 @@
       <c r="D168" s="17">
         <v>3420</v>
       </c>
-      <c r="E168" s="12"/>
-    </row>
-    <row r="169" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="16">
         <v>46303</v>
       </c>
@@ -4621,9 +4535,8 @@
       <c r="D169" s="17">
         <v>1399.44</v>
       </c>
-      <c r="E169" s="12"/>
-    </row>
-    <row r="170" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="16">
         <v>46303</v>
       </c>
@@ -4636,9 +4549,8 @@
       <c r="D170" s="17">
         <v>129246.28</v>
       </c>
-      <c r="E170" s="12"/>
-    </row>
-    <row r="171" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="16">
         <v>46303</v>
       </c>
@@ -4651,9 +4563,8 @@
       <c r="D171" s="17">
         <v>4986.8999999999996</v>
       </c>
-      <c r="E171" s="12"/>
-    </row>
-    <row r="172" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="16">
         <v>46303</v>
       </c>
@@ -4666,9 +4577,8 @@
       <c r="D172" s="17">
         <v>2569.75</v>
       </c>
-      <c r="E172" s="12"/>
-    </row>
-    <row r="173" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="16">
         <v>46303</v>
       </c>
@@ -4681,9 +4591,8 @@
       <c r="D173" s="17">
         <v>15250.29</v>
       </c>
-      <c r="E173" s="12"/>
-    </row>
-    <row r="174" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="16">
         <v>46303</v>
       </c>
@@ -4696,9 +4605,8 @@
       <c r="D174" s="17">
         <v>1192.51</v>
       </c>
-      <c r="E174" s="12"/>
-    </row>
-    <row r="175" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="16">
         <v>46303</v>
       </c>
@@ -4711,9 +4619,8 @@
       <c r="D175" s="17">
         <v>7149.55</v>
       </c>
-      <c r="E175" s="12"/>
-    </row>
-    <row r="176" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="16">
         <v>46303</v>
       </c>
@@ -4726,9 +4633,8 @@
       <c r="D176" s="18">
         <v>964.8</v>
       </c>
-      <c r="E176" s="12"/>
-    </row>
-    <row r="177" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="16">
         <v>46303</v>
       </c>
@@ -4741,9 +4647,8 @@
       <c r="D177" s="18">
         <v>815.6</v>
       </c>
-      <c r="E177" s="12"/>
-    </row>
-    <row r="178" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="16">
         <v>46303</v>
       </c>
@@ -4756,9 +4661,8 @@
       <c r="D178" s="18">
         <v>34.14</v>
       </c>
-      <c r="E178" s="12"/>
-    </row>
-    <row r="179" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="16">
         <v>46303</v>
       </c>
@@ -4771,9 +4675,8 @@
       <c r="D179" s="17">
         <v>3402.45</v>
       </c>
-      <c r="E179" s="12"/>
-    </row>
-    <row r="180" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="16">
         <v>46303</v>
       </c>
@@ -4786,9 +4689,8 @@
       <c r="D180" s="17">
         <v>73279.55</v>
       </c>
-      <c r="E180" s="12"/>
-    </row>
-    <row r="181" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="16">
         <v>46303</v>
       </c>
@@ -4801,9 +4703,8 @@
       <c r="D181" s="17">
         <v>32405.72</v>
       </c>
-      <c r="E181" s="12"/>
-    </row>
-    <row r="182" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="16">
         <v>46303</v>
       </c>
@@ -4816,9 +4717,8 @@
       <c r="D182" s="17">
         <v>5400</v>
       </c>
-      <c r="E182" s="12"/>
-    </row>
-    <row r="183" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="16">
         <v>46303</v>
       </c>
@@ -4831,9 +4731,8 @@
       <c r="D183" s="17">
         <v>46400</v>
       </c>
-      <c r="E183" s="12"/>
-    </row>
-    <row r="184" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="16">
         <v>46303</v>
       </c>
@@ -4846,9 +4745,8 @@
       <c r="D184" s="18">
         <v>495.54</v>
       </c>
-      <c r="E184" s="12"/>
-    </row>
-    <row r="185" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="16">
         <v>46303</v>
       </c>
@@ -4861,9 +4759,8 @@
       <c r="D185" s="18">
         <v>576</v>
       </c>
-      <c r="E185" s="12"/>
-    </row>
-    <row r="186" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="16">
         <v>46303</v>
       </c>
@@ -4876,9 +4773,8 @@
       <c r="D186" s="17">
         <v>2114</v>
       </c>
-      <c r="E186" s="12"/>
-    </row>
-    <row r="187" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="16">
         <v>46303</v>
       </c>
@@ -4891,9 +4787,8 @@
       <c r="D187" s="17">
         <v>2721.4</v>
       </c>
-      <c r="E187" s="12"/>
-    </row>
-    <row r="188" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="16">
         <v>46303</v>
       </c>
@@ -4906,9 +4801,8 @@
       <c r="D188" s="17">
         <v>18832.75</v>
       </c>
-      <c r="E188" s="12"/>
-    </row>
-    <row r="189" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="16">
         <v>46303</v>
       </c>
@@ -4921,9 +4815,8 @@
       <c r="D189" s="18">
         <v>603.84</v>
       </c>
-      <c r="E189" s="12"/>
-    </row>
-    <row r="190" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="16">
         <v>46303</v>
       </c>
@@ -4936,9 +4829,8 @@
       <c r="D190" s="17">
         <v>6579.82</v>
       </c>
-      <c r="E190" s="12"/>
-    </row>
-    <row r="191" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="16">
         <v>46303</v>
       </c>
@@ -4951,9 +4843,8 @@
       <c r="D191" s="17">
         <v>3189</v>
       </c>
-      <c r="E191" s="12"/>
-    </row>
-    <row r="192" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="16">
         <v>46303</v>
       </c>
@@ -4966,9 +4857,8 @@
       <c r="D192" s="17">
         <v>2649.41</v>
       </c>
-      <c r="E192" s="12"/>
-    </row>
-    <row r="193" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="16">
         <v>46303</v>
       </c>
@@ -4981,9 +4871,8 @@
       <c r="D193" s="17">
         <v>3125.5</v>
       </c>
-      <c r="E193" s="12"/>
-    </row>
-    <row r="194" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="16">
         <v>46303</v>
       </c>
@@ -4996,9 +4885,8 @@
       <c r="D194" s="18">
         <v>917.21</v>
       </c>
-      <c r="E194" s="12"/>
-    </row>
-    <row r="195" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="16">
         <v>46303</v>
       </c>
@@ -5011,9 +4899,8 @@
       <c r="D195" s="17">
         <v>1538.01</v>
       </c>
-      <c r="E195" s="12"/>
-    </row>
-    <row r="196" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="16">
         <v>46303</v>
       </c>
@@ -5026,9 +4913,8 @@
       <c r="D196" s="17">
         <v>4592.87</v>
       </c>
-      <c r="E196" s="12"/>
-    </row>
-    <row r="197" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="16">
         <v>46303</v>
       </c>
@@ -5041,9 +4927,8 @@
       <c r="D197" s="17">
         <v>30502.6</v>
       </c>
-      <c r="E197" s="12"/>
-    </row>
-    <row r="198" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="16">
         <v>46303</v>
       </c>
@@ -5056,9 +4941,8 @@
       <c r="D198" s="17">
         <v>1985.12</v>
       </c>
-      <c r="E198" s="12"/>
-    </row>
-    <row r="199" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="16">
         <v>46303</v>
       </c>
@@ -5071,9 +4955,8 @@
       <c r="D199" s="17">
         <v>1484.3</v>
       </c>
-      <c r="E199" s="12"/>
-    </row>
-    <row r="200" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="16">
         <v>46303</v>
       </c>
@@ -5086,9 +4969,8 @@
       <c r="D200" s="18">
         <v>980.75</v>
       </c>
-      <c r="E200" s="12"/>
-    </row>
-    <row r="201" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="16">
         <v>46303</v>
       </c>
@@ -5101,9 +4983,8 @@
       <c r="D201" s="17">
         <v>2157.64</v>
       </c>
-      <c r="E201" s="12"/>
-    </row>
-    <row r="202" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="16">
         <v>46303</v>
       </c>
@@ -5116,9 +4997,8 @@
       <c r="D202" s="17">
         <v>6608.45</v>
       </c>
-      <c r="E202" s="12"/>
-    </row>
-    <row r="203" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="16">
         <v>46303</v>
       </c>
@@ -5131,9 +5011,8 @@
       <c r="D203" s="18">
         <v>729.5</v>
       </c>
-      <c r="E203" s="12"/>
-    </row>
-    <row r="204" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="16">
         <v>46303</v>
       </c>
@@ -5146,9 +5025,8 @@
       <c r="D204" s="17">
         <v>2525.8000000000002</v>
       </c>
-      <c r="E204" s="12"/>
-    </row>
-    <row r="205" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="16">
         <v>46303</v>
       </c>
@@ -5161,9 +5039,8 @@
       <c r="D205" s="17">
         <v>1549.9</v>
       </c>
-      <c r="E205" s="12"/>
-    </row>
-    <row r="206" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="16">
         <v>46303</v>
       </c>
@@ -5176,9 +5053,8 @@
       <c r="D206" s="18">
         <v>562.20000000000005</v>
       </c>
-      <c r="E206" s="12"/>
-    </row>
-    <row r="207" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="16">
         <v>46303</v>
       </c>
@@ -5191,9 +5067,8 @@
       <c r="D207" s="17">
         <v>5590.1</v>
       </c>
-      <c r="E207" s="12"/>
-    </row>
-    <row r="208" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="16">
         <v>46303</v>
       </c>
@@ -5206,9 +5081,8 @@
       <c r="D208" s="17">
         <v>25103.75</v>
       </c>
-      <c r="E208" s="12"/>
-    </row>
-    <row r="209" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="16">
         <v>46303</v>
       </c>
@@ -5221,9 +5095,8 @@
       <c r="D209" s="17">
         <v>1268.7</v>
       </c>
-      <c r="E209" s="12"/>
-    </row>
-    <row r="210" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="16">
         <v>46303</v>
       </c>
@@ -5236,9 +5109,8 @@
       <c r="D210" s="17">
         <v>1142.56</v>
       </c>
-      <c r="E210" s="12"/>
-    </row>
-    <row r="211" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="16">
         <v>46303</v>
       </c>
@@ -5251,9 +5123,8 @@
       <c r="D211" s="18">
         <v>759.68</v>
       </c>
-      <c r="E211" s="12"/>
-    </row>
-    <row r="212" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="16">
         <v>46303</v>
       </c>
@@ -5266,9 +5137,8 @@
       <c r="D212" s="17">
         <v>6970.5</v>
       </c>
-      <c r="E212" s="12"/>
-    </row>
-    <row r="213" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="16">
         <v>46303</v>
       </c>
@@ -5281,9 +5151,8 @@
       <c r="D213" s="17">
         <v>2969.05</v>
       </c>
-      <c r="E213" s="12"/>
-    </row>
-    <row r="214" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="16">
         <v>46303</v>
       </c>
@@ -5296,9 +5165,8 @@
       <c r="D214" s="17">
         <v>2262</v>
       </c>
-      <c r="E214" s="12"/>
-    </row>
-    <row r="215" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="16">
         <v>46303</v>
       </c>
@@ -5311,9 +5179,8 @@
       <c r="D215" s="17">
         <v>2016</v>
       </c>
-      <c r="E215" s="12"/>
-    </row>
-    <row r="216" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="16">
         <v>46303</v>
       </c>
@@ -5326,9 +5193,8 @@
       <c r="D216" s="17">
         <v>10170.07</v>
       </c>
-      <c r="E216" s="12"/>
-    </row>
-    <row r="217" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="16">
         <v>46303</v>
       </c>
@@ -5341,9 +5207,8 @@
       <c r="D217" s="17">
         <v>11536.09</v>
       </c>
-      <c r="E217" s="12"/>
-    </row>
-    <row r="218" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="16">
         <v>46303</v>
       </c>
@@ -5356,9 +5221,8 @@
       <c r="D218" s="17">
         <v>7650</v>
       </c>
-      <c r="E218" s="12"/>
-    </row>
-    <row r="219" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="16">
         <v>46303</v>
       </c>
@@ -5371,9 +5235,8 @@
       <c r="D219" s="17">
         <v>8832</v>
       </c>
-      <c r="E219" s="12"/>
-    </row>
-    <row r="220" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="16">
         <v>46303</v>
       </c>
@@ -5386,9 +5249,8 @@
       <c r="D220" s="17">
         <v>2627.81</v>
       </c>
-      <c r="E220" s="12"/>
-    </row>
-    <row r="221" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="16">
         <v>46303</v>
       </c>
@@ -5401,9 +5263,8 @@
       <c r="D221" s="17">
         <v>40646.42</v>
       </c>
-      <c r="E221" s="12"/>
-    </row>
-    <row r="222" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="16">
         <v>46303</v>
       </c>
@@ -5416,9 +5277,8 @@
       <c r="D222" s="17">
         <v>7556.7</v>
       </c>
-      <c r="E222" s="12"/>
-    </row>
-    <row r="223" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="16">
         <v>46303</v>
       </c>
@@ -5431,9 +5291,8 @@
       <c r="D223" s="17">
         <v>3416.5</v>
       </c>
-      <c r="E223" s="12"/>
-    </row>
-    <row r="224" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="16">
         <v>46303</v>
       </c>
@@ -5446,9 +5305,8 @@
       <c r="D224" s="17">
         <v>1273.1199999999999</v>
       </c>
-      <c r="E224" s="12"/>
-    </row>
-    <row r="225" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="16">
         <v>46303</v>
       </c>
@@ -5461,9 +5319,8 @@
       <c r="D225" s="17">
         <v>1805.94</v>
       </c>
-      <c r="E225" s="12"/>
-    </row>
-    <row r="226" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="16">
         <v>46303</v>
       </c>
@@ -5476,9 +5333,8 @@
       <c r="D226" s="25">
         <v>923.23</v>
       </c>
-      <c r="E226" s="12"/>
-    </row>
-    <row r="227" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="16">
         <v>46304</v>
       </c>
@@ -5491,9 +5347,8 @@
       <c r="D227" s="33">
         <v>-50078.87</v>
       </c>
-      <c r="E227" s="12"/>
-    </row>
-    <row r="228" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="16">
         <v>46304</v>
       </c>
@@ -5506,9 +5361,8 @@
       <c r="D228" s="17">
         <v>21379.54</v>
       </c>
-      <c r="E228" s="12"/>
-    </row>
-    <row r="229" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="16">
         <v>46304</v>
       </c>
@@ -5521,9 +5375,8 @@
       <c r="D229" s="18">
         <v>681.51</v>
       </c>
-      <c r="E229" s="12"/>
-    </row>
-    <row r="230" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="230" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="16">
         <v>46304</v>
       </c>
@@ -5536,9 +5389,8 @@
       <c r="D230" s="18">
         <v>848.25</v>
       </c>
-      <c r="E230" s="12"/>
-    </row>
-    <row r="231" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="16">
         <v>46304</v>
       </c>
@@ -5551,9 +5403,8 @@
       <c r="D231" s="17">
         <v>8758.8799999999992</v>
       </c>
-      <c r="E231" s="12"/>
-    </row>
-    <row r="232" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="16">
         <v>46304</v>
       </c>
@@ -5566,9 +5417,8 @@
       <c r="D232" s="17">
         <v>6908</v>
       </c>
-      <c r="E232" s="12"/>
-    </row>
-    <row r="233" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="16">
         <v>46304</v>
       </c>
@@ -5581,9 +5431,8 @@
       <c r="D233" s="17">
         <v>1874</v>
       </c>
-      <c r="E233" s="12"/>
-    </row>
-    <row r="234" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="16">
         <v>46304</v>
       </c>
@@ -5596,9 +5445,8 @@
       <c r="D234" s="18">
         <v>764.9</v>
       </c>
-      <c r="E234" s="12"/>
-    </row>
-    <row r="235" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="16">
         <v>46304</v>
       </c>
@@ -5611,9 +5459,8 @@
       <c r="D235" s="17">
         <v>2553.71</v>
       </c>
-      <c r="E235" s="12"/>
-    </row>
-    <row r="236" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="16">
         <v>46304</v>
       </c>
@@ -5626,9 +5473,8 @@
       <c r="D236" s="17">
         <v>11702.28</v>
       </c>
-      <c r="E236" s="12"/>
-    </row>
-    <row r="237" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="237" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="16">
         <v>46304</v>
       </c>
@@ -5641,9 +5487,8 @@
       <c r="D237" s="17">
         <v>37790.199999999997</v>
       </c>
-      <c r="E237" s="12"/>
-    </row>
-    <row r="238" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="16">
         <v>46304</v>
       </c>
@@ -5656,9 +5501,8 @@
       <c r="D238" s="17">
         <v>2537.9699999999998</v>
       </c>
-      <c r="E238" s="12"/>
-    </row>
-    <row r="239" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="16">
         <v>46304</v>
       </c>
@@ -5671,9 +5515,8 @@
       <c r="D239" s="18">
         <v>37.64</v>
       </c>
-      <c r="E239" s="12"/>
-    </row>
-    <row r="240" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="16">
         <v>46304</v>
       </c>
@@ -5686,9 +5529,8 @@
       <c r="D240" s="18">
         <v>62.72</v>
       </c>
-      <c r="E240" s="12"/>
-    </row>
-    <row r="241" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="16">
         <v>46304</v>
       </c>
@@ -5701,9 +5543,8 @@
       <c r="D241" s="17">
         <v>12061.96</v>
       </c>
-      <c r="E241" s="12"/>
-    </row>
-    <row r="242" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="16">
         <v>46304</v>
       </c>
@@ -5716,9 +5557,8 @@
       <c r="D242" s="17">
         <v>1187.5</v>
       </c>
-      <c r="E242" s="12"/>
-    </row>
-    <row r="243" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="16">
         <v>46304</v>
       </c>
@@ -5731,9 +5571,8 @@
       <c r="D243" s="17">
         <v>9111.7800000000007</v>
       </c>
-      <c r="E243" s="12"/>
-    </row>
-    <row r="244" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="16">
         <v>46304</v>
       </c>
@@ -5746,9 +5585,8 @@
       <c r="D244" s="17">
         <v>5155</v>
       </c>
-      <c r="E244" s="12"/>
-    </row>
-    <row r="245" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="245" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="16">
         <v>46304</v>
       </c>
@@ -5761,9 +5599,8 @@
       <c r="D245" s="17">
         <v>35860</v>
       </c>
-      <c r="E245" s="12"/>
-    </row>
-    <row r="246" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="246" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="16">
         <v>46304</v>
       </c>
@@ -5776,9 +5613,8 @@
       <c r="D246" s="17">
         <v>1983.9</v>
       </c>
-      <c r="E246" s="12"/>
-    </row>
-    <row r="247" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="16">
         <v>46304</v>
       </c>
@@ -5791,9 +5627,8 @@
       <c r="D247" s="17">
         <v>4016.04</v>
       </c>
-      <c r="E247" s="12"/>
-    </row>
-    <row r="248" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="16">
         <v>46304</v>
       </c>
@@ -5806,9 +5641,8 @@
       <c r="D248" s="17">
         <v>9225.1</v>
       </c>
-      <c r="E248" s="12"/>
-    </row>
-    <row r="249" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="249" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="16">
         <v>46304</v>
       </c>
@@ -5821,9 +5655,8 @@
       <c r="D249" s="17">
         <v>1271.0999999999999</v>
       </c>
-      <c r="E249" s="12"/>
-    </row>
-    <row r="250" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="16">
         <v>46304</v>
       </c>
@@ -5836,9 +5669,8 @@
       <c r="D250" s="22">
         <v>-20287.580000000002</v>
       </c>
-      <c r="E250" s="12"/>
-    </row>
-    <row r="251" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="16">
         <v>46304</v>
       </c>
@@ -5851,9 +5683,8 @@
       <c r="D251" s="17">
         <v>1760.22</v>
       </c>
-      <c r="E251" s="12"/>
-    </row>
-    <row r="252" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="16">
         <v>46304</v>
       </c>
@@ -5866,9 +5697,8 @@
       <c r="D252" s="18">
         <v>804.72</v>
       </c>
-      <c r="E252" s="12"/>
-    </row>
-    <row r="253" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="16">
         <v>46304</v>
       </c>
@@ -5881,9 +5711,8 @@
       <c r="D253" s="17">
         <v>5131.3999999999996</v>
       </c>
-      <c r="E253" s="12"/>
-    </row>
-    <row r="254" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="16">
         <v>46304</v>
       </c>
@@ -5896,9 +5725,8 @@
       <c r="D254" s="17">
         <v>6740.68</v>
       </c>
-      <c r="E254" s="12"/>
-    </row>
-    <row r="255" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="255" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="16">
         <v>46304</v>
       </c>
@@ -5911,9 +5739,8 @@
       <c r="D255" s="17">
         <v>7095.74</v>
       </c>
-      <c r="E255" s="12"/>
-    </row>
-    <row r="256" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="16">
         <v>46304</v>
       </c>
@@ -5926,9 +5753,8 @@
       <c r="D256" s="17">
         <v>17000</v>
       </c>
-      <c r="E256" s="12"/>
-    </row>
-    <row r="257" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="257" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="16">
         <v>46304</v>
       </c>
@@ -5941,9 +5767,8 @@
       <c r="D257" s="17">
         <v>38852</v>
       </c>
-      <c r="E257" s="12"/>
-    </row>
-    <row r="258" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="258" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="16">
         <v>46304</v>
       </c>
@@ -5956,9 +5781,8 @@
       <c r="D258" s="17">
         <v>4442.67</v>
       </c>
-      <c r="E258" s="12"/>
-    </row>
-    <row r="259" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="16">
         <v>46304</v>
       </c>
@@ -5971,9 +5795,8 @@
       <c r="D259" s="17">
         <v>9365.4</v>
       </c>
-      <c r="E259" s="12"/>
-    </row>
-    <row r="260" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="260" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="16">
         <v>46304</v>
       </c>
@@ -5986,9 +5809,8 @@
       <c r="D260" s="17">
         <v>21547.88</v>
       </c>
-      <c r="E260" s="12"/>
-    </row>
-    <row r="261" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="16">
         <v>46304</v>
       </c>
@@ -6001,9 +5823,8 @@
       <c r="D261" s="17">
         <v>4240.1000000000004</v>
       </c>
-      <c r="E261" s="12"/>
-    </row>
-    <row r="262" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="16">
         <v>46304</v>
       </c>
@@ -6016,9 +5837,8 @@
       <c r="D262" s="17">
         <v>5505.01</v>
       </c>
-      <c r="E262" s="12"/>
-    </row>
-    <row r="263" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="263" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="16">
         <v>46304</v>
       </c>
@@ -6031,9 +5851,8 @@
       <c r="D263" s="17">
         <v>2005.6</v>
       </c>
-      <c r="E263" s="12"/>
-    </row>
-    <row r="264" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="16">
         <v>46304</v>
       </c>
@@ -6046,9 +5865,8 @@
       <c r="D264" s="18">
         <v>697.6</v>
       </c>
-      <c r="E264" s="12"/>
-    </row>
-    <row r="265" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="265" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="16">
         <v>46304</v>
       </c>
@@ -6061,9 +5879,8 @@
       <c r="D265" s="29">
         <v>6832.8</v>
       </c>
-      <c r="E265" s="12"/>
-    </row>
-    <row r="266" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="266" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="16">
         <v>46305</v>
       </c>
@@ -6076,9 +5893,8 @@
       <c r="D266" s="30">
         <v>300.57</v>
       </c>
-      <c r="E266" s="12"/>
-    </row>
-    <row r="267" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="267" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="16">
         <v>46305</v>
       </c>
@@ -6091,9 +5907,8 @@
       <c r="D267" s="18">
         <v>621.6</v>
       </c>
-      <c r="E267" s="12"/>
-    </row>
-    <row r="268" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="16">
         <v>46305</v>
       </c>
@@ -6106,9 +5921,8 @@
       <c r="D268" s="17">
         <v>41294.800000000003</v>
       </c>
-      <c r="E268" s="12"/>
-    </row>
-    <row r="269" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="269" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="16">
         <v>46305</v>
       </c>
@@ -6121,9 +5935,8 @@
       <c r="D269" s="17">
         <v>1455.15</v>
       </c>
-      <c r="E269" s="12"/>
-    </row>
-    <row r="270" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="270" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="16">
         <v>46305</v>
       </c>
@@ -6136,9 +5949,8 @@
       <c r="D270" s="17">
         <v>43200.37</v>
       </c>
-      <c r="E270" s="12"/>
-    </row>
-    <row r="271" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="16">
         <v>46305</v>
       </c>
@@ -6151,9 +5963,8 @@
       <c r="D271" s="17">
         <v>1351.6</v>
       </c>
-      <c r="E271" s="12"/>
-    </row>
-    <row r="272" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="272" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="16">
         <v>46305</v>
       </c>
@@ -6166,9 +5977,8 @@
       <c r="D272" s="17">
         <v>7265.75</v>
       </c>
-      <c r="E272" s="12"/>
-    </row>
-    <row r="273" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="273" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="16">
         <v>46305</v>
       </c>
@@ -6181,9 +5991,8 @@
       <c r="D273" s="17">
         <v>3262.2</v>
       </c>
-      <c r="E273" s="12"/>
-    </row>
-    <row r="274" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="16">
         <v>46305</v>
       </c>
@@ -6196,9 +6005,8 @@
       <c r="D274" s="18">
         <v>457.8</v>
       </c>
-      <c r="E274" s="12"/>
-    </row>
-    <row r="275" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="275" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="16">
         <v>46305</v>
       </c>
@@ -6211,9 +6019,8 @@
       <c r="D275" s="17">
         <v>2831.61</v>
       </c>
-      <c r="E275" s="12"/>
-    </row>
-    <row r="276" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="276" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="16">
         <v>46305</v>
       </c>
@@ -6226,9 +6033,8 @@
       <c r="D276" s="17">
         <v>2439.1</v>
       </c>
-      <c r="E276" s="12"/>
-    </row>
-    <row r="277" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="16">
         <v>46305</v>
       </c>
@@ -6241,9 +6047,8 @@
       <c r="D277" s="17">
         <v>13701.41</v>
       </c>
-      <c r="E277" s="12"/>
-    </row>
-    <row r="278" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="278" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="16">
         <v>46305</v>
       </c>
@@ -6256,9 +6061,8 @@
       <c r="D278" s="18">
         <v>553.5</v>
       </c>
-      <c r="E278" s="12"/>
-    </row>
-    <row r="279" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="16">
         <v>46305</v>
       </c>
@@ -6271,9 +6075,8 @@
       <c r="D279" s="18">
         <v>505.76</v>
       </c>
-      <c r="E279" s="12"/>
-    </row>
-    <row r="280" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="16">
         <v>46305</v>
       </c>
@@ -6286,9 +6089,8 @@
       <c r="D280" s="18">
         <v>305.2</v>
       </c>
-      <c r="E280" s="12"/>
-    </row>
-    <row r="281" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="16">
         <v>46305</v>
       </c>
@@ -6301,9 +6103,8 @@
       <c r="D281" s="17">
         <v>3520.5</v>
       </c>
-      <c r="E281" s="12"/>
-    </row>
-    <row r="282" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="282" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="16">
         <v>46305</v>
       </c>
@@ -6316,9 +6117,8 @@
       <c r="D282" s="17">
         <v>30712.720000000001</v>
       </c>
-      <c r="E282" s="12"/>
-    </row>
-    <row r="283" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="283" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="16">
         <v>46305</v>
       </c>
@@ -6331,9 +6131,8 @@
       <c r="D283" s="17">
         <v>1719.94</v>
       </c>
-      <c r="E283" s="12"/>
-    </row>
-    <row r="284" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="284" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="16">
         <v>46305</v>
       </c>
@@ -6346,9 +6145,8 @@
       <c r="D284" s="18">
         <v>988.87</v>
       </c>
-      <c r="E284" s="12"/>
-    </row>
-    <row r="285" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="285" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="16">
         <v>46305</v>
       </c>
@@ -6361,9 +6159,8 @@
       <c r="D285" s="17">
         <v>8708.09</v>
       </c>
-      <c r="E285" s="12"/>
-    </row>
-    <row r="286" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="286" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="16">
         <v>46305</v>
       </c>
@@ -6376,9 +6173,8 @@
       <c r="D286" s="17">
         <v>7790.69</v>
       </c>
-      <c r="E286" s="12"/>
-    </row>
-    <row r="287" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="287" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="16">
         <v>46305</v>
       </c>
@@ -6391,9 +6187,8 @@
       <c r="D287" s="17">
         <v>8500</v>
       </c>
-      <c r="E287" s="12"/>
-    </row>
-    <row r="288" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="288" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="16">
         <v>46305</v>
       </c>
@@ -6406,9 +6201,8 @@
       <c r="D288" s="29">
         <v>22285.75</v>
       </c>
-      <c r="E288" s="12"/>
-    </row>
-    <row r="289" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="16">
         <v>46306</v>
       </c>
@@ -6421,9 +6215,8 @@
       <c r="D289" s="30">
         <v>650.49</v>
       </c>
-      <c r="E289" s="12"/>
-    </row>
-    <row r="290" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="16">
         <v>46306</v>
       </c>
@@ -6436,9 +6229,8 @@
       <c r="D290" s="18">
         <v>553.83000000000004</v>
       </c>
-      <c r="E290" s="12"/>
-    </row>
-    <row r="291" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="291" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="16">
         <v>46306</v>
       </c>
@@ -6451,9 +6243,8 @@
       <c r="D291" s="18">
         <v>641.76</v>
       </c>
-      <c r="E291" s="12"/>
-    </row>
-    <row r="292" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="292" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="16">
         <v>46306</v>
       </c>
@@ -6466,9 +6257,8 @@
       <c r="D292" s="17">
         <v>2769.2</v>
       </c>
-      <c r="E292" s="12"/>
-    </row>
-    <row r="293" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="293" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="16">
         <v>46306</v>
       </c>
@@ -6481,9 +6271,8 @@
       <c r="D293" s="18">
         <v>352</v>
       </c>
-      <c r="E293" s="12"/>
-    </row>
-    <row r="294" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="294" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="16">
         <v>46306</v>
       </c>
@@ -6496,9 +6285,8 @@
       <c r="D294" s="18">
         <v>740.5</v>
       </c>
-      <c r="E294" s="12"/>
-    </row>
-    <row r="295" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="295" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="16">
         <v>46306</v>
       </c>
@@ -6511,9 +6299,8 @@
       <c r="D295" s="18">
         <v>128.69999999999999</v>
       </c>
-      <c r="E295" s="12"/>
-    </row>
-    <row r="296" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="296" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="16">
         <v>46306</v>
       </c>
@@ -6526,9 +6313,8 @@
       <c r="D296" s="17">
         <v>9196.69</v>
       </c>
-      <c r="E296" s="12"/>
-    </row>
-    <row r="297" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="297" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="16">
         <v>46306</v>
       </c>
@@ -6541,9 +6327,8 @@
       <c r="D297" s="18">
         <v>761.75</v>
       </c>
-      <c r="E297" s="12"/>
-    </row>
-    <row r="298" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="298" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="16">
         <v>46306</v>
       </c>
@@ -6556,9 +6341,8 @@
       <c r="D298" s="18">
         <v>623.29999999999995</v>
       </c>
-      <c r="E298" s="12"/>
-    </row>
-    <row r="299" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="299" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="16">
         <v>46306</v>
       </c>
@@ -6571,9 +6355,8 @@
       <c r="D299" s="17">
         <v>5548.79</v>
       </c>
-      <c r="E299" s="12"/>
-    </row>
-    <row r="300" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="300" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="16">
         <v>46306</v>
       </c>
@@ -6586,9 +6369,8 @@
       <c r="D300" s="18">
         <v>504</v>
       </c>
-      <c r="E300" s="12"/>
-    </row>
-    <row r="301" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="301" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="16">
         <v>46306</v>
       </c>
@@ -6601,9 +6383,8 @@
       <c r="D301" s="18">
         <v>123</v>
       </c>
-      <c r="E301" s="12"/>
-    </row>
-    <row r="302" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="16">
         <v>46306</v>
       </c>
@@ -6616,9 +6397,8 @@
       <c r="D302" s="18">
         <v>504</v>
       </c>
-      <c r="E302" s="12"/>
-    </row>
-    <row r="303" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="303" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="16">
         <v>46306</v>
       </c>
@@ -6631,9 +6411,8 @@
       <c r="D303" s="17">
         <v>7009.72</v>
       </c>
-      <c r="E303" s="12"/>
-    </row>
-    <row r="304" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="304" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="16">
         <v>46306</v>
       </c>
@@ -6646,9 +6425,8 @@
       <c r="D304" s="18">
         <v>355</v>
       </c>
-      <c r="E304" s="12"/>
-    </row>
-    <row r="305" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="305" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="16">
         <v>46306</v>
       </c>
@@ -6661,9 +6439,8 @@
       <c r="D305" s="17">
         <v>8360.6299999999992</v>
       </c>
-      <c r="E305" s="12"/>
-    </row>
-    <row r="306" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="306" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="16">
         <v>46306</v>
       </c>
@@ -6676,9 +6453,8 @@
       <c r="D306" s="17">
         <v>17634.599999999999</v>
       </c>
-      <c r="E306" s="12"/>
-    </row>
-    <row r="307" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="307" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="16">
         <v>46306</v>
       </c>
@@ -6691,9 +6467,8 @@
       <c r="D307" s="18">
         <v>513</v>
       </c>
-      <c r="E307" s="12"/>
-    </row>
-    <row r="308" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="308" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="16">
         <v>46306</v>
       </c>
@@ -6706,9 +6481,8 @@
       <c r="D308" s="18">
         <v>440</v>
       </c>
-      <c r="E308" s="12"/>
-    </row>
-    <row r="309" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="309" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="16">
         <v>46306</v>
       </c>
@@ -6721,9 +6495,8 @@
       <c r="D309" s="17">
         <v>4324.6000000000004</v>
       </c>
-      <c r="E309" s="12"/>
-    </row>
-    <row r="310" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="310" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="16">
         <v>46306</v>
       </c>
@@ -6736,9 +6509,8 @@
       <c r="D310" s="17">
         <v>2556</v>
       </c>
-      <c r="E310" s="12"/>
-    </row>
-    <row r="311" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="311" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="16">
         <v>46306</v>
       </c>
@@ -6751,9 +6523,8 @@
       <c r="D311" s="17">
         <v>1526.04</v>
       </c>
-      <c r="E311" s="12"/>
-    </row>
-    <row r="312" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="312" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="16">
         <v>46306</v>
       </c>
@@ -6766,9 +6537,8 @@
       <c r="D312" s="17">
         <v>1021.28</v>
       </c>
-      <c r="E312" s="12"/>
-    </row>
-    <row r="313" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="313" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="16">
         <v>46306</v>
       </c>
@@ -6781,9 +6551,8 @@
       <c r="D313" s="18">
         <v>704.4</v>
       </c>
-      <c r="E313" s="12"/>
-    </row>
-    <row r="314" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="314" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="16">
         <v>46306</v>
       </c>
@@ -6796,9 +6565,8 @@
       <c r="D314" s="17">
         <v>1281.22</v>
       </c>
-      <c r="E314" s="12"/>
-    </row>
-    <row r="315" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="315" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="16">
         <v>46306</v>
       </c>
@@ -6811,9 +6579,8 @@
       <c r="D315" s="17">
         <v>2384.5700000000002</v>
       </c>
-      <c r="E315" s="12"/>
-    </row>
-    <row r="316" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="316" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="16">
         <v>46306</v>
       </c>
@@ -6826,9 +6593,8 @@
       <c r="D316" s="17">
         <v>5978.3</v>
       </c>
-      <c r="E316" s="12"/>
-    </row>
-    <row r="317" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="317" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="16">
         <v>46306</v>
       </c>
@@ -6841,9 +6607,8 @@
       <c r="D317" s="17">
         <v>2822.1</v>
       </c>
-      <c r="E317" s="12"/>
-    </row>
-    <row r="318" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="318" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="16">
         <v>46306</v>
       </c>
@@ -6856,9 +6621,8 @@
       <c r="D318" s="18">
         <v>566.6</v>
       </c>
-      <c r="E318" s="12"/>
-    </row>
-    <row r="319" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="319" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="16">
         <v>46306</v>
       </c>
@@ -6871,9 +6635,8 @@
       <c r="D319" s="17">
         <v>1611</v>
       </c>
-      <c r="E319" s="12"/>
-    </row>
-    <row r="320" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="320" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="16">
         <v>46306</v>
       </c>
@@ -6886,9 +6649,8 @@
       <c r="D320" s="17">
         <v>14150.4</v>
       </c>
-      <c r="E320" s="12"/>
-    </row>
-    <row r="321" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="321" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="16">
         <v>46306</v>
       </c>
@@ -6901,9 +6663,8 @@
       <c r="D321" s="18">
         <v>237.2</v>
       </c>
-      <c r="E321" s="12"/>
-    </row>
-    <row r="322" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="322" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="16">
         <v>46306</v>
       </c>
@@ -6916,9 +6677,8 @@
       <c r="D322" s="17">
         <v>4093.7</v>
       </c>
-      <c r="E322" s="12"/>
-    </row>
-    <row r="323" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="323" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="16">
         <v>46306</v>
       </c>
@@ -6931,9 +6691,8 @@
       <c r="D323" s="17">
         <v>2575.17</v>
       </c>
-      <c r="E323" s="12"/>
-    </row>
-    <row r="324" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="324" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="16">
         <v>46306</v>
       </c>
@@ -6946,9 +6705,8 @@
       <c r="D324" s="17">
         <v>65472.4</v>
       </c>
-      <c r="E324" s="12"/>
-    </row>
-    <row r="325" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="325" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="16">
         <v>46306</v>
       </c>
@@ -6961,9 +6719,8 @@
       <c r="D325" s="25">
         <v>844.76</v>
       </c>
-      <c r="E325" s="12"/>
-    </row>
-    <row r="326" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="326" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="16">
         <v>46307</v>
       </c>
@@ -6976,9 +6733,8 @@
       <c r="D326" s="28">
         <v>1218.92</v>
       </c>
-      <c r="E326" s="12"/>
-    </row>
-    <row r="327" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="327" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="16">
         <v>46307</v>
       </c>
@@ -6991,9 +6747,8 @@
       <c r="D327" s="17">
         <v>1287</v>
       </c>
-      <c r="E327" s="12"/>
-    </row>
-    <row r="328" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="328" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="16">
         <v>46307</v>
       </c>
@@ -7006,9 +6761,8 @@
       <c r="D328" s="17">
         <v>2341.1</v>
       </c>
-      <c r="E328" s="12"/>
-    </row>
-    <row r="329" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="16">
         <v>46307</v>
       </c>
@@ -7021,9 +6775,8 @@
       <c r="D329" s="18">
         <v>568.62</v>
       </c>
-      <c r="E329" s="12"/>
-    </row>
-    <row r="330" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="330" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="16">
         <v>46307</v>
       </c>
@@ -7036,9 +6789,8 @@
       <c r="D330" s="18">
         <v>667.2</v>
       </c>
-      <c r="E330" s="12"/>
-    </row>
-    <row r="331" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="331" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="16">
         <v>46307</v>
       </c>
@@ -7051,9 +6803,8 @@
       <c r="D331" s="18">
         <v>365.66</v>
       </c>
-      <c r="E331" s="12"/>
-    </row>
-    <row r="332" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="332" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="16">
         <v>46307</v>
       </c>
@@ -7066,9 +6817,8 @@
       <c r="D332" s="17">
         <v>2100</v>
       </c>
-      <c r="E332" s="12"/>
-    </row>
-    <row r="333" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="333" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="16">
         <v>46307</v>
       </c>
@@ -7081,9 +6831,8 @@
       <c r="D333" s="17">
         <v>2158.1</v>
       </c>
-      <c r="E333" s="12"/>
-    </row>
-    <row r="334" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="334" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="16">
         <v>46307</v>
       </c>
@@ -7096,9 +6845,8 @@
       <c r="D334" s="17">
         <v>17054.740000000002</v>
       </c>
-      <c r="E334" s="12"/>
-    </row>
-    <row r="335" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="335" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="16">
         <v>46307</v>
       </c>
@@ -7111,9 +6859,8 @@
       <c r="D335" s="17">
         <v>5722.17</v>
       </c>
-      <c r="E335" s="12"/>
-    </row>
-    <row r="336" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="336" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="16">
         <v>46307</v>
       </c>
@@ -7126,9 +6873,8 @@
       <c r="D336" s="18">
         <v>516.84</v>
       </c>
-      <c r="E336" s="12"/>
-    </row>
-    <row r="337" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="337" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="16">
         <v>46307</v>
       </c>
@@ -7141,9 +6887,8 @@
       <c r="D337" s="17">
         <v>3136.1</v>
       </c>
-      <c r="E337" s="12"/>
-    </row>
-    <row r="338" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="338" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="16">
         <v>46307</v>
       </c>
@@ -7156,9 +6901,8 @@
       <c r="D338" s="17">
         <v>1920</v>
       </c>
-      <c r="E338" s="12"/>
-    </row>
-    <row r="339" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="339" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="16">
         <v>46307</v>
       </c>
@@ -7171,9 +6915,8 @@
       <c r="D339" s="17">
         <v>5388.8</v>
       </c>
-      <c r="E339" s="12"/>
-    </row>
-    <row r="340" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="340" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="16">
         <v>46307</v>
       </c>
@@ -7186,9 +6929,8 @@
       <c r="D340" s="17">
         <v>63968.3</v>
       </c>
-      <c r="E340" s="12"/>
-    </row>
-    <row r="341" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="341" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="16">
         <v>46307</v>
       </c>
@@ -7201,9 +6943,8 @@
       <c r="D341" s="18">
         <v>338.8</v>
       </c>
-      <c r="E341" s="12"/>
-    </row>
-    <row r="342" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="342" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="16">
         <v>46307</v>
       </c>
@@ -7216,9 +6957,8 @@
       <c r="D342" s="17">
         <v>8556.82</v>
       </c>
-      <c r="E342" s="12"/>
-    </row>
-    <row r="343" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="16">
         <v>46307</v>
       </c>
@@ -7231,9 +6971,8 @@
       <c r="D343" s="17">
         <v>6749.72</v>
       </c>
-      <c r="E343" s="12"/>
-    </row>
-    <row r="344" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="344" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="16">
         <v>46307</v>
       </c>
@@ -7246,9 +6985,8 @@
       <c r="D344" s="18">
         <v>952.8</v>
       </c>
-      <c r="E344" s="12"/>
-    </row>
-    <row r="345" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="345" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="16">
         <v>46307</v>
       </c>
@@ -7261,9 +6999,8 @@
       <c r="D345" s="17">
         <v>1126.24</v>
       </c>
-      <c r="E345" s="12"/>
-    </row>
-    <row r="346" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="346" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="16">
         <v>46307</v>
       </c>
@@ -7276,9 +7013,8 @@
       <c r="D346" s="18">
         <v>749.79</v>
       </c>
-      <c r="E346" s="12"/>
-    </row>
-    <row r="347" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="347" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="16">
         <v>46307</v>
       </c>
@@ -7291,9 +7027,8 @@
       <c r="D347" s="17">
         <v>2750.5</v>
       </c>
-      <c r="E347" s="12"/>
-    </row>
-    <row r="348" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="348" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="16">
         <v>46307</v>
       </c>
@@ -7306,9 +7041,8 @@
       <c r="D348" s="17">
         <v>2535.8000000000002</v>
       </c>
-      <c r="E348" s="12"/>
-    </row>
-    <row r="349" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="349" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="16">
         <v>46307</v>
       </c>
@@ -7321,9 +7055,8 @@
       <c r="D349" s="17">
         <v>8514.76</v>
       </c>
-      <c r="E349" s="12"/>
-    </row>
-    <row r="350" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="350" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="16">
         <v>46307</v>
       </c>
@@ -7336,9 +7069,8 @@
       <c r="D350" s="17">
         <v>1363.62</v>
       </c>
-      <c r="E350" s="12"/>
-    </row>
-    <row r="351" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="351" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="16">
         <v>46307</v>
       </c>
@@ -7351,9 +7083,8 @@
       <c r="D351" s="17">
         <v>3681.05</v>
       </c>
-      <c r="E351" s="12"/>
-    </row>
-    <row r="352" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="352" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="16">
         <v>46307</v>
       </c>
@@ -7366,9 +7097,8 @@
       <c r="D352" s="17">
         <v>2009.47</v>
       </c>
-      <c r="E352" s="12"/>
-    </row>
-    <row r="353" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="353" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="16">
         <v>46307</v>
       </c>
@@ -7381,9 +7111,8 @@
       <c r="D353" s="17">
         <v>4417.8999999999996</v>
       </c>
-      <c r="E353" s="12"/>
-    </row>
-    <row r="354" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="354" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="16">
         <v>46307</v>
       </c>
@@ -7396,9 +7125,8 @@
       <c r="D354" s="17">
         <v>2467.12</v>
       </c>
-      <c r="E354" s="12"/>
-    </row>
-    <row r="355" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="355" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="16">
         <v>46307</v>
       </c>
@@ -7411,9 +7139,8 @@
       <c r="D355" s="17">
         <v>8419.14</v>
       </c>
-      <c r="E355" s="12"/>
-    </row>
-    <row r="356" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="16">
         <v>46307</v>
       </c>
@@ -7426,9 +7153,8 @@
       <c r="D356" s="18">
         <v>450</v>
       </c>
-      <c r="E356" s="12"/>
-    </row>
-    <row r="357" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="16">
         <v>46307</v>
       </c>
@@ -7441,9 +7167,8 @@
       <c r="D357" s="17">
         <v>1377.66</v>
       </c>
-      <c r="E357" s="12"/>
-    </row>
-    <row r="358" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="16">
         <v>46307</v>
       </c>
@@ -7456,9 +7181,8 @@
       <c r="D358" s="17">
         <v>1615.1</v>
       </c>
-      <c r="E358" s="12"/>
-    </row>
-    <row r="359" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="359" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="16">
         <v>46307</v>
       </c>
@@ -7471,9 +7195,8 @@
       <c r="D359" s="18">
         <v>596.09</v>
       </c>
-      <c r="E359" s="12"/>
-    </row>
-    <row r="360" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="360" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="16">
         <v>46307</v>
       </c>
@@ -7486,9 +7209,8 @@
       <c r="D360" s="18">
         <v>646.72</v>
       </c>
-      <c r="E360" s="12"/>
-    </row>
-    <row r="361" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="16">
         <v>46307</v>
       </c>
@@ -7501,9 +7223,8 @@
       <c r="D361" s="18">
         <v>224.1</v>
       </c>
-      <c r="E361" s="12"/>
-    </row>
-    <row r="362" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="16">
         <v>46307</v>
       </c>
@@ -7516,9 +7237,8 @@
       <c r="D362" s="17">
         <v>11648.33</v>
       </c>
-      <c r="E362" s="12"/>
-    </row>
-    <row r="363" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="16">
         <v>46307</v>
       </c>
@@ -7531,9 +7251,8 @@
       <c r="D363" s="17">
         <v>8928.52</v>
       </c>
-      <c r="E363" s="12"/>
-    </row>
-    <row r="364" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="16">
         <v>46307</v>
       </c>
@@ -7546,9 +7265,8 @@
       <c r="D364" s="17">
         <v>17519.009999999998</v>
       </c>
-      <c r="E364" s="12"/>
-    </row>
-    <row r="365" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="16">
         <v>46307</v>
       </c>
@@ -7561,9 +7279,8 @@
       <c r="D365" s="17">
         <v>1691.84</v>
       </c>
-      <c r="E365" s="12"/>
-    </row>
-    <row r="366" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="16">
         <v>46307</v>
       </c>
@@ -7576,9 +7293,8 @@
       <c r="D366" s="17">
         <v>1164.4000000000001</v>
       </c>
-      <c r="E366" s="12"/>
-    </row>
-    <row r="367" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="16">
         <v>46307</v>
       </c>
@@ -7591,9 +7307,8 @@
       <c r="D367" s="17">
         <v>1872.8</v>
       </c>
-      <c r="E367" s="12"/>
-    </row>
-    <row r="368" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="16">
         <v>46307</v>
       </c>
@@ -7606,9 +7321,8 @@
       <c r="D368" s="18">
         <v>789.14</v>
       </c>
-      <c r="E368" s="12"/>
-    </row>
-    <row r="369" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="16">
         <v>46307</v>
       </c>
@@ -7621,9 +7335,8 @@
       <c r="D369" s="17">
         <v>2712.68</v>
       </c>
-      <c r="E369" s="12"/>
-    </row>
-    <row r="370" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="16">
         <v>46307</v>
       </c>
@@ -7636,9 +7349,8 @@
       <c r="D370" s="29">
         <v>1991.6</v>
       </c>
-      <c r="E370" s="12"/>
-    </row>
-    <row r="371" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="16">
         <v>46308</v>
       </c>
@@ -7651,9 +7363,8 @@
       <c r="D371" s="28">
         <v>2783.73</v>
       </c>
-      <c r="E371" s="12"/>
-    </row>
-    <row r="372" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="16">
         <v>46308</v>
       </c>
@@ -7666,9 +7377,8 @@
       <c r="D372" s="18">
         <v>283.60000000000002</v>
       </c>
-      <c r="E372" s="12"/>
-    </row>
-    <row r="373" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="16">
         <v>46308</v>
       </c>
@@ -7681,9 +7391,8 @@
       <c r="D373" s="17">
         <v>28735.33</v>
       </c>
-      <c r="E373" s="12"/>
-    </row>
-    <row r="374" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="16">
         <v>46308</v>
       </c>
@@ -7696,9 +7405,8 @@
       <c r="D374" s="17">
         <v>3064.28</v>
       </c>
-      <c r="E374" s="12"/>
-    </row>
-    <row r="375" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="16">
         <v>46308</v>
       </c>
@@ -7711,9 +7419,8 @@
       <c r="D375" s="17">
         <v>1193.1099999999999</v>
       </c>
-      <c r="E375" s="12"/>
-    </row>
-    <row r="376" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="16">
         <v>46308</v>
       </c>
@@ -7726,9 +7433,8 @@
       <c r="D376" s="17">
         <v>1414.25</v>
       </c>
-      <c r="E376" s="12"/>
-    </row>
-    <row r="377" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="16">
         <v>46308</v>
       </c>
@@ -7741,9 +7447,8 @@
       <c r="D377" s="17">
         <v>1165.2</v>
       </c>
-      <c r="E377" s="12"/>
-    </row>
-    <row r="378" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="16">
         <v>46308</v>
       </c>
@@ -7756,9 +7461,8 @@
       <c r="D378" s="18">
         <v>248.9</v>
       </c>
-      <c r="E378" s="12"/>
-    </row>
-    <row r="379" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="16">
         <v>46308</v>
       </c>
@@ -7771,9 +7475,8 @@
       <c r="D379" s="18">
         <v>863.42</v>
       </c>
-      <c r="E379" s="12"/>
-    </row>
-    <row r="380" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="16">
         <v>46308</v>
       </c>
@@ -7786,9 +7489,8 @@
       <c r="D380" s="18">
         <v>300.83999999999997</v>
       </c>
-      <c r="E380" s="12"/>
-    </row>
-    <row r="381" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="16">
         <v>46308</v>
       </c>
@@ -7801,9 +7503,8 @@
       <c r="D381" s="18">
         <v>285.83</v>
       </c>
-      <c r="E381" s="12"/>
-    </row>
-    <row r="382" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="16">
         <v>46308</v>
       </c>
@@ -7816,9 +7517,8 @@
       <c r="D382" s="17">
         <v>23092.46</v>
       </c>
-      <c r="E382" s="12"/>
-    </row>
-    <row r="383" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="16">
         <v>46308</v>
       </c>
@@ -7831,9 +7531,8 @@
       <c r="D383" s="17">
         <v>26935.55</v>
       </c>
-      <c r="E383" s="12"/>
-    </row>
-    <row r="384" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="16">
         <v>46308</v>
       </c>
@@ -7846,9 +7545,8 @@
       <c r="D384" s="21">
         <v>-886.1</v>
       </c>
-      <c r="E384" s="12"/>
-    </row>
-    <row r="385" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="385" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="16">
         <v>46308</v>
       </c>
@@ -7861,9 +7559,8 @@
       <c r="D385" s="17">
         <v>5692.68</v>
       </c>
-      <c r="E385" s="12"/>
-    </row>
-    <row r="386" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="386" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="16">
         <v>46308</v>
       </c>
@@ -7876,9 +7573,8 @@
       <c r="D386" s="17">
         <v>1074</v>
       </c>
-      <c r="E386" s="12"/>
-    </row>
-    <row r="387" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="387" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="16">
         <v>46308</v>
       </c>
@@ -7891,9 +7587,8 @@
       <c r="D387" s="17">
         <v>17585.79</v>
       </c>
-      <c r="E387" s="12"/>
-    </row>
-    <row r="388" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="388" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="16">
         <v>46308</v>
       </c>
@@ -7906,9 +7601,8 @@
       <c r="D388" s="17">
         <v>190584</v>
       </c>
-      <c r="E388" s="12"/>
-    </row>
-    <row r="389" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="389" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="16">
         <v>46308</v>
       </c>
@@ -7921,9 +7615,8 @@
       <c r="D389" s="17">
         <v>67423.039999999994</v>
       </c>
-      <c r="E389" s="12"/>
-    </row>
-    <row r="390" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="390" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="16">
         <v>46308</v>
       </c>
@@ -7936,9 +7629,8 @@
       <c r="D390" s="18">
         <v>578.1</v>
       </c>
-      <c r="E390" s="12"/>
-    </row>
-    <row r="391" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="391" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="16">
         <v>46308</v>
       </c>
@@ -7951,9 +7643,8 @@
       <c r="D391" s="17">
         <v>1003.13</v>
       </c>
-      <c r="E391" s="12"/>
-    </row>
-    <row r="392" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="16">
         <v>46308</v>
       </c>
@@ -7966,9 +7657,8 @@
       <c r="D392" s="17">
         <v>4922.72</v>
       </c>
-      <c r="E392" s="12"/>
-    </row>
-    <row r="393" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="393" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="16">
         <v>46308</v>
       </c>
@@ -7981,9 +7671,8 @@
       <c r="D393" s="22">
         <v>-12182.18</v>
       </c>
-      <c r="E393" s="12"/>
-    </row>
-    <row r="394" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="394" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="16">
         <v>46308</v>
       </c>
@@ -7996,9 +7685,8 @@
       <c r="D394" s="17">
         <v>1346.79</v>
       </c>
-      <c r="E394" s="12"/>
-    </row>
-    <row r="395" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="395" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="16">
         <v>46308</v>
       </c>
@@ -8011,9 +7699,8 @@
       <c r="D395" s="17">
         <v>5236.78</v>
       </c>
-      <c r="E395" s="12"/>
-    </row>
-    <row r="396" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="396" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="16">
         <v>46308</v>
       </c>
@@ -8026,9 +7713,8 @@
       <c r="D396" s="17">
         <v>1498.17</v>
       </c>
-      <c r="E396" s="12"/>
-    </row>
-    <row r="397" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="397" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="16">
         <v>46308</v>
       </c>
@@ -8041,9 +7727,8 @@
       <c r="D397" s="17">
         <v>1249.2</v>
       </c>
-      <c r="E397" s="12"/>
-    </row>
-    <row r="398" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="398" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="16">
         <v>46308</v>
       </c>
@@ -8056,9 +7741,8 @@
       <c r="D398" s="18">
         <v>45.36</v>
       </c>
-      <c r="E398" s="12"/>
-    </row>
-    <row r="399" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="399" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="16">
         <v>46308</v>
       </c>
@@ -8071,9 +7755,8 @@
       <c r="D399" s="17">
         <v>11361.01</v>
       </c>
-      <c r="E399" s="12"/>
-    </row>
-    <row r="400" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="400" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="16">
         <v>46308</v>
       </c>
@@ -8086,9 +7769,8 @@
       <c r="D400" s="17">
         <v>9115.39</v>
       </c>
-      <c r="E400" s="12"/>
-    </row>
-    <row r="401" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="401" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="16">
         <v>46308</v>
       </c>
@@ -8101,9 +7783,8 @@
       <c r="D401" s="17">
         <v>4696.7299999999996</v>
       </c>
-      <c r="E401" s="12"/>
-    </row>
-    <row r="402" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="402" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="16">
         <v>46308</v>
       </c>
@@ -8116,9 +7797,8 @@
       <c r="D402" s="17">
         <v>17732.740000000002</v>
       </c>
-      <c r="E402" s="12"/>
-    </row>
-    <row r="403" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="403" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="16">
         <v>46308</v>
       </c>
@@ -8131,9 +7811,8 @@
       <c r="D403" s="17">
         <v>7943.55</v>
       </c>
-      <c r="E403" s="12"/>
-    </row>
-    <row r="404" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="404" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="16">
         <v>46308</v>
       </c>
@@ -8146,9 +7825,8 @@
       <c r="D404" s="17">
         <v>1531.16</v>
       </c>
-      <c r="E404" s="12"/>
-    </row>
-    <row r="405" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="405" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="16">
         <v>46308</v>
       </c>
@@ -8161,9 +7839,8 @@
       <c r="D405" s="17">
         <v>1965.6</v>
       </c>
-      <c r="E405" s="12"/>
-    </row>
-    <row r="406" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="406" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="16">
         <v>46308</v>
       </c>
@@ -8176,9 +7853,8 @@
       <c r="D406" s="18">
         <v>833.92</v>
       </c>
-      <c r="E406" s="12"/>
-    </row>
-    <row r="407" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="407" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="16">
         <v>46308</v>
       </c>
@@ -8191,9 +7867,8 @@
       <c r="D407" s="17">
         <v>25571.98</v>
       </c>
-      <c r="E407" s="12"/>
-    </row>
-    <row r="408" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="408" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="16">
         <v>46308</v>
       </c>
@@ -8206,9 +7881,8 @@
       <c r="D408" s="17">
         <v>4496.25</v>
       </c>
-      <c r="E408" s="12"/>
-    </row>
-    <row r="409" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="409" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="16">
         <v>46308</v>
       </c>
@@ -8221,9 +7895,8 @@
       <c r="D409" s="17">
         <v>2541</v>
       </c>
-      <c r="E409" s="12"/>
-    </row>
-    <row r="410" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="410" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="16">
         <v>46308</v>
       </c>
@@ -8236,9 +7909,8 @@
       <c r="D410" s="36">
         <v>-16400</v>
       </c>
-      <c r="E410" s="12"/>
-    </row>
-    <row r="411" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="411" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="16">
         <v>46309</v>
       </c>
@@ -8251,9 +7923,8 @@
       <c r="D411" s="28">
         <v>3250</v>
       </c>
-      <c r="E411" s="12"/>
-    </row>
-    <row r="412" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="412" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="16">
         <v>46309</v>
       </c>
@@ -8266,9 +7937,8 @@
       <c r="D412" s="17">
         <v>1668.01</v>
       </c>
-      <c r="E412" s="12"/>
-    </row>
-    <row r="413" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="413" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="16">
         <v>46309</v>
       </c>
@@ -8281,9 +7951,8 @@
       <c r="D413" s="18">
         <v>392.4</v>
       </c>
-      <c r="E413" s="12"/>
-    </row>
-    <row r="414" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="414" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="16">
         <v>46309</v>
       </c>
@@ -8296,9 +7965,8 @@
       <c r="D414" s="17">
         <v>1148.23</v>
       </c>
-      <c r="E414" s="12"/>
-    </row>
-    <row r="415" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="415" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="16">
         <v>46309</v>
       </c>
@@ -8311,9 +7979,8 @@
       <c r="D415" s="18">
         <v>811.2</v>
       </c>
-      <c r="E415" s="12"/>
-    </row>
-    <row r="416" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="416" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="16">
         <v>46309</v>
       </c>
@@ -8326,9 +7993,8 @@
       <c r="D416" s="18">
         <v>43.47</v>
       </c>
-      <c r="E416" s="12"/>
-    </row>
-    <row r="417" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="417" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="16">
         <v>46309</v>
       </c>
@@ -8341,9 +8007,8 @@
       <c r="D417" s="17">
         <v>22411.11</v>
       </c>
-      <c r="E417" s="12"/>
-    </row>
-    <row r="418" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="418" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="16">
         <v>46309</v>
       </c>
@@ -8356,9 +8021,8 @@
       <c r="D418" s="17">
         <v>3131.08</v>
       </c>
-      <c r="E418" s="12"/>
-    </row>
-    <row r="419" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="419" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="16">
         <v>46309</v>
       </c>
@@ -8371,9 +8035,8 @@
       <c r="D419" s="17">
         <v>2160</v>
       </c>
-      <c r="E419" s="12"/>
-    </row>
-    <row r="420" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="420" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="16">
         <v>46309</v>
       </c>
@@ -8386,9 +8049,8 @@
       <c r="D420" s="17">
         <v>6634.8</v>
       </c>
-      <c r="E420" s="12"/>
-    </row>
-    <row r="421" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="421" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="16">
         <v>46309</v>
       </c>
@@ -8401,9 +8063,8 @@
       <c r="D421" s="17">
         <v>10333.950000000001</v>
       </c>
-      <c r="E421" s="12"/>
-    </row>
-    <row r="422" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="422" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="16">
         <v>46309</v>
       </c>
@@ -8416,9 +8077,8 @@
       <c r="D422" s="17">
         <v>1638</v>
       </c>
-      <c r="E422" s="12"/>
-    </row>
-    <row r="423" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="423" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="16">
         <v>46309</v>
       </c>
@@ -8431,9 +8091,8 @@
       <c r="D423" s="17">
         <v>6720</v>
       </c>
-      <c r="E423" s="12"/>
-    </row>
-    <row r="424" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="424" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="16">
         <v>46309</v>
       </c>
@@ -8446,9 +8105,8 @@
       <c r="D424" s="17">
         <v>6518.4</v>
       </c>
-      <c r="E424" s="12"/>
-    </row>
-    <row r="425" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="425" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="16">
         <v>46309</v>
       </c>
@@ -8461,9 +8119,8 @@
       <c r="D425" s="17">
         <v>10092.4</v>
       </c>
-      <c r="E425" s="12"/>
-    </row>
-    <row r="426" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="426" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="16">
         <v>46309</v>
       </c>
@@ -8476,9 +8133,8 @@
       <c r="D426" s="17">
         <v>16382.08</v>
       </c>
-      <c r="E426" s="12"/>
-    </row>
-    <row r="427" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="427" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="16">
         <v>46309</v>
       </c>
@@ -8491,9 +8147,8 @@
       <c r="D427" s="17">
         <v>10213</v>
       </c>
-      <c r="E427" s="12"/>
-    </row>
-    <row r="428" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="428" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="16">
         <v>46309</v>
       </c>
@@ -8506,9 +8161,8 @@
       <c r="D428" s="21">
         <v>-34.5</v>
       </c>
-      <c r="E428" s="12"/>
-    </row>
-    <row r="429" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="429" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="16">
         <v>46309</v>
       </c>
@@ -8521,9 +8175,8 @@
       <c r="D429" s="17">
         <v>44712.71</v>
       </c>
-      <c r="E429" s="12"/>
-    </row>
-    <row r="430" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="430" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A430" s="16">
         <v>46309</v>
       </c>
@@ -8536,9 +8189,8 @@
       <c r="D430" s="17">
         <v>1583.07</v>
       </c>
-      <c r="E430" s="12"/>
-    </row>
-    <row r="431" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="431" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A431" s="16">
         <v>46309</v>
       </c>
@@ -8551,9 +8203,8 @@
       <c r="D431" s="17">
         <v>9284.0400000000009</v>
       </c>
-      <c r="E431" s="12"/>
-    </row>
-    <row r="432" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="432" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A432" s="16">
         <v>46309</v>
       </c>
@@ -8566,9 +8217,8 @@
       <c r="D432" s="17">
         <v>7280.76</v>
       </c>
-      <c r="E432" s="12"/>
-    </row>
-    <row r="433" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="433" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A433" s="16">
         <v>46309</v>
       </c>
@@ -8581,9 +8231,8 @@
       <c r="D433" s="22">
         <v>-2386.0500000000002</v>
       </c>
-      <c r="E433" s="12"/>
-    </row>
-    <row r="434" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="434" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A434" s="16">
         <v>46309</v>
       </c>
@@ -8596,9 +8245,8 @@
       <c r="D434" s="17">
         <v>2811.76</v>
       </c>
-      <c r="E434" s="12"/>
-    </row>
-    <row r="435" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="435" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A435" s="16">
         <v>46309</v>
       </c>
@@ -8611,9 +8259,8 @@
       <c r="D435" s="17">
         <v>1219.98</v>
       </c>
-      <c r="E435" s="12"/>
-    </row>
-    <row r="436" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="436" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A436" s="16">
         <v>46309</v>
       </c>
@@ -8626,9 +8273,8 @@
       <c r="D436" s="18">
         <v>762.9</v>
       </c>
-      <c r="E436" s="12"/>
-    </row>
-    <row r="437" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="437" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A437" s="16">
         <v>46309</v>
       </c>
@@ -8641,9 +8287,8 @@
       <c r="D437" s="17">
         <v>1594.8</v>
       </c>
-      <c r="E437" s="12"/>
-    </row>
-    <row r="438" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="438" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A438" s="16">
         <v>46309</v>
       </c>
@@ -8656,9 +8301,8 @@
       <c r="D438" s="17">
         <v>10130.57</v>
       </c>
-      <c r="E438" s="12"/>
-    </row>
-    <row r="439" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="439" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A439" s="16">
         <v>46309</v>
       </c>
@@ -8671,9 +8315,8 @@
       <c r="D439" s="17">
         <v>1647.31</v>
       </c>
-      <c r="E439" s="12"/>
-    </row>
-    <row r="440" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="440" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A440" s="16">
         <v>46309</v>
       </c>
@@ -8686,9 +8329,8 @@
       <c r="D440" s="17">
         <v>19867.580000000002</v>
       </c>
-      <c r="E440" s="12"/>
-    </row>
-    <row r="441" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="441" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A441" s="16">
         <v>46309</v>
       </c>
@@ -8701,9 +8343,8 @@
       <c r="D441" s="21">
         <v>-69</v>
       </c>
-      <c r="E441" s="12"/>
-    </row>
-    <row r="442" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="442" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A442" s="16">
         <v>46309</v>
       </c>
@@ -8716,9 +8357,8 @@
       <c r="D442" s="22">
         <v>-3434.86</v>
       </c>
-      <c r="E442" s="12"/>
-    </row>
-    <row r="443" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="443" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="16">
         <v>46309</v>
       </c>
@@ -8731,9 +8371,8 @@
       <c r="D443" s="17">
         <v>3165</v>
       </c>
-      <c r="E443" s="12"/>
-    </row>
-    <row r="444" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="444" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A444" s="16">
         <v>46309</v>
       </c>
@@ -8746,9 +8385,8 @@
       <c r="D444" s="17">
         <v>4762.8</v>
       </c>
-      <c r="E444" s="12"/>
-    </row>
-    <row r="445" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="445" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A445" s="16">
         <v>46309</v>
       </c>
@@ -8761,9 +8399,8 @@
       <c r="D445" s="22">
         <v>-8210.1</v>
       </c>
-      <c r="E445" s="12"/>
-    </row>
-    <row r="446" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="446" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A446" s="16">
         <v>46309</v>
       </c>
@@ -8776,9 +8413,8 @@
       <c r="D446" s="17">
         <v>1417.5</v>
       </c>
-      <c r="E446" s="12"/>
-    </row>
-    <row r="447" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="447" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A447" s="16">
         <v>46309</v>
       </c>
@@ -8791,9 +8427,8 @@
       <c r="D447" s="17">
         <v>1749.84</v>
       </c>
-      <c r="E447" s="12"/>
-    </row>
-    <row r="448" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="448" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A448" s="16">
         <v>46309</v>
       </c>
@@ -8806,9 +8441,8 @@
       <c r="D448" s="17">
         <v>3159.05</v>
       </c>
-      <c r="E448" s="12"/>
-    </row>
-    <row r="449" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="449" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A449" s="16">
         <v>46309</v>
       </c>
@@ -8821,9 +8455,8 @@
       <c r="D449" s="17">
         <v>1690.48</v>
       </c>
-      <c r="E449" s="12"/>
-    </row>
-    <row r="450" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="450" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A450" s="16">
         <v>46309</v>
       </c>
@@ -8836,9 +8469,8 @@
       <c r="D450" s="17">
         <v>37130.18</v>
       </c>
-      <c r="E450" s="12"/>
-    </row>
-    <row r="451" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="451" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A451" s="16">
         <v>46309</v>
       </c>
@@ -8851,9 +8483,8 @@
       <c r="D451" s="17">
         <v>13838.8</v>
       </c>
-      <c r="E451" s="12"/>
-    </row>
-    <row r="452" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="452" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A452" s="16">
         <v>46309</v>
       </c>
@@ -8866,9 +8497,8 @@
       <c r="D452" s="17">
         <v>4760</v>
       </c>
-      <c r="E452" s="12"/>
-    </row>
-    <row r="453" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="453" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A453" s="16">
         <v>46309</v>
       </c>
@@ -8881,9 +8511,8 @@
       <c r="D453" s="17">
         <v>2380</v>
       </c>
-      <c r="E453" s="12"/>
-    </row>
-    <row r="454" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="454" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A454" s="16">
         <v>46309</v>
       </c>
@@ -8896,9 +8525,8 @@
       <c r="D454" s="29">
         <v>1406.66</v>
       </c>
-      <c r="E454" s="12"/>
-    </row>
-    <row r="455" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="455" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A455" s="16">
         <v>46310</v>
       </c>
@@ -8911,9 +8539,8 @@
       <c r="D455" s="30">
         <v>466.6</v>
       </c>
-      <c r="E455" s="12"/>
-    </row>
-    <row r="456" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="456" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A456" s="16">
         <v>46310</v>
       </c>
@@ -8926,9 +8553,8 @@
       <c r="D456" s="17">
         <v>2858.4</v>
       </c>
-      <c r="E456" s="12"/>
-    </row>
-    <row r="457" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="457" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A457" s="16">
         <v>46310</v>
       </c>
@@ -8941,9 +8567,8 @@
       <c r="D457" s="17">
         <v>9739.98</v>
       </c>
-      <c r="E457" s="12"/>
-    </row>
-    <row r="458" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="458" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A458" s="16">
         <v>46310</v>
       </c>
@@ -8956,9 +8581,8 @@
       <c r="D458" s="17">
         <v>6734.48</v>
       </c>
-      <c r="E458" s="12"/>
-    </row>
-    <row r="459" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="459" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A459" s="16">
         <v>46310</v>
       </c>
@@ -8971,9 +8595,8 @@
       <c r="D459" s="17">
         <v>3978</v>
       </c>
-      <c r="E459" s="12"/>
-    </row>
-    <row r="460" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="460" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A460" s="16">
         <v>46310</v>
       </c>
@@ -8986,9 +8609,8 @@
       <c r="D460" s="18">
         <v>193.15</v>
       </c>
-      <c r="E460" s="12"/>
-    </row>
-    <row r="461" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="461" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A461" s="16">
         <v>46310</v>
       </c>
@@ -9001,9 +8623,8 @@
       <c r="D461" s="17">
         <v>2574.64</v>
       </c>
-      <c r="E461" s="12"/>
-    </row>
-    <row r="462" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="462" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A462" s="16">
         <v>46310</v>
       </c>
@@ -9016,9 +8637,8 @@
       <c r="D462" s="17">
         <v>1154.73</v>
       </c>
-      <c r="E462" s="12"/>
-    </row>
-    <row r="463" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="463" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A463" s="16">
         <v>46310</v>
       </c>
@@ -9031,9 +8651,8 @@
       <c r="D463" s="17">
         <v>6977.89</v>
       </c>
-      <c r="E463" s="12"/>
-    </row>
-    <row r="464" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="464" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A464" s="16">
         <v>46310</v>
       </c>
@@ -9046,9 +8665,8 @@
       <c r="D464" s="17">
         <v>17074.04</v>
       </c>
-      <c r="E464" s="12"/>
-    </row>
-    <row r="465" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="465" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A465" s="16">
         <v>46310</v>
       </c>
@@ -9061,9 +8679,8 @@
       <c r="D465" s="17">
         <v>2304</v>
       </c>
-      <c r="E465" s="12"/>
-    </row>
-    <row r="466" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="466" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A466" s="16">
         <v>46310</v>
       </c>
@@ -9076,9 +8693,8 @@
       <c r="D466" s="17">
         <v>1520.89</v>
       </c>
-      <c r="E466" s="12"/>
-    </row>
-    <row r="467" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="467" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A467" s="16">
         <v>46310</v>
       </c>
@@ -9091,9 +8707,8 @@
       <c r="D467" s="17">
         <v>12949.2</v>
       </c>
-      <c r="E467" s="12"/>
-    </row>
-    <row r="468" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="468" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A468" s="16">
         <v>46310</v>
       </c>
@@ -9106,9 +8721,8 @@
       <c r="D468" s="17">
         <v>1258.8</v>
       </c>
-      <c r="E468" s="12"/>
-    </row>
-    <row r="469" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="469" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A469" s="16">
         <v>46310</v>
       </c>
@@ -9121,9 +8735,8 @@
       <c r="D469" s="17">
         <v>5413.5</v>
       </c>
-      <c r="E469" s="12"/>
-    </row>
-    <row r="470" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="470" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A470" s="16">
         <v>46310</v>
       </c>
@@ -9136,9 +8749,8 @@
       <c r="D470" s="17">
         <v>31491.9</v>
       </c>
-      <c r="E470" s="12"/>
-    </row>
-    <row r="471" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="471" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A471" s="16">
         <v>46310</v>
       </c>
@@ -9151,9 +8763,8 @@
       <c r="D471" s="17">
         <v>6270.65</v>
       </c>
-      <c r="E471" s="12"/>
-    </row>
-    <row r="472" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="472" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A472" s="16">
         <v>46310</v>
       </c>
@@ -9166,9 +8777,8 @@
       <c r="D472" s="17">
         <v>52512.4</v>
       </c>
-      <c r="E472" s="12"/>
-    </row>
-    <row r="473" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="473" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A473" s="16">
         <v>46310</v>
       </c>
@@ -9181,9 +8791,8 @@
       <c r="D473" s="18">
         <v>621.20000000000005</v>
       </c>
-      <c r="E473" s="12"/>
-    </row>
-    <row r="474" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="474" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A474" s="16">
         <v>46310</v>
       </c>
@@ -9196,9 +8805,8 @@
       <c r="D474" s="18">
         <v>981.19</v>
       </c>
-      <c r="E474" s="12"/>
-    </row>
-    <row r="475" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="475" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A475" s="16">
         <v>46310</v>
       </c>
@@ -9211,9 +8819,8 @@
       <c r="D475" s="17">
         <v>4710.55</v>
       </c>
-      <c r="E475" s="12"/>
-    </row>
-    <row r="476" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="476" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A476" s="16">
         <v>46310</v>
       </c>
@@ -9226,9 +8833,8 @@
       <c r="D476" s="17">
         <v>2399.42</v>
       </c>
-      <c r="E476" s="12"/>
-    </row>
-    <row r="477" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="477" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A477" s="16">
         <v>46310</v>
       </c>
@@ -9241,9 +8847,8 @@
       <c r="D477" s="17">
         <v>2451.42</v>
       </c>
-      <c r="E477" s="12"/>
-    </row>
-    <row r="478" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="478" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A478" s="16">
         <v>46310</v>
       </c>
@@ -9256,9 +8861,8 @@
       <c r="D478" s="17">
         <v>1788.3</v>
       </c>
-      <c r="E478" s="12"/>
-    </row>
-    <row r="479" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="479" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="16">
         <v>46310</v>
       </c>
@@ -9271,9 +8875,8 @@
       <c r="D479" s="17">
         <v>15364.56</v>
       </c>
-      <c r="E479" s="12"/>
-    </row>
-    <row r="480" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="480" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A480" s="16">
         <v>46310</v>
       </c>
@@ -9286,9 +8889,8 @@
       <c r="D480" s="17">
         <v>12803.04</v>
       </c>
-      <c r="E480" s="12"/>
-    </row>
-    <row r="481" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="481" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A481" s="16">
         <v>46310</v>
       </c>
@@ -9301,9 +8903,8 @@
       <c r="D481" s="17">
         <v>4219.2700000000004</v>
       </c>
-      <c r="E481" s="12"/>
-    </row>
-    <row r="482" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="482" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A482" s="16">
         <v>46310</v>
       </c>
@@ -9316,9 +8917,8 @@
       <c r="D482" s="17">
         <v>1374.25</v>
       </c>
-      <c r="E482" s="12"/>
-    </row>
-    <row r="483" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="483" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A483" s="16">
         <v>46310</v>
       </c>
@@ -9331,9 +8931,8 @@
       <c r="D483" s="17">
         <v>1137.3699999999999</v>
       </c>
-      <c r="E483" s="12"/>
-    </row>
-    <row r="484" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="484" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A484" s="16">
         <v>46310</v>
       </c>
@@ -9346,9 +8945,8 @@
       <c r="D484" s="18">
         <v>958.3</v>
       </c>
-      <c r="E484" s="12"/>
-    </row>
-    <row r="485" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="485" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A485" s="16">
         <v>46310</v>
       </c>
@@ -9361,9 +8959,8 @@
       <c r="D485" s="17">
         <v>5366.52</v>
       </c>
-      <c r="E485" s="12"/>
-    </row>
-    <row r="486" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="486" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A486" s="16">
         <v>46310</v>
       </c>
@@ -9376,9 +8973,8 @@
       <c r="D486" s="17">
         <v>2087.5</v>
       </c>
-      <c r="E486" s="12"/>
-    </row>
-    <row r="487" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="487" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A487" s="16">
         <v>46310</v>
       </c>
@@ -9391,9 +8987,8 @@
       <c r="D487" s="18">
         <v>584.9</v>
       </c>
-      <c r="E487" s="12"/>
-    </row>
-    <row r="488" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="488" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A488" s="16">
         <v>46310</v>
       </c>
@@ -9406,9 +9001,8 @@
       <c r="D488" s="17">
         <v>3601.41</v>
       </c>
-      <c r="E488" s="12"/>
-    </row>
-    <row r="489" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="489" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A489" s="16">
         <v>46310</v>
       </c>
@@ -9421,9 +9015,8 @@
       <c r="D489" s="18">
         <v>889.55</v>
       </c>
-      <c r="E489" s="12"/>
-    </row>
-    <row r="490" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="490" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A490" s="16">
         <v>46310</v>
       </c>
@@ -9436,9 +9029,8 @@
       <c r="D490" s="18">
         <v>938.84</v>
       </c>
-      <c r="E490" s="12"/>
-    </row>
-    <row r="491" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="491" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A491" s="16">
         <v>46310</v>
       </c>
@@ -9451,9 +9043,8 @@
       <c r="D491" s="18">
         <v>366.33</v>
       </c>
-      <c r="E491" s="12"/>
-    </row>
-    <row r="492" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="492" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A492" s="16">
         <v>46310</v>
       </c>
@@ -9466,9 +9057,8 @@
       <c r="D492" s="17">
         <v>3484.09</v>
       </c>
-      <c r="E492" s="12"/>
-    </row>
-    <row r="493" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="493" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A493" s="16">
         <v>46310</v>
       </c>
@@ -9481,9 +9071,8 @@
       <c r="D493" s="17">
         <v>2787.7</v>
       </c>
-      <c r="E493" s="12"/>
-    </row>
-    <row r="494" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="494" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A494" s="16">
         <v>46310</v>
       </c>
@@ -9496,9 +9085,8 @@
       <c r="D494" s="17">
         <v>5395.52</v>
       </c>
-      <c r="E494" s="12"/>
-    </row>
-    <row r="495" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="495" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A495" s="16">
         <v>46310</v>
       </c>
@@ -9511,9 +9099,8 @@
       <c r="D495" s="17">
         <v>1746.28</v>
       </c>
-      <c r="E495" s="12"/>
-    </row>
-    <row r="496" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="496" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A496" s="16">
         <v>46310</v>
       </c>
@@ -9526,9 +9113,8 @@
       <c r="D496" s="18">
         <v>241.3</v>
       </c>
-      <c r="E496" s="12"/>
-    </row>
-    <row r="497" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="497" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A497" s="16">
         <v>46310</v>
       </c>
@@ -9541,9 +9127,8 @@
       <c r="D497" s="17">
         <v>4700.8999999999996</v>
       </c>
-      <c r="E497" s="12"/>
-    </row>
-    <row r="498" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="498" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A498" s="16">
         <v>46310</v>
       </c>
@@ -9556,9 +9141,8 @@
       <c r="D498" s="17">
         <v>1305.9000000000001</v>
       </c>
-      <c r="E498" s="12"/>
-    </row>
-    <row r="499" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="499" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A499" s="16">
         <v>46310</v>
       </c>
@@ -9571,9 +9155,8 @@
       <c r="D499" s="17">
         <v>1227.8</v>
       </c>
-      <c r="E499" s="12"/>
-    </row>
-    <row r="500" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="500" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A500" s="16">
         <v>46310</v>
       </c>
@@ -9586,9 +9169,8 @@
       <c r="D500" s="17">
         <v>1203.5999999999999</v>
       </c>
-      <c r="E500" s="12"/>
-    </row>
-    <row r="501" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="501" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A501" s="16">
         <v>46310</v>
       </c>
@@ -9601,9 +9183,8 @@
       <c r="D501" s="17">
         <v>1592.28</v>
       </c>
-      <c r="E501" s="12"/>
-    </row>
-    <row r="502" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="502" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A502" s="16">
         <v>46310</v>
       </c>
@@ -9616,9 +9197,8 @@
       <c r="D502" s="17">
         <v>22384.3</v>
       </c>
-      <c r="E502" s="12"/>
-    </row>
-    <row r="503" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="503" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A503" s="16">
         <v>46310</v>
       </c>
@@ -9631,9 +9211,8 @@
       <c r="D503" s="18">
         <v>295.89999999999998</v>
       </c>
-      <c r="E503" s="12"/>
-    </row>
-    <row r="504" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="504" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A504" s="16">
         <v>46310</v>
       </c>
@@ -9646,9 +9225,8 @@
       <c r="D504" s="18">
         <v>360</v>
       </c>
-      <c r="E504" s="12"/>
-    </row>
-    <row r="505" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="505" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A505" s="16">
         <v>46310</v>
       </c>
@@ -9661,9 +9239,8 @@
       <c r="D505" s="18">
         <v>719.4</v>
       </c>
-      <c r="E505" s="12"/>
-    </row>
-    <row r="506" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="506" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A506" s="16">
         <v>46310</v>
       </c>
@@ -9676,9 +9253,8 @@
       <c r="D506" s="17">
         <v>3064.44</v>
       </c>
-      <c r="E506" s="12"/>
-    </row>
-    <row r="507" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="507" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A507" s="16">
         <v>46310</v>
       </c>
@@ -9691,9 +9267,8 @@
       <c r="D507" s="17">
         <v>2398</v>
       </c>
-      <c r="E507" s="12"/>
-    </row>
-    <row r="508" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="508" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A508" s="16">
         <v>46310</v>
       </c>
@@ -9706,9 +9281,8 @@
       <c r="D508" s="18">
         <v>294.3</v>
       </c>
-      <c r="E508" s="12"/>
-    </row>
-    <row r="509" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="509" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A509" s="16">
         <v>46310</v>
       </c>
@@ -9721,9 +9295,8 @@
       <c r="D509" s="25">
         <v>100.28</v>
       </c>
-      <c r="E509" s="12"/>
-    </row>
-    <row r="510" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="510" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A510" s="16">
         <v>46311</v>
       </c>
@@ -9736,9 +9309,8 @@
       <c r="D510" s="28">
         <v>32122.91</v>
       </c>
-      <c r="E510" s="12"/>
-    </row>
-    <row r="511" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="511" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A511" s="16">
         <v>46311</v>
       </c>
@@ -9751,9 +9323,8 @@
       <c r="D511" s="17">
         <v>71159.070000000007</v>
       </c>
-      <c r="E511" s="12"/>
-    </row>
-    <row r="512" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="512" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A512" s="16">
         <v>46311</v>
       </c>
@@ -9766,9 +9337,8 @@
       <c r="D512" s="17">
         <v>37009.65</v>
       </c>
-      <c r="E512" s="12"/>
-    </row>
-    <row r="513" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="513" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A513" s="16">
         <v>46311</v>
       </c>
@@ -9781,9 +9351,8 @@
       <c r="D513" s="17">
         <v>44061.99</v>
       </c>
-      <c r="E513" s="12"/>
-    </row>
-    <row r="514" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="514" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A514" s="16">
         <v>46311</v>
       </c>
@@ -9796,9 +9365,8 @@
       <c r="D514" s="17">
         <v>184150.64</v>
       </c>
-      <c r="E514" s="12"/>
-    </row>
-    <row r="515" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="515" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A515" s="16">
         <v>46311</v>
       </c>
@@ -9811,9 +9379,8 @@
       <c r="D515" s="17">
         <v>75218.929999999993</v>
       </c>
-      <c r="E515" s="12"/>
-    </row>
-    <row r="516" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="516" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A516" s="16">
         <v>46311</v>
       </c>
@@ -9826,9 +9393,8 @@
       <c r="D516" s="17">
         <v>20275.66</v>
       </c>
-      <c r="E516" s="12"/>
-    </row>
-    <row r="517" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="517" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A517" s="16">
         <v>46311</v>
       </c>
@@ -9841,9 +9407,8 @@
       <c r="D517" s="17">
         <v>352337.1</v>
       </c>
-      <c r="E517" s="12"/>
-    </row>
-    <row r="518" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="518" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A518" s="16">
         <v>46311</v>
       </c>
@@ -9856,9 +9421,8 @@
       <c r="D518" s="17">
         <v>9696</v>
       </c>
-      <c r="E518" s="12"/>
-    </row>
-    <row r="519" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="519" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A519" s="16">
         <v>46311</v>
       </c>
@@ -9871,9 +9435,8 @@
       <c r="D519" s="17">
         <v>1225.1199999999999</v>
       </c>
-      <c r="E519" s="12"/>
-    </row>
-    <row r="520" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="520" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A520" s="16">
         <v>46311</v>
       </c>
@@ -9886,9 +9449,8 @@
       <c r="D520" s="17">
         <v>7252.16</v>
       </c>
-      <c r="E520" s="12"/>
-    </row>
-    <row r="521" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="521" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A521" s="16">
         <v>46311</v>
       </c>
@@ -9901,9 +9463,8 @@
       <c r="D521" s="17">
         <v>16783.7</v>
       </c>
-      <c r="E521" s="12"/>
-    </row>
-    <row r="522" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="522" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A522" s="16">
         <v>46311</v>
       </c>
@@ -9916,9 +9477,8 @@
       <c r="D522" s="17">
         <v>4832</v>
       </c>
-      <c r="E522" s="12"/>
-    </row>
-    <row r="523" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="523" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A523" s="16">
         <v>46311</v>
       </c>
@@ -9931,9 +9491,8 @@
       <c r="D523" s="18">
         <v>501.3</v>
       </c>
-      <c r="E523" s="12"/>
-    </row>
-    <row r="524" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="524" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A524" s="16">
         <v>46311</v>
       </c>
@@ -9946,9 +9505,8 @@
       <c r="D524" s="17">
         <v>1650</v>
       </c>
-      <c r="E524" s="12"/>
-    </row>
-    <row r="525" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="525" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A525" s="16">
         <v>46311</v>
       </c>
@@ -9961,9 +9519,8 @@
       <c r="D525" s="18">
         <v>543.67999999999995</v>
       </c>
-      <c r="E525" s="12"/>
-    </row>
-    <row r="526" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="526" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A526" s="16">
         <v>46311</v>
       </c>
@@ -9976,9 +9533,8 @@
       <c r="D526" s="18">
         <v>823.55</v>
       </c>
-      <c r="E526" s="12"/>
-    </row>
-    <row r="527" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="527" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A527" s="16">
         <v>46311</v>
       </c>
@@ -9991,9 +9547,8 @@
       <c r="D527" s="17">
         <v>1807.29</v>
       </c>
-      <c r="E527" s="12"/>
-    </row>
-    <row r="528" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="528" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="16">
         <v>46311</v>
       </c>
@@ -10006,9 +9561,8 @@
       <c r="D528" s="17">
         <v>87368.02</v>
       </c>
-      <c r="E528" s="12"/>
-    </row>
-    <row r="529" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="529" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A529" s="16">
         <v>46311</v>
       </c>
@@ -10021,9 +9575,8 @@
       <c r="D529" s="17">
         <v>2550</v>
       </c>
-      <c r="E529" s="12"/>
-    </row>
-    <row r="530" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="530" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A530" s="16">
         <v>46311</v>
       </c>
@@ -10036,9 +9589,8 @@
       <c r="D530" s="17">
         <v>1978.55</v>
       </c>
-      <c r="E530" s="12"/>
-    </row>
-    <row r="531" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="531" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A531" s="16">
         <v>46311</v>
       </c>
@@ -10051,9 +9603,8 @@
       <c r="D531" s="17">
         <v>10697.12</v>
       </c>
-      <c r="E531" s="12"/>
-    </row>
-    <row r="532" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="532" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A532" s="16">
         <v>46311</v>
       </c>
@@ -10066,9 +9617,8 @@
       <c r="D532" s="17">
         <v>108834.32</v>
       </c>
-      <c r="E532" s="12"/>
-    </row>
-    <row r="533" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="533" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A533" s="16">
         <v>46311</v>
       </c>
@@ -10081,9 +9631,8 @@
       <c r="D533" s="17">
         <v>6213.73</v>
       </c>
-      <c r="E533" s="12"/>
-    </row>
-    <row r="534" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="534" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A534" s="16">
         <v>46311</v>
       </c>
@@ -10096,9 +9645,8 @@
       <c r="D534" s="17">
         <v>31559.200000000001</v>
       </c>
-      <c r="E534" s="12"/>
-    </row>
-    <row r="535" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="535" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A535" s="16">
         <v>46311</v>
       </c>
@@ -10111,9 +9659,8 @@
       <c r="D535" s="17">
         <v>3239.37</v>
       </c>
-      <c r="E535" s="12"/>
-    </row>
-    <row r="536" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="536" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A536" s="16">
         <v>46311</v>
       </c>
@@ -10126,9 +9673,8 @@
       <c r="D536" s="17">
         <v>11946.84</v>
       </c>
-      <c r="E536" s="12"/>
-    </row>
-    <row r="537" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="537" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A537" s="16">
         <v>46311</v>
       </c>
@@ -10141,9 +9687,8 @@
       <c r="D537" s="18">
         <v>734.03</v>
       </c>
-      <c r="E537" s="12"/>
-    </row>
-    <row r="538" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="538" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A538" s="16">
         <v>46311</v>
       </c>
@@ -10156,9 +9701,8 @@
       <c r="D538" s="17">
         <v>1249.75</v>
       </c>
-      <c r="E538" s="12"/>
-    </row>
-    <row r="539" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="539" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A539" s="16">
         <v>46311</v>
       </c>
@@ -10171,9 +9715,8 @@
       <c r="D539" s="17">
         <v>1095.5</v>
       </c>
-      <c r="E539" s="12"/>
-    </row>
-    <row r="540" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="540" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A540" s="16">
         <v>46311</v>
       </c>
@@ -10186,9 +9729,8 @@
       <c r="D540" s="17">
         <v>3746.95</v>
       </c>
-      <c r="E540" s="12"/>
-    </row>
-    <row r="541" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="541" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A541" s="16">
         <v>46311</v>
       </c>
@@ -10201,9 +9743,8 @@
       <c r="D541" s="17">
         <v>5653.55</v>
       </c>
-      <c r="E541" s="12"/>
-    </row>
-    <row r="542" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="542" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A542" s="16">
         <v>46311</v>
       </c>
@@ -10216,9 +9757,8 @@
       <c r="D542" s="17">
         <v>1133.6099999999999</v>
       </c>
-      <c r="E542" s="12"/>
-    </row>
-    <row r="543" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="543" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A543" s="16">
         <v>46311</v>
       </c>
@@ -10231,9 +9771,8 @@
       <c r="D543" s="18">
         <v>642.83000000000004</v>
       </c>
-      <c r="E543" s="12"/>
-    </row>
-    <row r="544" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="544" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A544" s="16">
         <v>46311</v>
       </c>
@@ -10246,9 +9785,8 @@
       <c r="D544" s="17">
         <v>2548</v>
       </c>
-      <c r="E544" s="12"/>
-    </row>
-    <row r="545" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="545" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A545" s="16">
         <v>46311</v>
       </c>
@@ -10261,9 +9799,8 @@
       <c r="D545" s="17">
         <v>4749</v>
       </c>
-      <c r="E545" s="12"/>
-    </row>
-    <row r="546" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="546" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A546" s="16">
         <v>46311</v>
       </c>
@@ -10276,9 +9813,8 @@
       <c r="D546" s="17">
         <v>5210.75</v>
       </c>
-      <c r="E546" s="12"/>
-    </row>
-    <row r="547" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="547" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A547" s="16">
         <v>46311</v>
       </c>
@@ -10291,9 +9827,8 @@
       <c r="D547" s="18">
         <v>943.12</v>
       </c>
-      <c r="E547" s="12"/>
-    </row>
-    <row r="548" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="548" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A548" s="16">
         <v>46311</v>
       </c>
@@ -10306,9 +9841,8 @@
       <c r="D548" s="17">
         <v>2530.02</v>
       </c>
-      <c r="E548" s="12"/>
-    </row>
-    <row r="549" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="549" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A549" s="16">
         <v>46311</v>
       </c>
@@ -10321,9 +9855,8 @@
       <c r="D549" s="17">
         <v>1931.94</v>
       </c>
-      <c r="E549" s="12"/>
-    </row>
-    <row r="550" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="550" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A550" s="16">
         <v>46311</v>
       </c>
@@ -10336,9 +9869,8 @@
       <c r="D550" s="17">
         <v>5616.03</v>
       </c>
-      <c r="E550" s="12"/>
-    </row>
-    <row r="551" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="551" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A551" s="16">
         <v>46311</v>
       </c>
@@ -10351,9 +9883,8 @@
       <c r="D551" s="18">
         <v>637.37</v>
       </c>
-      <c r="E551" s="12"/>
-    </row>
-    <row r="552" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="552" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A552" s="16">
         <v>46311</v>
       </c>
@@ -10366,9 +9897,8 @@
       <c r="D552" s="18">
         <v>794.88</v>
       </c>
-      <c r="E552" s="12"/>
-    </row>
-    <row r="553" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="553" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A553" s="16">
         <v>46311</v>
       </c>
@@ -10381,9 +9911,8 @@
       <c r="D553" s="17">
         <v>1260</v>
       </c>
-      <c r="E553" s="12"/>
-    </row>
-    <row r="554" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="554" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A554" s="16">
         <v>46311</v>
       </c>
@@ -10396,9 +9925,8 @@
       <c r="D554" s="17">
         <v>25324.1</v>
       </c>
-      <c r="E554" s="12"/>
-    </row>
-    <row r="555" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="555" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A555" s="16">
         <v>46311</v>
       </c>
@@ -10411,9 +9939,8 @@
       <c r="D555" s="17">
         <v>4278.84</v>
       </c>
-      <c r="E555" s="12"/>
-    </row>
-    <row r="556" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="556" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A556" s="16">
         <v>46311</v>
       </c>
@@ -10426,9 +9953,8 @@
       <c r="D556" s="18">
         <v>969.83</v>
       </c>
-      <c r="E556" s="12"/>
-    </row>
-    <row r="557" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="557" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A557" s="16">
         <v>46311</v>
       </c>
@@ -10441,9 +9967,8 @@
       <c r="D557" s="17">
         <v>4092.84</v>
       </c>
-      <c r="E557" s="12"/>
-    </row>
-    <row r="558" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="558" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A558" s="16">
         <v>46311</v>
       </c>
@@ -10456,9 +9981,8 @@
       <c r="D558" s="18">
         <v>715.19</v>
       </c>
-      <c r="E558" s="12"/>
-    </row>
-    <row r="559" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="559" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A559" s="16">
         <v>46311</v>
       </c>
@@ -10471,9 +9995,8 @@
       <c r="D559" s="17">
         <v>5750.58</v>
       </c>
-      <c r="E559" s="12"/>
-    </row>
-    <row r="560" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="560" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A560" s="16">
         <v>46311</v>
       </c>
@@ -10486,9 +10009,8 @@
       <c r="D560" s="17">
         <v>3769.29</v>
       </c>
-      <c r="E560" s="12"/>
-    </row>
-    <row r="561" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="561" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A561" s="16">
         <v>46311</v>
       </c>
@@ -10501,9 +10023,8 @@
       <c r="D561" s="17">
         <v>7241.05</v>
       </c>
-      <c r="E561" s="12"/>
-    </row>
-    <row r="562" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="562" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A562" s="16">
         <v>46311</v>
       </c>
@@ -10516,9 +10037,8 @@
       <c r="D562" s="17">
         <v>3196.24</v>
       </c>
-      <c r="E562" s="12"/>
-    </row>
-    <row r="563" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="563" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A563" s="16">
         <v>46311</v>
       </c>
@@ -10531,9 +10051,8 @@
       <c r="D563" s="17">
         <v>7577.7</v>
       </c>
-      <c r="E563" s="12"/>
-    </row>
-    <row r="564" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="564" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A564" s="16">
         <v>46311</v>
       </c>
@@ -10546,9 +10065,8 @@
       <c r="D564" s="17">
         <v>2729.69</v>
       </c>
-      <c r="E564" s="12"/>
-    </row>
-    <row r="565" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="565" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A565" s="16">
         <v>46311</v>
       </c>
@@ -10561,9 +10079,8 @@
       <c r="D565" s="17">
         <v>1828.47</v>
       </c>
-      <c r="E565" s="12"/>
-    </row>
-    <row r="566" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="566" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A566" s="16">
         <v>46311</v>
       </c>
@@ -10576,9 +10093,8 @@
       <c r="D566" s="17">
         <v>1442.5</v>
       </c>
-      <c r="E566" s="12"/>
-    </row>
-    <row r="567" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="567" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A567" s="16">
         <v>46311</v>
       </c>
@@ -10591,9 +10107,8 @@
       <c r="D567" s="17">
         <v>6617.7</v>
       </c>
-      <c r="E567" s="12"/>
-    </row>
-    <row r="568" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="568" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A568" s="16">
         <v>46311</v>
       </c>
@@ -10606,9 +10121,8 @@
       <c r="D568" s="17">
         <v>20124.900000000001</v>
       </c>
-      <c r="E568" s="12"/>
-    </row>
-    <row r="569" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="569" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A569" s="16">
         <v>46311</v>
       </c>
@@ -10621,9 +10135,8 @@
       <c r="D569" s="17">
         <v>1577.28</v>
       </c>
-      <c r="E569" s="12"/>
-    </row>
-    <row r="570" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="570" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A570" s="16">
         <v>46311</v>
       </c>
@@ -10636,9 +10149,8 @@
       <c r="D570" s="17">
         <v>9912</v>
       </c>
-      <c r="E570" s="12"/>
-    </row>
-    <row r="571" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="571" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A571" s="16">
         <v>46311</v>
       </c>
@@ -10651,9 +10163,8 @@
       <c r="D571" s="17">
         <v>42350</v>
       </c>
-      <c r="E571" s="12"/>
-    </row>
-    <row r="572" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="572" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A572" s="16">
         <v>46311</v>
       </c>
@@ -10666,9 +10177,8 @@
       <c r="D572" s="17">
         <v>4335</v>
       </c>
-      <c r="E572" s="12"/>
-    </row>
-    <row r="573" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="573" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A573" s="16">
         <v>46311</v>
       </c>
@@ -10681,9 +10191,8 @@
       <c r="D573" s="17">
         <v>8100</v>
       </c>
-      <c r="E573" s="12"/>
-    </row>
-    <row r="574" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="574" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A574" s="16">
         <v>46311</v>
       </c>
@@ -10696,9 +10205,8 @@
       <c r="D574" s="18">
         <v>968.87</v>
       </c>
-      <c r="E574" s="12"/>
-    </row>
-    <row r="575" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="575" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A575" s="16">
         <v>46311</v>
       </c>
@@ -10711,9 +10219,8 @@
       <c r="D575" s="17">
         <v>2400.84</v>
       </c>
-      <c r="E575" s="12"/>
-    </row>
-    <row r="576" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="576" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A576" s="16">
         <v>46311</v>
       </c>
@@ -10726,9 +10233,8 @@
       <c r="D576" s="17">
         <v>3167.27</v>
       </c>
-      <c r="E576" s="12"/>
-    </row>
-    <row r="577" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="577" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A577" s="16">
         <v>46311</v>
       </c>
@@ -10741,9 +10247,8 @@
       <c r="D577" s="18">
         <v>67.8</v>
       </c>
-      <c r="E577" s="12"/>
-    </row>
-    <row r="578" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="578" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A578" s="16">
         <v>46311</v>
       </c>
@@ -10756,9 +10261,8 @@
       <c r="D578" s="18">
         <v>261.92</v>
       </c>
-      <c r="E578" s="12"/>
-    </row>
-    <row r="579" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="579" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A579" s="16">
         <v>46311</v>
       </c>
@@ -10771,9 +10275,8 @@
       <c r="D579" s="29">
         <v>12833</v>
       </c>
-      <c r="E579" s="12"/>
-    </row>
-    <row r="580" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="580" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A580" s="16">
         <v>46314</v>
       </c>
@@ -10786,9 +10289,8 @@
       <c r="D580" s="28">
         <v>1003.1</v>
       </c>
-      <c r="E580" s="12"/>
-    </row>
-    <row r="581" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="581" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A581" s="16">
         <v>46314</v>
       </c>
@@ -10801,9 +10303,8 @@
       <c r="D581" s="17">
         <v>6082</v>
       </c>
-      <c r="E581" s="12"/>
-    </row>
-    <row r="582" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="582" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A582" s="16">
         <v>46314</v>
       </c>
@@ -10816,9 +10317,8 @@
       <c r="D582" s="17">
         <v>28389.8</v>
       </c>
-      <c r="E582" s="12"/>
-    </row>
-    <row r="583" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="583" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A583" s="16">
         <v>46314</v>
       </c>
@@ -10831,9 +10331,8 @@
       <c r="D583" s="17">
         <v>1192.8399999999999</v>
       </c>
-      <c r="E583" s="12"/>
-    </row>
-    <row r="584" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="584" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A584" s="16">
         <v>46314</v>
       </c>
@@ -10846,9 +10345,8 @@
       <c r="D584" s="17">
         <v>1260.49</v>
       </c>
-      <c r="E584" s="12"/>
-    </row>
-    <row r="585" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="585" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A585" s="16">
         <v>46314</v>
       </c>
@@ -10861,9 +10359,8 @@
       <c r="D585" s="17">
         <v>4977.3</v>
       </c>
-      <c r="E585" s="12"/>
-    </row>
-    <row r="586" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="586" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A586" s="16">
         <v>46314</v>
       </c>
@@ -10876,9 +10373,8 @@
       <c r="D586" s="17">
         <v>1476.75</v>
       </c>
-      <c r="E586" s="12"/>
-    </row>
-    <row r="587" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="587" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A587" s="16">
         <v>46314</v>
       </c>
@@ -10891,9 +10387,8 @@
       <c r="D587" s="18">
         <v>588.88</v>
       </c>
-      <c r="E587" s="12"/>
-    </row>
-    <row r="588" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="588" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A588" s="16">
         <v>46314</v>
       </c>
@@ -10906,9 +10401,8 @@
       <c r="D588" s="17">
         <v>11019</v>
       </c>
-      <c r="E588" s="12"/>
-    </row>
-    <row r="589" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="589" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A589" s="16">
         <v>46314</v>
       </c>
@@ -10921,9 +10415,8 @@
       <c r="D589" s="17">
         <v>1697.12</v>
       </c>
-      <c r="E589" s="12"/>
-    </row>
-    <row r="590" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="590" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A590" s="16">
         <v>46314</v>
       </c>
@@ -10936,9 +10429,8 @@
       <c r="D590" s="18">
         <v>511.2</v>
       </c>
-      <c r="E590" s="12"/>
-    </row>
-    <row r="591" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="591" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A591" s="16">
         <v>46314</v>
       </c>
@@ -10951,9 +10443,8 @@
       <c r="D591" s="17">
         <v>7325.81</v>
       </c>
-      <c r="E591" s="12"/>
-    </row>
-    <row r="592" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="592" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A592" s="16">
         <v>46314</v>
       </c>
@@ -10966,9 +10457,8 @@
       <c r="D592" s="17">
         <v>17289.98</v>
       </c>
-      <c r="E592" s="12"/>
-    </row>
-    <row r="593" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="593" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A593" s="16">
         <v>46314</v>
       </c>
@@ -10981,9 +10471,8 @@
       <c r="D593" s="17">
         <v>23280</v>
       </c>
-      <c r="E593" s="12"/>
-    </row>
-    <row r="594" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="594" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A594" s="16">
         <v>46314</v>
       </c>
@@ -10996,9 +10485,8 @@
       <c r="D594" s="18">
         <v>740.39</v>
       </c>
-      <c r="E594" s="12"/>
-    </row>
-    <row r="595" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="595" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A595" s="16">
         <v>46314</v>
       </c>
@@ -11011,9 +10499,8 @@
       <c r="D595" s="18">
         <v>420</v>
       </c>
-      <c r="E595" s="12"/>
-    </row>
-    <row r="596" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="596" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A596" s="16">
         <v>46314</v>
       </c>
@@ -11026,9 +10513,8 @@
       <c r="D596" s="18">
         <v>209.72</v>
       </c>
-      <c r="E596" s="12"/>
-    </row>
-    <row r="597" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="597" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A597" s="16">
         <v>46314</v>
       </c>
@@ -11041,9 +10527,8 @@
       <c r="D597" s="17">
         <v>6516.26</v>
       </c>
-      <c r="E597" s="12"/>
-    </row>
-    <row r="598" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="598" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A598" s="16">
         <v>46314</v>
       </c>
@@ -11056,9 +10541,8 @@
       <c r="D598" s="17">
         <v>1572.23</v>
       </c>
-      <c r="E598" s="12"/>
-    </row>
-    <row r="599" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="599" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A599" s="16">
         <v>46314</v>
       </c>
@@ -11071,9 +10555,8 @@
       <c r="D599" s="17">
         <v>15153.08</v>
       </c>
-      <c r="E599" s="12"/>
-    </row>
-    <row r="600" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="600" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A600" s="16">
         <v>46314</v>
       </c>
@@ -11086,9 +10569,8 @@
       <c r="D600" s="17">
         <v>1267.3599999999999</v>
       </c>
-      <c r="E600" s="12"/>
-    </row>
-    <row r="601" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="601" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A601" s="16">
         <v>46314</v>
       </c>
@@ -11101,9 +10583,8 @@
       <c r="D601" s="17">
         <v>1276.5999999999999</v>
       </c>
-      <c r="E601" s="12"/>
-    </row>
-    <row r="602" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="602" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A602" s="16">
         <v>46314</v>
       </c>
@@ -11116,9 +10597,8 @@
       <c r="D602" s="17">
         <v>3834.6</v>
       </c>
-      <c r="E602" s="12"/>
-    </row>
-    <row r="603" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="603" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A603" s="16">
         <v>46314</v>
       </c>
@@ -11131,9 +10611,8 @@
       <c r="D603" s="17">
         <v>1721.8</v>
       </c>
-      <c r="E603" s="12"/>
-    </row>
-    <row r="604" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="604" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A604" s="16">
         <v>46314</v>
       </c>
@@ -11146,9 +10625,8 @@
       <c r="D604" s="18">
         <v>614.28</v>
       </c>
-      <c r="E604" s="12"/>
-    </row>
-    <row r="605" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="605" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A605" s="16">
         <v>46314</v>
       </c>
@@ -11161,9 +10639,8 @@
       <c r="D605" s="17">
         <v>1367.07</v>
       </c>
-      <c r="E605" s="12"/>
-    </row>
-    <row r="606" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="606" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A606" s="16">
         <v>46314</v>
       </c>
@@ -11176,9 +10653,8 @@
       <c r="D606" s="17">
         <v>1008.8</v>
       </c>
-      <c r="E606" s="12"/>
-    </row>
-    <row r="607" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="607" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A607" s="16">
         <v>46314</v>
       </c>
@@ -11191,9 +10667,8 @@
       <c r="D607" s="17">
         <v>4350.58</v>
       </c>
-      <c r="E607" s="12"/>
-    </row>
-    <row r="608" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="608" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A608" s="16">
         <v>46314</v>
       </c>
@@ -11206,9 +10681,8 @@
       <c r="D608" s="17">
         <v>6077.7</v>
       </c>
-      <c r="E608" s="12"/>
-    </row>
-    <row r="609" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="609" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A609" s="16">
         <v>46314</v>
       </c>
@@ -11221,9 +10695,8 @@
       <c r="D609" s="17">
         <v>11619</v>
       </c>
-      <c r="E609" s="12"/>
-    </row>
-    <row r="610" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="610" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A610" s="16">
         <v>46314</v>
       </c>
@@ -11236,9 +10709,8 @@
       <c r="D610" s="17">
         <v>2385.3000000000002</v>
       </c>
-      <c r="E610" s="12"/>
-    </row>
-    <row r="611" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="611" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A611" s="16">
         <v>46314</v>
       </c>
@@ -11251,9 +10723,8 @@
       <c r="D611" s="17">
         <v>31621.85</v>
       </c>
-      <c r="E611" s="12"/>
-    </row>
-    <row r="612" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="612" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A612" s="16">
         <v>46314</v>
       </c>
@@ -11266,9 +10737,8 @@
       <c r="D612" s="17">
         <v>68322.289999999994</v>
       </c>
-      <c r="E612" s="12"/>
-    </row>
-    <row r="613" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="613" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A613" s="16">
         <v>46314</v>
       </c>
@@ -11281,9 +10751,8 @@
       <c r="D613" s="18">
         <v>711.6</v>
       </c>
-      <c r="E613" s="12"/>
-    </row>
-    <row r="614" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="614" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A614" s="16">
         <v>46314</v>
       </c>
@@ -11296,9 +10765,8 @@
       <c r="D614" s="17">
         <v>35261.879999999997</v>
       </c>
-      <c r="E614" s="12"/>
-    </row>
-    <row r="615" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="615" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A615" s="16">
         <v>46314</v>
       </c>
@@ -11311,9 +10779,8 @@
       <c r="D615" s="17">
         <v>6738.02</v>
       </c>
-      <c r="E615" s="12"/>
-    </row>
-    <row r="616" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="616" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A616" s="16">
         <v>46314</v>
       </c>
@@ -11326,9 +10793,8 @@
       <c r="D616" s="18">
         <v>796.2</v>
       </c>
-      <c r="E616" s="12"/>
-    </row>
-    <row r="617" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="617" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A617" s="16">
         <v>46314</v>
       </c>
@@ -11341,9 +10807,8 @@
       <c r="D617" s="17">
         <v>25840</v>
       </c>
-      <c r="E617" s="12"/>
-    </row>
-    <row r="618" spans="1:5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="618" spans="1:4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A618" s="16">
         <v>46314</v>
       </c>
@@ -11356,7 +10821,804 @@
       <c r="D618" s="29">
         <v>1044.56</v>
       </c>
-      <c r="E618" s="12"/>
+    </row>
+    <row r="619" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A619" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B619" s="45">
+        <v>101</v>
+      </c>
+      <c r="C619" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="D619" s="47">
+        <v>13323.95</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A620" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B620" s="48">
+        <v>101</v>
+      </c>
+      <c r="C620" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="D620" s="43">
+        <v>-55768.84</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A621" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B621" s="3">
+        <v>101</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D621" s="41">
+        <v>55838.54</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A622" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B622" s="3">
+        <v>101</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D622" s="41">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A623" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B623" s="3">
+        <v>101</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D623" s="41">
+        <v>3760.5</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A624" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B624" s="48">
+        <v>101</v>
+      </c>
+      <c r="C624" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D624" s="43">
+        <v>-3608</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A625" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B625" s="3">
+        <v>101</v>
+      </c>
+      <c r="C625" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D625" s="41">
+        <v>7985.15</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A626" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B626" s="3">
+        <v>101</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D626" s="41">
+        <v>2076.4699999999998</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A627" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B627" s="3">
+        <v>101</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D627" s="41">
+        <v>5557.21</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A628" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B628" s="3">
+        <v>101</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D628" s="41">
+        <v>13847.99</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A629" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B629" s="3">
+        <v>101</v>
+      </c>
+      <c r="C629" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D629" s="44">
+        <v>214.82</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A630" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B630" s="3">
+        <v>101</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D630" s="41">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A631" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B631" s="3">
+        <v>101</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D631" s="44">
+        <v>544.82000000000005</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A632" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B632" s="3">
+        <v>101</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D632" s="41">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A633" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B633" s="3">
+        <v>101</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D633" s="41">
+        <v>25886.46</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A634" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B634" s="3">
+        <v>101</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D634" s="44">
+        <v>500.9</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A635" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B635" s="3">
+        <v>101</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D635" s="44">
+        <v>364.32</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A636" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B636" s="3">
+        <v>101</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D636" s="41">
+        <v>23277.06</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A637" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B637" s="3">
+        <v>101</v>
+      </c>
+      <c r="C637" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D637" s="44">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A638" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B638" s="3">
+        <v>101</v>
+      </c>
+      <c r="C638" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D638" s="41">
+        <v>21486.36</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A639" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B639" s="48">
+        <v>101</v>
+      </c>
+      <c r="C639" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D639" s="43">
+        <v>-3775.5</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A640" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B640" s="3">
+        <v>101</v>
+      </c>
+      <c r="C640" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D640" s="41">
+        <v>14512.3</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A641" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B641" s="3">
+        <v>101</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D641" s="41">
+        <v>10216.86</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A642" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B642" s="3">
+        <v>101</v>
+      </c>
+      <c r="C642" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D642" s="41">
+        <v>3528.2</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A643" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B643" s="3">
+        <v>101</v>
+      </c>
+      <c r="C643" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D643" s="41">
+        <v>86365.37</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A644" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B644" s="3">
+        <v>101</v>
+      </c>
+      <c r="C644" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D644" s="41">
+        <v>7531.75</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A645" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B645" s="3">
+        <v>101</v>
+      </c>
+      <c r="C645" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D645" s="44">
+        <v>642.16</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A646" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B646" s="3">
+        <v>101</v>
+      </c>
+      <c r="C646" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D646" s="44">
+        <v>616.14</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A647" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B647" s="3">
+        <v>101</v>
+      </c>
+      <c r="C647" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D647" s="41">
+        <v>4333.8900000000003</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A648" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B648" s="3">
+        <v>101</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D648" s="41">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A649" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B649" s="3">
+        <v>101</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D649" s="44">
+        <v>697.32</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A650" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B650" s="3">
+        <v>101</v>
+      </c>
+      <c r="C650" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D650" s="41">
+        <v>2693.24</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A651" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B651" s="3">
+        <v>101</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D651" s="41">
+        <v>28127.439999999999</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A652" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B652" s="3">
+        <v>101</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D652" s="41">
+        <v>5268.9</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A653" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B653" s="3">
+        <v>101</v>
+      </c>
+      <c r="C653" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D653" s="41">
+        <v>3558</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A654" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B654" s="3">
+        <v>101</v>
+      </c>
+      <c r="C654" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D654" s="41">
+        <v>2771.7</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A655" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B655" s="3">
+        <v>101</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D655" s="41">
+        <v>2805.96</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A656" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B656" s="3">
+        <v>101</v>
+      </c>
+      <c r="C656" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D656" s="41">
+        <v>1170.45</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A657" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B657" s="3">
+        <v>101</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D657" s="41">
+        <v>1281.8399999999999</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A658" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B658" s="3">
+        <v>101</v>
+      </c>
+      <c r="C658" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D658" s="41">
+        <v>2782.44</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A659" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B659" s="3">
+        <v>101</v>
+      </c>
+      <c r="C659" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D659" s="41">
+        <v>1303.49</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A660" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B660" s="3">
+        <v>101</v>
+      </c>
+      <c r="C660" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D660" s="41">
+        <v>7547.3</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A661" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B661" s="3">
+        <v>101</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D661" s="41">
+        <v>14854.77</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A662" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B662" s="3">
+        <v>101</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D662" s="41">
+        <v>6467.2</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A663" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B663" s="3">
+        <v>101</v>
+      </c>
+      <c r="C663" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D663" s="44">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A664" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B664" s="3">
+        <v>101</v>
+      </c>
+      <c r="C664" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D664" s="41">
+        <v>1899.2</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A665" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B665" s="3">
+        <v>101</v>
+      </c>
+      <c r="C665" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D665" s="44">
+        <v>673.31</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A666" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B666" s="3">
+        <v>101</v>
+      </c>
+      <c r="C666" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D666" s="44">
+        <v>43.04</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A667" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B667" s="3">
+        <v>101</v>
+      </c>
+      <c r="C667" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D667" s="41">
+        <v>1026.5899999999999</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A668" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B668" s="3">
+        <v>101</v>
+      </c>
+      <c r="C668" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D668" s="44">
+        <v>511.5</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A669" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B669" s="3">
+        <v>101</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D669" s="41">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A670" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B670" s="3">
+        <v>101</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D670" s="41">
+        <v>1912.5</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A671" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B671" s="3">
+        <v>101</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D671" s="41">
+        <v>1021.5</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A672" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B672" s="3">
+        <v>101</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D672" s="41">
+        <v>5005.8</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A673" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B673" s="3">
+        <v>101</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D673" s="41">
+        <v>68825.39</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A674" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B674" s="3">
+        <v>101</v>
+      </c>
+      <c r="C674" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D674" s="44">
+        <v>205.45</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A675" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B675" s="49">
+        <v>101</v>
+      </c>
+      <c r="C675" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="D675" s="51">
+        <v>14159.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE16016-5FBA-486C-A349-0925041B09E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AB6FD6-E1B2-41FE-BF51-4FB2D05427D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -1479,18 +1479,6 @@
     <xf numFmtId="4" fontId="20" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="19" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -1523,6 +1511,18 @@
     </xf>
     <xf numFmtId="4" fontId="19" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1900,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19101EBF-008C-4E37-90C0-CF2D419D5300}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1909,16 +1909,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="40"/>
+      <c r="C1" s="51"/>
     </row>
     <row r="2" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38"/>
+      <c r="A2" s="49"/>
       <c r="B2" s="1" t="s">
         <v>78</v>
       </c>
@@ -2103,14 +2103,25 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B19">
+        <v>548968.22</v>
+      </c>
+      <c r="C19">
+        <v>-24640.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="5">
-        <v>6314600.4000000004</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-239616.11</v>
+      <c r="B20" s="5">
+        <v>6838785.3700000001</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-264257.05</v>
       </c>
     </row>
   </sheetData>
@@ -2151,8 +2162,11 @@
     <hyperlink ref="B3" r:id="rId30" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{57C038F4-9037-4D9B-8567-B2DBF298F437}"/>
     <hyperlink ref="B18" r:id="rId31" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{03D2D6FF-12B4-4538-8F9C-83559C00711E}"/>
     <hyperlink ref="C18" r:id="rId32" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F40DF996-3027-4D6F-B560-A994ECD0B5DB}"/>
+    <hyperlink ref="B19" r:id="rId33" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6866647E-AEF9-4707-8437-EEFD20D22BE1}"/>
+    <hyperlink ref="C19" r:id="rId34" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{86BC9795-12E6-4058-945B-DB513080C406}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId35"/>
 </worksheet>
 </file>
 
@@ -10826,13 +10840,13 @@
       <c r="A619" s="13">
         <v>46315</v>
       </c>
-      <c r="B619" s="45">
-        <v>101</v>
-      </c>
-      <c r="C619" s="46" t="s">
+      <c r="B619" s="41">
+        <v>101</v>
+      </c>
+      <c r="C619" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="D619" s="47">
+      <c r="D619" s="43">
         <v>13323.95</v>
       </c>
     </row>
@@ -10840,13 +10854,13 @@
       <c r="A620" s="13">
         <v>46315</v>
       </c>
-      <c r="B620" s="48">
-        <v>101</v>
-      </c>
-      <c r="C620" s="42" t="s">
+      <c r="B620" s="44">
+        <v>101</v>
+      </c>
+      <c r="C620" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="D620" s="43">
+      <c r="D620" s="39">
         <v>-55768.84</v>
       </c>
     </row>
@@ -10860,7 +10874,7 @@
       <c r="C621" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D621" s="41">
+      <c r="D621" s="37">
         <v>55838.54</v>
       </c>
     </row>
@@ -10874,7 +10888,7 @@
       <c r="C622" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D622" s="41">
+      <c r="D622" s="37">
         <v>4080</v>
       </c>
     </row>
@@ -10888,7 +10902,7 @@
       <c r="C623" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D623" s="41">
+      <c r="D623" s="37">
         <v>3760.5</v>
       </c>
     </row>
@@ -10896,13 +10910,13 @@
       <c r="A624" s="13">
         <v>46315</v>
       </c>
-      <c r="B624" s="48">
-        <v>101</v>
-      </c>
-      <c r="C624" s="42" t="s">
+      <c r="B624" s="44">
+        <v>101</v>
+      </c>
+      <c r="C624" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="D624" s="43">
+      <c r="D624" s="39">
         <v>-3608</v>
       </c>
     </row>
@@ -10916,7 +10930,7 @@
       <c r="C625" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D625" s="41">
+      <c r="D625" s="37">
         <v>7985.15</v>
       </c>
     </row>
@@ -10930,7 +10944,7 @@
       <c r="C626" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D626" s="41">
+      <c r="D626" s="37">
         <v>2076.4699999999998</v>
       </c>
     </row>
@@ -10944,7 +10958,7 @@
       <c r="C627" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D627" s="41">
+      <c r="D627" s="37">
         <v>5557.21</v>
       </c>
     </row>
@@ -10958,7 +10972,7 @@
       <c r="C628" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D628" s="41">
+      <c r="D628" s="37">
         <v>13847.99</v>
       </c>
     </row>
@@ -10972,7 +10986,7 @@
       <c r="C629" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D629" s="44">
+      <c r="D629" s="40">
         <v>214.82</v>
       </c>
     </row>
@@ -10986,7 +11000,7 @@
       <c r="C630" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D630" s="41">
+      <c r="D630" s="37">
         <v>1716</v>
       </c>
     </row>
@@ -11000,7 +11014,7 @@
       <c r="C631" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D631" s="44">
+      <c r="D631" s="40">
         <v>544.82000000000005</v>
       </c>
     </row>
@@ -11014,7 +11028,7 @@
       <c r="C632" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D632" s="41">
+      <c r="D632" s="37">
         <v>1990</v>
       </c>
     </row>
@@ -11028,7 +11042,7 @@
       <c r="C633" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D633" s="41">
+      <c r="D633" s="37">
         <v>25886.46</v>
       </c>
     </row>
@@ -11042,7 +11056,7 @@
       <c r="C634" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D634" s="44">
+      <c r="D634" s="40">
         <v>500.9</v>
       </c>
     </row>
@@ -11056,7 +11070,7 @@
       <c r="C635" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D635" s="44">
+      <c r="D635" s="40">
         <v>364.32</v>
       </c>
     </row>
@@ -11070,7 +11084,7 @@
       <c r="C636" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D636" s="41">
+      <c r="D636" s="37">
         <v>23277.06</v>
       </c>
     </row>
@@ -11084,7 +11098,7 @@
       <c r="C637" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D637" s="44">
+      <c r="D637" s="40">
         <v>513</v>
       </c>
     </row>
@@ -11098,7 +11112,7 @@
       <c r="C638" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D638" s="41">
+      <c r="D638" s="37">
         <v>21486.36</v>
       </c>
     </row>
@@ -11106,13 +11120,13 @@
       <c r="A639" s="13">
         <v>46315</v>
       </c>
-      <c r="B639" s="48">
-        <v>101</v>
-      </c>
-      <c r="C639" s="42" t="s">
+      <c r="B639" s="44">
+        <v>101</v>
+      </c>
+      <c r="C639" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="D639" s="43">
+      <c r="D639" s="39">
         <v>-3775.5</v>
       </c>
     </row>
@@ -11126,7 +11140,7 @@
       <c r="C640" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D640" s="41">
+      <c r="D640" s="37">
         <v>14512.3</v>
       </c>
     </row>
@@ -11140,7 +11154,7 @@
       <c r="C641" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D641" s="41">
+      <c r="D641" s="37">
         <v>10216.86</v>
       </c>
     </row>
@@ -11154,7 +11168,7 @@
       <c r="C642" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D642" s="41">
+      <c r="D642" s="37">
         <v>3528.2</v>
       </c>
     </row>
@@ -11168,7 +11182,7 @@
       <c r="C643" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D643" s="41">
+      <c r="D643" s="37">
         <v>86365.37</v>
       </c>
     </row>
@@ -11182,7 +11196,7 @@
       <c r="C644" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D644" s="41">
+      <c r="D644" s="37">
         <v>7531.75</v>
       </c>
     </row>
@@ -11196,7 +11210,7 @@
       <c r="C645" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D645" s="44">
+      <c r="D645" s="40">
         <v>642.16</v>
       </c>
     </row>
@@ -11210,7 +11224,7 @@
       <c r="C646" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D646" s="44">
+      <c r="D646" s="40">
         <v>616.14</v>
       </c>
     </row>
@@ -11224,7 +11238,7 @@
       <c r="C647" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D647" s="41">
+      <c r="D647" s="37">
         <v>4333.8900000000003</v>
       </c>
     </row>
@@ -11238,7 +11252,7 @@
       <c r="C648" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D648" s="41">
+      <c r="D648" s="37">
         <v>2112</v>
       </c>
     </row>
@@ -11252,7 +11266,7 @@
       <c r="C649" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D649" s="44">
+      <c r="D649" s="40">
         <v>697.32</v>
       </c>
     </row>
@@ -11266,7 +11280,7 @@
       <c r="C650" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D650" s="41">
+      <c r="D650" s="37">
         <v>2693.24</v>
       </c>
     </row>
@@ -11280,7 +11294,7 @@
       <c r="C651" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D651" s="41">
+      <c r="D651" s="37">
         <v>28127.439999999999</v>
       </c>
     </row>
@@ -11294,7 +11308,7 @@
       <c r="C652" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D652" s="41">
+      <c r="D652" s="37">
         <v>5268.9</v>
       </c>
     </row>
@@ -11308,7 +11322,7 @@
       <c r="C653" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D653" s="41">
+      <c r="D653" s="37">
         <v>3558</v>
       </c>
     </row>
@@ -11322,7 +11336,7 @@
       <c r="C654" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D654" s="41">
+      <c r="D654" s="37">
         <v>2771.7</v>
       </c>
     </row>
@@ -11336,7 +11350,7 @@
       <c r="C655" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D655" s="41">
+      <c r="D655" s="37">
         <v>2805.96</v>
       </c>
     </row>
@@ -11350,7 +11364,7 @@
       <c r="C656" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D656" s="41">
+      <c r="D656" s="37">
         <v>1170.45</v>
       </c>
     </row>
@@ -11364,7 +11378,7 @@
       <c r="C657" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D657" s="41">
+      <c r="D657" s="37">
         <v>1281.8399999999999</v>
       </c>
     </row>
@@ -11378,7 +11392,7 @@
       <c r="C658" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D658" s="41">
+      <c r="D658" s="37">
         <v>2782.44</v>
       </c>
     </row>
@@ -11392,7 +11406,7 @@
       <c r="C659" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D659" s="41">
+      <c r="D659" s="37">
         <v>1303.49</v>
       </c>
     </row>
@@ -11406,7 +11420,7 @@
       <c r="C660" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D660" s="41">
+      <c r="D660" s="37">
         <v>7547.3</v>
       </c>
     </row>
@@ -11420,7 +11434,7 @@
       <c r="C661" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D661" s="41">
+      <c r="D661" s="37">
         <v>14854.77</v>
       </c>
     </row>
@@ -11434,7 +11448,7 @@
       <c r="C662" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D662" s="41">
+      <c r="D662" s="37">
         <v>6467.2</v>
       </c>
     </row>
@@ -11448,7 +11462,7 @@
       <c r="C663" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D663" s="44">
+      <c r="D663" s="40">
         <v>741</v>
       </c>
     </row>
@@ -11462,7 +11476,7 @@
       <c r="C664" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D664" s="41">
+      <c r="D664" s="37">
         <v>1899.2</v>
       </c>
     </row>
@@ -11476,7 +11490,7 @@
       <c r="C665" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D665" s="44">
+      <c r="D665" s="40">
         <v>673.31</v>
       </c>
     </row>
@@ -11490,7 +11504,7 @@
       <c r="C666" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D666" s="44">
+      <c r="D666" s="40">
         <v>43.04</v>
       </c>
     </row>
@@ -11504,7 +11518,7 @@
       <c r="C667" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D667" s="41">
+      <c r="D667" s="37">
         <v>1026.5899999999999</v>
       </c>
     </row>
@@ -11518,7 +11532,7 @@
       <c r="C668" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D668" s="44">
+      <c r="D668" s="40">
         <v>511.5</v>
       </c>
     </row>
@@ -11532,7 +11546,7 @@
       <c r="C669" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D669" s="41">
+      <c r="D669" s="37">
         <v>1920</v>
       </c>
     </row>
@@ -11546,7 +11560,7 @@
       <c r="C670" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D670" s="41">
+      <c r="D670" s="37">
         <v>1912.5</v>
       </c>
     </row>
@@ -11560,7 +11574,7 @@
       <c r="C671" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D671" s="41">
+      <c r="D671" s="37">
         <v>1021.5</v>
       </c>
     </row>
@@ -11574,7 +11588,7 @@
       <c r="C672" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D672" s="41">
+      <c r="D672" s="37">
         <v>5005.8</v>
       </c>
     </row>
@@ -11588,7 +11602,7 @@
       <c r="C673" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D673" s="41">
+      <c r="D673" s="37">
         <v>68825.39</v>
       </c>
     </row>
@@ -11602,7 +11616,7 @@
       <c r="C674" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D674" s="44">
+      <c r="D674" s="40">
         <v>205.45</v>
       </c>
     </row>
@@ -11610,13 +11624,13 @@
       <c r="A675" s="13">
         <v>46315</v>
       </c>
-      <c r="B675" s="49">
-        <v>101</v>
-      </c>
-      <c r="C675" s="50" t="s">
+      <c r="B675" s="45">
+        <v>101</v>
+      </c>
+      <c r="C675" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="D675" s="51">
+      <c r="D675" s="47">
         <v>14159.4</v>
       </c>
     </row>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AB6FD6-E1B2-41FE-BF51-4FB2D05427D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3914F6D3-88F0-4CEC-B685-CD3E109245BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="223">
   <si>
     <t>Filial</t>
   </si>
@@ -681,6 +681,15 @@
   </si>
   <si>
     <t>ARS ENSINO SUPERIOR</t>
+  </si>
+  <si>
+    <t>HOSP BARRA DOR I</t>
+  </si>
+  <si>
+    <t>H NOSSA SRA CONCEICA</t>
+  </si>
+  <si>
+    <t>COI CLINICA 39.086.1</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1380,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1523,6 +1532,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2172,16 +2184,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:D675"/>
+  <dimension ref="A1:D721"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="12"/>
-    <col min="6" max="6" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="12"/>
+    <col min="5" max="5" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11634,6 +11645,650 @@
         <v>14159.4</v>
       </c>
     </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A676" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B676" s="12">
+        <v>101</v>
+      </c>
+      <c r="C676" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D676" s="52">
+        <v>52362.9</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A677" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B677" s="12">
+        <v>101</v>
+      </c>
+      <c r="C677" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D677" s="12">
+        <v>733.5</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A678" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B678" s="12">
+        <v>101</v>
+      </c>
+      <c r="C678" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D678" s="12">
+        <v>539.01</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A679" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B679" s="12">
+        <v>101</v>
+      </c>
+      <c r="C679" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D679" s="12">
+        <v>650.49</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A680" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B680" s="12">
+        <v>101</v>
+      </c>
+      <c r="C680" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D680" s="12">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A681" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B681" s="12">
+        <v>101</v>
+      </c>
+      <c r="C681" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D681" s="12">
+        <v>979.59</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A682" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B682" s="12">
+        <v>101</v>
+      </c>
+      <c r="C682" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D682" s="52">
+        <v>7699.01</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A683" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B683" s="12">
+        <v>101</v>
+      </c>
+      <c r="C683" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D683" s="52">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A684" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B684" s="12">
+        <v>101</v>
+      </c>
+      <c r="C684" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D684" s="52">
+        <v>3760.5</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A685" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B685" s="12">
+        <v>101</v>
+      </c>
+      <c r="C685" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D685" s="52">
+        <v>65871.62</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A686" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B686" s="12">
+        <v>101</v>
+      </c>
+      <c r="C686" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D686" s="12">
+        <v>239.53</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A687" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B687" s="12">
+        <v>101</v>
+      </c>
+      <c r="C687" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D687" s="52">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A688" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B688" s="12">
+        <v>101</v>
+      </c>
+      <c r="C688" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D688" s="52">
+        <v>2836.51</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A689" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B689" s="12">
+        <v>101</v>
+      </c>
+      <c r="C689" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D689" s="52">
+        <v>29025.5</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A690" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B690" s="12">
+        <v>101</v>
+      </c>
+      <c r="C690" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D690" s="52">
+        <v>4968</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A691" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B691" s="12">
+        <v>101</v>
+      </c>
+      <c r="C691" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D691" s="52">
+        <v>-1625</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A692" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B692" s="12">
+        <v>101</v>
+      </c>
+      <c r="C692" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D692" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A693" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B693" s="12">
+        <v>101</v>
+      </c>
+      <c r="C693" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D693" s="52">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A694" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B694" s="12">
+        <v>101</v>
+      </c>
+      <c r="C694" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D694" s="12">
+        <v>-500.9</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A695" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B695" s="12">
+        <v>101</v>
+      </c>
+      <c r="C695" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D695" s="52">
+        <v>5772.09</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A696" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B696" s="12">
+        <v>101</v>
+      </c>
+      <c r="C696" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D696" s="52">
+        <v>1091.42</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A697" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B697" s="12">
+        <v>101</v>
+      </c>
+      <c r="C697" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D697" s="52">
+        <v>13836.2</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A698" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B698" s="12">
+        <v>101</v>
+      </c>
+      <c r="C698" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D698" s="52">
+        <v>3891.09</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A699" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B699" s="12">
+        <v>101</v>
+      </c>
+      <c r="C699" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D699" s="52">
+        <v>-7027.68</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A700" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B700" s="12">
+        <v>101</v>
+      </c>
+      <c r="C700" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D700" s="52">
+        <v>26872.07</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A701" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B701" s="12">
+        <v>101</v>
+      </c>
+      <c r="C701" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D701" s="52">
+        <v>11888.17</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A702" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B702" s="12">
+        <v>101</v>
+      </c>
+      <c r="C702" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D702" s="52">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A703" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B703" s="12">
+        <v>101</v>
+      </c>
+      <c r="C703" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D703" s="52">
+        <v>-10339.959999999999</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A704" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B704" s="12">
+        <v>101</v>
+      </c>
+      <c r="C704" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D704" s="52">
+        <v>1533.96</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A705" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B705" s="12">
+        <v>101</v>
+      </c>
+      <c r="C705" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D705" s="52">
+        <v>3617.46</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A706" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B706" s="12">
+        <v>101</v>
+      </c>
+      <c r="C706" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D706" s="52">
+        <v>-5147.3999999999996</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A707" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B707" s="12">
+        <v>101</v>
+      </c>
+      <c r="C707" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D707" s="52">
+        <v>81796.06</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A708" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B708" s="12">
+        <v>101</v>
+      </c>
+      <c r="C708" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D708" s="52">
+        <v>1639.96</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A709" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B709" s="12">
+        <v>101</v>
+      </c>
+      <c r="C709" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D709" s="12">
+        <v>697.32</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A710" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B710" s="12">
+        <v>101</v>
+      </c>
+      <c r="C710" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D710" s="52">
+        <v>28127.439999999999</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A711" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B711" s="12">
+        <v>101</v>
+      </c>
+      <c r="C711" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D711" s="52">
+        <v>11770.06</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A712" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B712" s="12">
+        <v>101</v>
+      </c>
+      <c r="C712" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D712" s="52">
+        <v>4590.1400000000003</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A713" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B713" s="12">
+        <v>101</v>
+      </c>
+      <c r="C713" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D713" s="52">
+        <v>8070.92</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A714" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B714" s="12">
+        <v>101</v>
+      </c>
+      <c r="C714" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D714" s="52">
+        <v>17442.8</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A715" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B715" s="12">
+        <v>101</v>
+      </c>
+      <c r="C715" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D715" s="12">
+        <v>598.83000000000004</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A716" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B716" s="12">
+        <v>101</v>
+      </c>
+      <c r="C716" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D716" s="52">
+        <v>80536.3</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A717" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B717" s="12">
+        <v>101</v>
+      </c>
+      <c r="C717" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D717" s="52">
+        <v>54056.1</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A718" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B718" s="12">
+        <v>101</v>
+      </c>
+      <c r="C718" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D718" s="52">
+        <v>5345.41</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A719" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B719" s="12">
+        <v>101</v>
+      </c>
+      <c r="C719" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D719" s="52">
+        <v>1728.45</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A720" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B720" s="12">
+        <v>101</v>
+      </c>
+      <c r="C720" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D720" s="52">
+        <v>1588.1</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A721" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B721" s="12">
+        <v>101</v>
+      </c>
+      <c r="C721" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D721" s="12">
+        <v>417.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC3B8B4-8BBC-4146-BB53-D833FA4AFBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1DBFB3-004B-4660-AC17-7BDBDD53D6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
@@ -1071,7 +1071,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1231,6 +1231,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1276,7 +1291,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1299,6 +1314,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1675,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19101EBF-008C-4E37-90C0-CF2D419D5300}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1902,21 +1920,32 @@
         <v>46318</v>
       </c>
       <c r="B21">
-        <v>369121.69</v>
+        <v>380210.58</v>
       </c>
       <c r="C21">
-        <v>-728.82</v>
+        <v>-19833.009999999998</v>
       </c>
     </row>
     <row r="22" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="9">
+        <v>46321</v>
+      </c>
+      <c r="B22">
+        <v>187326.15</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="2">
-        <v>7855067.1399999997</v>
-      </c>
-      <c r="C22" s="2">
-        <v>-291673.07</v>
+      <c r="B23" s="2">
+        <v>8053482.1799999997</v>
+      </c>
+      <c r="C23" s="2">
+        <v>-310777.26</v>
       </c>
     </row>
   </sheetData>
@@ -1955,11 +1984,13 @@
     <hyperlink ref="C18" r:id="rId32" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F40DF996-3027-4D6F-B560-A994ECD0B5DB}"/>
     <hyperlink ref="B19" r:id="rId33" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6866647E-AEF9-4707-8437-EEFD20D22BE1}"/>
     <hyperlink ref="C19" r:id="rId34" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{86BC9795-12E6-4058-945B-DB513080C406}"/>
-    <hyperlink ref="B21" r:id="rId35" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{8AC67425-6A9D-4CE6-BE58-59016843D5F9}"/>
-    <hyperlink ref="C21" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{D7178C55-B681-4C63-9551-790DB0963D8A}"/>
+    <hyperlink ref="B21" r:id="rId35" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{ABF3F658-C78C-46C1-A6A0-EACB1F1312FC}"/>
+    <hyperlink ref="C21" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A5E30353-68AD-4555-A4A4-F43F7F15A167}"/>
+    <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6A546647-FE3F-4BCF-9E75-A6F5618DE61E}"/>
+    <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{67F55B4C-CA3E-4682-89A5-7FB10930EF0B}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId37"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId39"/>
 </worksheet>
 </file>
 

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1DBFB3-004B-4660-AC17-7BDBDD53D6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7066F92A-3C54-4E55-B093-4C70A5EBDB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="236">
   <si>
     <t>Filial</t>
   </si>
@@ -723,6 +723,12 @@
   </si>
   <si>
     <t>ALTHAIA</t>
+  </si>
+  <si>
+    <t>SECONCI CENTRO</t>
+  </si>
+  <si>
+    <t>DASA UNIDADE CENTRAL</t>
   </si>
 </sst>
 </file>
@@ -1996,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -12997,6 +13003,734 @@
         <v>2043.13</v>
       </c>
     </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A786" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B786" s="5">
+        <v>101</v>
+      </c>
+      <c r="C786" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D786" s="8">
+        <v>6482.29</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A787" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B787" s="5">
+        <v>101</v>
+      </c>
+      <c r="C787" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D787" s="8">
+        <v>3734.99</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A788" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B788" s="5">
+        <v>101</v>
+      </c>
+      <c r="C788" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D788" s="8">
+        <v>3388.45</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A789" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B789" s="5">
+        <v>101</v>
+      </c>
+      <c r="C789" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D789" s="8">
+        <v>1830.25</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A790" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B790" s="5">
+        <v>101</v>
+      </c>
+      <c r="C790" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D790" s="8">
+        <v>4233.4399999999996</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A791" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B791" s="5">
+        <v>101</v>
+      </c>
+      <c r="C791" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D791" s="8">
+        <v>2359.8200000000002</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A792" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B792" s="5">
+        <v>101</v>
+      </c>
+      <c r="C792" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D792" s="8">
+        <v>62.38</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A793" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B793" s="5">
+        <v>101</v>
+      </c>
+      <c r="C793" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D793" s="8">
+        <v>18390.54</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A794" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B794" s="5">
+        <v>101</v>
+      </c>
+      <c r="C794" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D794" s="8">
+        <v>-5109.24</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A795" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B795" s="5">
+        <v>101</v>
+      </c>
+      <c r="C795" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D795" s="8">
+        <v>1169.6300000000001</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A796" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B796" s="5">
+        <v>101</v>
+      </c>
+      <c r="C796" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D796" s="8">
+        <v>4069.44</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A797" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B797" s="5">
+        <v>101</v>
+      </c>
+      <c r="C797" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D797" s="8">
+        <v>6860.52</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A798" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B798" s="5">
+        <v>101</v>
+      </c>
+      <c r="C798" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D798" s="8">
+        <v>17075.599999999999</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A799" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B799" s="5">
+        <v>101</v>
+      </c>
+      <c r="C799" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D799" s="8">
+        <v>629.70000000000005</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A800" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B800" s="5">
+        <v>101</v>
+      </c>
+      <c r="C800" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D800" s="8">
+        <v>23280</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A801" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B801" s="5">
+        <v>101</v>
+      </c>
+      <c r="C801" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D801" s="8">
+        <v>-14507.95</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A802" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B802" s="5">
+        <v>101</v>
+      </c>
+      <c r="C802" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D802" s="8">
+        <v>30772.58</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A803" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B803" s="5">
+        <v>101</v>
+      </c>
+      <c r="C803" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D803" s="8">
+        <v>4565.7700000000004</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A804" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B804" s="5">
+        <v>101</v>
+      </c>
+      <c r="C804" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D804" s="8">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A805" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B805" s="5">
+        <v>101</v>
+      </c>
+      <c r="C805" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D805" s="8">
+        <v>3718.6</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A806" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B806" s="5">
+        <v>101</v>
+      </c>
+      <c r="C806" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D806" s="8">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A807" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B807" s="5">
+        <v>101</v>
+      </c>
+      <c r="C807" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D807" s="8">
+        <v>23535.3</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A808" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B808" s="5">
+        <v>101</v>
+      </c>
+      <c r="C808" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D808" s="8">
+        <v>1324.51</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A809" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B809" s="5">
+        <v>101</v>
+      </c>
+      <c r="C809" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D809" s="8">
+        <v>2430.8000000000002</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A810" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B810" s="5">
+        <v>101</v>
+      </c>
+      <c r="C810" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D810" s="8">
+        <v>9221</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A811" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B811" s="5">
+        <v>101</v>
+      </c>
+      <c r="C811" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D811" s="8">
+        <v>1003.3</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A812" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B812" s="5">
+        <v>101</v>
+      </c>
+      <c r="C812" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D812" s="8">
+        <v>1186.92</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A813" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B813" s="5">
+        <v>101</v>
+      </c>
+      <c r="C813" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D813" s="8">
+        <v>4779.62</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A814" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B814" s="5">
+        <v>101</v>
+      </c>
+      <c r="C814" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D814" s="8">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A815" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B815" s="5">
+        <v>101</v>
+      </c>
+      <c r="C815" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D815" s="8">
+        <v>1836.69</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A816" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B816" s="5">
+        <v>101</v>
+      </c>
+      <c r="C816" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D816" s="8">
+        <v>1251.8499999999999</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A817" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B817" s="5">
+        <v>101</v>
+      </c>
+      <c r="C817" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D817" s="8">
+        <v>562.20000000000005</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A818" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B818" s="5">
+        <v>101</v>
+      </c>
+      <c r="C818" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D818" s="8">
+        <v>2790.95</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A819" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B819" s="5">
+        <v>101</v>
+      </c>
+      <c r="C819" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D819" s="8">
+        <v>18450.2</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A820" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B820" s="5">
+        <v>101</v>
+      </c>
+      <c r="C820" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D820" s="8">
+        <v>1783.2</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A821" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B821" s="5">
+        <v>101</v>
+      </c>
+      <c r="C821" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D821" s="8">
+        <v>1808.11</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A822" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B822" s="5">
+        <v>101</v>
+      </c>
+      <c r="C822" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D822" s="8">
+        <v>469.15</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A823" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B823" s="5">
+        <v>101</v>
+      </c>
+      <c r="C823" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D823" s="8">
+        <v>2848.8</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A824" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B824" s="5">
+        <v>101</v>
+      </c>
+      <c r="C824" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D824" s="8">
+        <v>760.2</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A825" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B825" s="5">
+        <v>101</v>
+      </c>
+      <c r="C825" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D825" s="8">
+        <v>2538.0500000000002</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A826" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B826" s="5">
+        <v>101</v>
+      </c>
+      <c r="C826" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D826" s="8">
+        <v>1276.1199999999999</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A827" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B827" s="5">
+        <v>101</v>
+      </c>
+      <c r="C827" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D827" s="8">
+        <v>1478.7</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A828" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B828" s="5">
+        <v>101</v>
+      </c>
+      <c r="C828" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D828" s="8">
+        <v>1573.78</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A829" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B829" s="5">
+        <v>101</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D829" s="8">
+        <v>1705.41</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A830" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B830" s="5">
+        <v>101</v>
+      </c>
+      <c r="C830" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D830" s="8">
+        <v>14430</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A831" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B831" s="5">
+        <v>101</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D831" s="8">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A832" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B832" s="5">
+        <v>101</v>
+      </c>
+      <c r="C832" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D832" s="8">
+        <v>122850</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A833" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B833" s="5">
+        <v>101</v>
+      </c>
+      <c r="C833" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D833" s="8">
+        <v>-215.82</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A834" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B834" s="5">
+        <v>101</v>
+      </c>
+      <c r="C834" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D834" s="8">
+        <v>1666.25</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A835" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B835" s="5">
+        <v>101</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D835" s="8">
+        <v>4412.2</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A836" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B836" s="5">
+        <v>101</v>
+      </c>
+      <c r="C836" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D836" s="8">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A837" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B837" s="5">
+        <v>101</v>
+      </c>
+      <c r="C837" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D837" s="8">
+        <v>14134.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7066F92A-3C54-4E55-B093-4C70A5EBDB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE0B3E1-62E1-44BA-B87A-0B3E5F518935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -1077,7 +1077,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1237,21 +1237,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF808080"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE2E6"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF808080"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1297,7 +1282,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1320,9 +1305,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1703,7 +1685,7 @@
   <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1933,11 +1915,11 @@
       </c>
     </row>
     <row r="22" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
+      <c r="A22" s="3">
         <v>46321</v>
       </c>
       <c r="B22">
-        <v>187326.15</v>
+        <v>690331.86</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1948,7 +1930,7 @@
         <v>75</v>
       </c>
       <c r="B23" s="2">
-        <v>8053482.1799999997</v>
+        <v>8556487.8900000006</v>
       </c>
       <c r="C23" s="2">
         <v>-310777.26</v>
@@ -1992,8 +1974,8 @@
     <hyperlink ref="C19" r:id="rId34" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{86BC9795-12E6-4058-945B-DB513080C406}"/>
     <hyperlink ref="B21" r:id="rId35" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{ABF3F658-C78C-46C1-A6A0-EACB1F1312FC}"/>
     <hyperlink ref="C21" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A5E30353-68AD-4555-A4A4-F43F7F15A167}"/>
-    <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6A546647-FE3F-4BCF-9E75-A6F5618DE61E}"/>
-    <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{67F55B4C-CA3E-4682-89A5-7FB10930EF0B}"/>
+    <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C4F5F9A5-AC8F-4808-8572-70D87C9D82F9}"/>
+    <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FD324AB2-9D0D-4917-8ADD-F06162E9FBEA}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId39"/>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE0B3E1-62E1-44BA-B87A-0B3E5F518935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F094D1D-294F-414B-BFEC-A1DEC515B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="242">
   <si>
     <t>Filial</t>
   </si>
@@ -729,6 +729,24 @@
   </si>
   <si>
     <t>DASA UNIDADE CENTRAL</t>
+  </si>
+  <si>
+    <t>WCA DO BRASIL</t>
+  </si>
+  <si>
+    <t>TRE TRIBUNAL</t>
+  </si>
+  <si>
+    <t>LAB SANTA LUZIA</t>
+  </si>
+  <si>
+    <t>HOSP HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>DASA LAB HORMON</t>
+  </si>
+  <si>
+    <t>DASA 61.486.650/0686</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19101EBF-008C-4E37-90C0-CF2D419D5300}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1919,21 +1937,32 @@
         <v>46321</v>
       </c>
       <c r="B22">
-        <v>690331.86</v>
+        <v>833062.77</v>
       </c>
       <c r="C22">
+        <v>-8601.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>46322</v>
+      </c>
+      <c r="B23">
+        <v>146303.18</v>
+      </c>
+      <c r="C23">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="2">
-        <v>8556487.8900000006</v>
-      </c>
-      <c r="C23" s="2">
-        <v>-310777.26</v>
+      <c r="B24" s="2">
+        <v>8845521.9800000004</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-319379.15000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1974,17 +2003,19 @@
     <hyperlink ref="C19" r:id="rId34" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{86BC9795-12E6-4058-945B-DB513080C406}"/>
     <hyperlink ref="B21" r:id="rId35" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{ABF3F658-C78C-46C1-A6A0-EACB1F1312FC}"/>
     <hyperlink ref="C21" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A5E30353-68AD-4555-A4A4-F43F7F15A167}"/>
-    <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C4F5F9A5-AC8F-4808-8572-70D87C9D82F9}"/>
-    <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FD324AB2-9D0D-4917-8ADD-F06162E9FBEA}"/>
+    <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F5D8DE54-95D1-46C8-88FE-0455E31F55EA}"/>
+    <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6508494-A2ED-45CE-A06F-52BAF7398889}"/>
+    <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E234A0FC-3F1D-4E49-89FE-CFF8150000F6}"/>
+    <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{3AB773AA-3A9E-4C38-8792-28BC2A833A14}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId39"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId41"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -13713,6 +13744,748 @@
         <v>14134.72</v>
       </c>
     </row>
+    <row r="838" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A838" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B838" s="5">
+        <v>101</v>
+      </c>
+      <c r="C838" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D838" s="8">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A839" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B839" s="5">
+        <v>101</v>
+      </c>
+      <c r="C839" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D839" s="8">
+        <v>128598.54</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A840" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B840" s="5">
+        <v>101</v>
+      </c>
+      <c r="C840" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D840" s="8">
+        <v>8212.14</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A841" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B841" s="5">
+        <v>101</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D841" s="8">
+        <v>2480.7600000000002</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A842" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B842" s="5">
+        <v>101</v>
+      </c>
+      <c r="C842" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D842" s="8">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A843" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B843" s="5">
+        <v>101</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D843" s="8">
+        <v>4145.6400000000003</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A844" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B844" s="5">
+        <v>101</v>
+      </c>
+      <c r="C844" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D844" s="8">
+        <v>2647.33</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A845" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B845" s="5">
+        <v>101</v>
+      </c>
+      <c r="C845" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D845" s="8">
+        <v>9171.9</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A846" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B846" s="5">
+        <v>101</v>
+      </c>
+      <c r="C846" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D846" s="8">
+        <v>2574.64</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A847" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B847" s="5">
+        <v>101</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D847" s="8">
+        <v>567.6</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A848" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B848" s="5">
+        <v>101</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D848" s="8">
+        <v>1511.02</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A849" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B849" s="5">
+        <v>101</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D849" s="8">
+        <v>23563.1</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A850" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B850" s="5">
+        <v>101</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D850" s="8">
+        <v>-761.75</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A851" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B851" s="5">
+        <v>101</v>
+      </c>
+      <c r="C851" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D851" s="8">
+        <v>1582.08</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A852" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B852" s="5">
+        <v>101</v>
+      </c>
+      <c r="C852" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D852" s="8">
+        <v>1273.5</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A853" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B853" s="5">
+        <v>101</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D853" s="8">
+        <v>-639.84</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A854" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B854" s="5">
+        <v>101</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D854" s="8">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A855" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B855" s="5">
+        <v>101</v>
+      </c>
+      <c r="C855" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D855" s="8">
+        <v>14381.87</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A856" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B856" s="5">
+        <v>101</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D856" s="8">
+        <v>-3373.44</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A857" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B857" s="5">
+        <v>101</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D857" s="8">
+        <v>5353.44</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A858" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B858" s="5">
+        <v>101</v>
+      </c>
+      <c r="C858" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D858" s="8">
+        <v>5562.9</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A859" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B859" s="5">
+        <v>101</v>
+      </c>
+      <c r="C859" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D859" s="8">
+        <v>20711.900000000001</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A860" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B860" s="5">
+        <v>101</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D860" s="8">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A861" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B861" s="5">
+        <v>101</v>
+      </c>
+      <c r="C861" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D861" s="8">
+        <v>-2700</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A862" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B862" s="5">
+        <v>101</v>
+      </c>
+      <c r="C862" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D862" s="8">
+        <v>216623.32</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A863" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B863" s="5">
+        <v>101</v>
+      </c>
+      <c r="C863" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D863" s="8">
+        <v>5527.5</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A864" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B864" s="5">
+        <v>101</v>
+      </c>
+      <c r="C864" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D864" s="8">
+        <v>2108.84</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A865" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B865" s="5">
+        <v>101</v>
+      </c>
+      <c r="C865" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D865" s="8">
+        <v>24648.5</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A866" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B866" s="5">
+        <v>101</v>
+      </c>
+      <c r="C866" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D866" s="8">
+        <v>4589.7</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A867" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B867" s="5">
+        <v>101</v>
+      </c>
+      <c r="C867" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D867" s="8">
+        <v>4656.08</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A868" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B868" s="5">
+        <v>101</v>
+      </c>
+      <c r="C868" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D868" s="8">
+        <v>-639.84</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A869" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B869" s="5">
+        <v>101</v>
+      </c>
+      <c r="C869" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D869" s="8">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A870" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B870" s="5">
+        <v>101</v>
+      </c>
+      <c r="C870" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D870" s="8">
+        <v>12354</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A871" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B871" s="5">
+        <v>101</v>
+      </c>
+      <c r="C871" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D871" s="8">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A872" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B872" s="5">
+        <v>101</v>
+      </c>
+      <c r="C872" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D872" s="8">
+        <v>1137.79</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A873" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B873" s="5">
+        <v>101</v>
+      </c>
+      <c r="C873" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D873" s="8">
+        <v>1899.2</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A874" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B874" s="5">
+        <v>101</v>
+      </c>
+      <c r="C874" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D874" s="8">
+        <v>1899.2</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A875" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B875" s="5">
+        <v>101</v>
+      </c>
+      <c r="C875" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D875" s="8">
+        <v>524.1</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A876" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B876" s="5">
+        <v>101</v>
+      </c>
+      <c r="C876" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D876" s="8">
+        <v>1172.02</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A877" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B877" s="5">
+        <v>101</v>
+      </c>
+      <c r="C877" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D877" s="8">
+        <v>9133.14</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A878" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B878" s="5">
+        <v>101</v>
+      </c>
+      <c r="C878" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D878" s="8">
+        <v>1831.77</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A879" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B879" s="5">
+        <v>101</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D879" s="8">
+        <v>25944.23</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A880" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B880" s="5">
+        <v>101</v>
+      </c>
+      <c r="C880" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D880" s="8">
+        <v>104016.74</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A881" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B881" s="5">
+        <v>101</v>
+      </c>
+      <c r="C881" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D881" s="8">
+        <v>4432.3999999999996</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A882" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B882" s="5">
+        <v>101</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D882" s="8">
+        <v>1139.52</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A883" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B883" s="5">
+        <v>101</v>
+      </c>
+      <c r="C883" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D883" s="8">
+        <v>2859.4</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A884" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B884" s="5">
+        <v>101</v>
+      </c>
+      <c r="C884" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D884" s="8">
+        <v>124297.77</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A885" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B885" s="5">
+        <v>101</v>
+      </c>
+      <c r="C885" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D885" s="8">
+        <v>-487.02</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A886" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B886" s="5">
+        <v>101</v>
+      </c>
+      <c r="C886" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D886" s="8">
+        <v>26259.13</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A887" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B887" s="5">
+        <v>101</v>
+      </c>
+      <c r="C887" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D887" s="8">
+        <v>305.2</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A888" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B888" s="5">
+        <v>101</v>
+      </c>
+      <c r="C888" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D888" s="8">
+        <v>1481.55</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A889" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B889" s="5">
+        <v>101</v>
+      </c>
+      <c r="C889" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D889" s="8">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A890" s="6">
+        <v>46321</v>
+      </c>
+      <c r="B890" s="5">
+        <v>101</v>
+      </c>
+      <c r="C890" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D890" s="8">
+        <v>1259.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F094D1D-294F-414B-BFEC-A1DEC515B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69B647A-02C4-4198-A020-DF8034DAFEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -1948,7 +1948,7 @@
         <v>46322</v>
       </c>
       <c r="B23">
-        <v>146303.18</v>
+        <v>333797.8</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>75</v>
       </c>
       <c r="B24" s="2">
-        <v>8845521.9800000004</v>
+        <v>9033016.5999999996</v>
       </c>
       <c r="C24" s="2">
         <v>-319379.15000000002</v>
@@ -2005,8 +2005,8 @@
     <hyperlink ref="C21" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A5E30353-68AD-4555-A4A4-F43F7F15A167}"/>
     <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F5D8DE54-95D1-46C8-88FE-0455E31F55EA}"/>
     <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6508494-A2ED-45CE-A06F-52BAF7398889}"/>
-    <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E234A0FC-3F1D-4E49-89FE-CFF8150000F6}"/>
-    <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{3AB773AA-3A9E-4C38-8792-28BC2A833A14}"/>
+    <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{DD30AD69-0057-402B-A83E-B59DBD36F3B0}"/>
+    <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5B426AA7-E462-4457-8A68-E5B75510379A}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId41"/>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69B647A-02C4-4198-A020-DF8034DAFEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665EC49B-C0C2-4D53-9B4D-E33D969C4799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="246">
   <si>
     <t>Filial</t>
   </si>
@@ -747,6 +747,18 @@
   </si>
   <si>
     <t>DASA 61.486.650/0686</t>
+  </si>
+  <si>
+    <t>SOMA CAMPINAS 03.469</t>
+  </si>
+  <si>
+    <t>INSTITUTO HOC</t>
+  </si>
+  <si>
+    <t>HOSP DR. J M</t>
+  </si>
+  <si>
+    <t>GENERA SERVICOS LABO</t>
   </si>
 </sst>
 </file>
@@ -1948,10 +1960,10 @@
         <v>46322</v>
       </c>
       <c r="B23">
-        <v>333797.8</v>
+        <v>501074.18</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>-397.64</v>
       </c>
     </row>
     <row r="24" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
@@ -1959,10 +1971,10 @@
         <v>75</v>
       </c>
       <c r="B24" s="2">
-        <v>9033016.5999999996</v>
+        <v>9200292.9800000004</v>
       </c>
       <c r="C24" s="2">
-        <v>-319379.15000000002</v>
+        <v>-319776.78999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2005,8 +2017,8 @@
     <hyperlink ref="C21" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A5E30353-68AD-4555-A4A4-F43F7F15A167}"/>
     <hyperlink ref="B22" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F5D8DE54-95D1-46C8-88FE-0455E31F55EA}"/>
     <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6508494-A2ED-45CE-A06F-52BAF7398889}"/>
-    <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{DD30AD69-0057-402B-A83E-B59DBD36F3B0}"/>
-    <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5B426AA7-E462-4457-8A68-E5B75510379A}"/>
+    <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{AEE793B7-F5AF-487A-B107-0E30AC64A5B3}"/>
+    <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5B2D560A-0C63-4359-ACFB-3F512F59B412}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId41"/>
@@ -2015,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D948"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -2026,17 +2038,17 @@
     <col min="6" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>74</v>
       </c>
     </row>
@@ -14484,6 +14496,818 @@
       </c>
       <c r="D890" s="8">
         <v>1259.01</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A891" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B891" s="5">
+        <v>101</v>
+      </c>
+      <c r="C891" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D891" s="8">
+        <v>216925.18</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A892" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B892" s="5">
+        <v>101</v>
+      </c>
+      <c r="C892" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D892" s="8">
+        <v>13304.93</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A893" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B893" s="5">
+        <v>101</v>
+      </c>
+      <c r="C893" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D893" s="8">
+        <v>15819.99</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A894" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B894" s="5">
+        <v>101</v>
+      </c>
+      <c r="C894" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D894" s="8">
+        <v>186.3</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A895" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B895" s="5">
+        <v>101</v>
+      </c>
+      <c r="C895" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D895" s="8">
+        <v>502.8</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A896" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B896" s="5">
+        <v>101</v>
+      </c>
+      <c r="C896" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D896" s="8">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A897" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B897" s="5">
+        <v>101</v>
+      </c>
+      <c r="C897" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D897" s="8">
+        <v>3207.44</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A898" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B898" s="5">
+        <v>101</v>
+      </c>
+      <c r="C898" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D898" s="8">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A899" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B899" s="5">
+        <v>101</v>
+      </c>
+      <c r="C899" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D899" s="8">
+        <v>174.02</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A900" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B900" s="5">
+        <v>101</v>
+      </c>
+      <c r="C900" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D900" s="8">
+        <v>1291.05</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A901" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B901" s="5">
+        <v>101</v>
+      </c>
+      <c r="C901" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D901" s="8">
+        <v>-214.82</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A902" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B902" s="5">
+        <v>101</v>
+      </c>
+      <c r="C902" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D902" s="8">
+        <v>5653</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A903" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B903" s="5">
+        <v>101</v>
+      </c>
+      <c r="C903" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D903" s="8">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A904" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B904" s="5">
+        <v>101</v>
+      </c>
+      <c r="C904" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D904" s="8">
+        <v>566.6</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A905" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B905" s="5">
+        <v>101</v>
+      </c>
+      <c r="C905" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D905" s="8">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="906" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A906" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B906" s="5">
+        <v>101</v>
+      </c>
+      <c r="C906" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D906" s="8">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="907" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A907" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B907" s="5">
+        <v>101</v>
+      </c>
+      <c r="C907" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D907" s="8">
+        <v>404.79</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A908" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B908" s="5">
+        <v>101</v>
+      </c>
+      <c r="C908" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D908" s="8">
+        <v>252.69</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A909" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B909" s="5">
+        <v>101</v>
+      </c>
+      <c r="C909" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D909" s="8">
+        <v>511.55</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A910" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B910" s="5">
+        <v>101</v>
+      </c>
+      <c r="C910" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D910" s="8">
+        <v>651.20000000000005</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A911" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B911" s="5">
+        <v>101</v>
+      </c>
+      <c r="C911" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D911" s="8">
+        <v>1905.73</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A912" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B912" s="5">
+        <v>101</v>
+      </c>
+      <c r="C912" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D912" s="8">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A913" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B913" s="5">
+        <v>101</v>
+      </c>
+      <c r="C913" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D913" s="8">
+        <v>24812.44</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A914" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B914" s="5">
+        <v>101</v>
+      </c>
+      <c r="C914" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D914" s="8">
+        <v>65.680000000000007</v>
+      </c>
+    </row>
+    <row r="915" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A915" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B915" s="5">
+        <v>101</v>
+      </c>
+      <c r="C915" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D915" s="8">
+        <v>17556.349999999999</v>
+      </c>
+    </row>
+    <row r="916" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A916" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B916" s="5">
+        <v>101</v>
+      </c>
+      <c r="C916" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D916" s="8">
+        <v>3969.77</v>
+      </c>
+    </row>
+    <row r="917" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A917" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B917" s="5">
+        <v>101</v>
+      </c>
+      <c r="C917" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D917" s="8">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="918" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A918" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B918" s="5">
+        <v>101</v>
+      </c>
+      <c r="C918" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D918" s="8">
+        <v>845.5</v>
+      </c>
+    </row>
+    <row r="919" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A919" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B919" s="5">
+        <v>101</v>
+      </c>
+      <c r="C919" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D919" s="8">
+        <v>116091.37</v>
+      </c>
+    </row>
+    <row r="920" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A920" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B920" s="5">
+        <v>101</v>
+      </c>
+      <c r="C920" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D920" s="8">
+        <v>2558.52</v>
+      </c>
+    </row>
+    <row r="921" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A921" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B921" s="5">
+        <v>101</v>
+      </c>
+      <c r="C921" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D921" s="8">
+        <v>1403.02</v>
+      </c>
+    </row>
+    <row r="922" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A922" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B922" s="5">
+        <v>101</v>
+      </c>
+      <c r="C922" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D922" s="8">
+        <v>593.46</v>
+      </c>
+    </row>
+    <row r="923" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A923" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B923" s="5">
+        <v>101</v>
+      </c>
+      <c r="C923" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D923" s="8">
+        <v>1227.48</v>
+      </c>
+    </row>
+    <row r="924" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A924" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B924" s="5">
+        <v>101</v>
+      </c>
+      <c r="C924" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D924" s="8">
+        <v>1979.94</v>
+      </c>
+    </row>
+    <row r="925" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A925" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B925" s="5">
+        <v>101</v>
+      </c>
+      <c r="C925" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D925" s="8">
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="926" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A926" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B926" s="5">
+        <v>101</v>
+      </c>
+      <c r="C926" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D926" s="8">
+        <v>7054.3</v>
+      </c>
+    </row>
+    <row r="927" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A927" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B927" s="5">
+        <v>101</v>
+      </c>
+      <c r="C927" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D927" s="8">
+        <v>4382.76</v>
+      </c>
+    </row>
+    <row r="928" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A928" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B928" s="5">
+        <v>101</v>
+      </c>
+      <c r="C928" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D928" s="8">
+        <v>1867.78</v>
+      </c>
+    </row>
+    <row r="929" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A929" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B929" s="5">
+        <v>101</v>
+      </c>
+      <c r="C929" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D929" s="8">
+        <v>687.8</v>
+      </c>
+    </row>
+    <row r="930" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A930" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B930" s="5">
+        <v>101</v>
+      </c>
+      <c r="C930" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D930" s="8">
+        <v>11332</v>
+      </c>
+    </row>
+    <row r="931" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A931" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B931" s="5">
+        <v>101</v>
+      </c>
+      <c r="C931" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D931" s="8">
+        <v>3461.43</v>
+      </c>
+    </row>
+    <row r="932" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A932" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B932" s="5">
+        <v>101</v>
+      </c>
+      <c r="C932" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D932" s="8">
+        <v>75.760000000000005</v>
+      </c>
+    </row>
+    <row r="933" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A933" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B933" s="5">
+        <v>101</v>
+      </c>
+      <c r="C933" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D933" s="8">
+        <v>52.03</v>
+      </c>
+    </row>
+    <row r="934" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A934" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B934" s="5">
+        <v>101</v>
+      </c>
+      <c r="C934" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D934" s="8">
+        <v>433.1</v>
+      </c>
+    </row>
+    <row r="935" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A935" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B935" s="5">
+        <v>101</v>
+      </c>
+      <c r="C935" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D935" s="8">
+        <v>163.85</v>
+      </c>
+    </row>
+    <row r="936" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A936" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B936" s="5">
+        <v>101</v>
+      </c>
+      <c r="C936" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D936" s="8">
+        <v>8030.12</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A937" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B937" s="5">
+        <v>101</v>
+      </c>
+      <c r="C937" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D937" s="8">
+        <v>763.47</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A938" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B938" s="5">
+        <v>101</v>
+      </c>
+      <c r="C938" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D938" s="8">
+        <v>4705.68</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A939" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B939" s="5">
+        <v>101</v>
+      </c>
+      <c r="C939" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D939" s="8">
+        <v>1272.45</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A940" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B940" s="5">
+        <v>101</v>
+      </c>
+      <c r="C940" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D940" s="8">
+        <v>10687</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A941" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B941" s="5">
+        <v>101</v>
+      </c>
+      <c r="C941" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D941" s="8">
+        <v>21714</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A942" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B942" s="5">
+        <v>101</v>
+      </c>
+      <c r="C942" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D942" s="8">
+        <v>-182.82</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A943" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B943" s="5">
+        <v>101</v>
+      </c>
+      <c r="C943" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D943" s="8">
+        <v>1815.66</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A944" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B944" s="5">
+        <v>101</v>
+      </c>
+      <c r="C944" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D944" s="8">
+        <v>988.45</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A945" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B945" s="5">
+        <v>101</v>
+      </c>
+      <c r="C945" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D945" s="8">
+        <v>821.8</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A946" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B946" s="5">
+        <v>101</v>
+      </c>
+      <c r="C946" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D946" s="8">
+        <v>610.4</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A947" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B947" s="5">
+        <v>101</v>
+      </c>
+      <c r="C947" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D947" s="8">
+        <v>3412.9</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A948" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B948" s="5">
+        <v>101</v>
+      </c>
+      <c r="C948" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D948" s="8">
+        <v>213.64</v>
       </c>
     </row>
   </sheetData>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665EC49B-C0C2-4D53-9B4D-E33D969C4799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1711666A-997D-4D0B-9B08-1367F1DAB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -1711,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19101EBF-008C-4E37-90C0-CF2D419D5300}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1967,14 +1967,25 @@
       </c>
     </row>
     <row r="24" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3">
+        <v>46323</v>
+      </c>
+      <c r="B24">
+        <v>346987.98</v>
+      </c>
+      <c r="C24">
+        <v>-14081.69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="2">
-        <v>9200292.9800000004</v>
-      </c>
-      <c r="C24" s="2">
-        <v>-319776.78999999998</v>
+      <c r="B25" s="2">
+        <v>9449348.9600000009</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-333858.48</v>
       </c>
     </row>
   </sheetData>
@@ -2019,9 +2030,11 @@
     <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6508494-A2ED-45CE-A06F-52BAF7398889}"/>
     <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{AEE793B7-F5AF-487A-B107-0E30AC64A5B3}"/>
     <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5B2D560A-0C63-4359-ACFB-3F512F59B412}"/>
+    <hyperlink ref="B24" r:id="rId41" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{AFF04227-3C77-4389-88C6-89725CA803DA}"/>
+    <hyperlink ref="C24" r:id="rId42" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{123386E2-900D-431C-A53B-090E37DD1B5B}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId41"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId43"/>
 </worksheet>
 </file>
 

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1711666A-997D-4D0B-9B08-1367F1DAB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E9EC6B-862D-4F8B-BC67-0222A14F6142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="248">
   <si>
     <t>Filial</t>
   </si>
@@ -759,6 +759,12 @@
   </si>
   <si>
     <t>GENERA SERVICOS LABO</t>
+  </si>
+  <si>
+    <t>MEDISE</t>
+  </si>
+  <si>
+    <t>CONGREGACAO</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1267,6 +1273,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1312,7 +1333,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1335,6 +1356,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1967,11 +1991,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="9">
         <v>46323</v>
       </c>
       <c r="B24">
-        <v>346987.98</v>
+        <v>367755.97</v>
       </c>
       <c r="C24">
         <v>-14081.69</v>
@@ -1982,7 +2006,7 @@
         <v>75</v>
       </c>
       <c r="B25" s="2">
-        <v>9449348.9600000009</v>
+        <v>9470116.9499999993</v>
       </c>
       <c r="C25" s="2">
         <v>-333858.48</v>
@@ -2030,8 +2054,8 @@
     <hyperlink ref="C22" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6508494-A2ED-45CE-A06F-52BAF7398889}"/>
     <hyperlink ref="B23" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{AEE793B7-F5AF-487A-B107-0E30AC64A5B3}"/>
     <hyperlink ref="C23" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5B2D560A-0C63-4359-ACFB-3F512F59B412}"/>
-    <hyperlink ref="B24" r:id="rId41" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{AFF04227-3C77-4389-88C6-89725CA803DA}"/>
-    <hyperlink ref="C24" r:id="rId42" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{123386E2-900D-431C-A53B-090E37DD1B5B}"/>
+    <hyperlink ref="B24" r:id="rId41" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{34D1B18E-35BC-42C7-9732-5F6E5B4D5F23}"/>
+    <hyperlink ref="C24" r:id="rId42" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{76B454AD-05EE-48D8-8898-81B3D35B99AC}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId43"/>
@@ -2040,15 +2064,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:D948"/>
+  <dimension ref="A1:D995"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="5"/>
+    <col min="5" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15323,6 +15346,664 @@
         <v>213.64</v>
       </c>
     </row>
+    <row r="949" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A949" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B949" s="5">
+        <v>101</v>
+      </c>
+      <c r="C949" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D949" s="8">
+        <v>117397.42</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A950" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B950" s="5">
+        <v>101</v>
+      </c>
+      <c r="C950" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D950" s="8">
+        <v>12117.82</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A951" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B951" s="5">
+        <v>101</v>
+      </c>
+      <c r="C951" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D951" s="8">
+        <v>12102.4</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A952" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B952" s="5">
+        <v>101</v>
+      </c>
+      <c r="C952" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D952" s="5">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A953" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B953" s="5">
+        <v>101</v>
+      </c>
+      <c r="C953" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D953" s="8">
+        <v>1213.28</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A954" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B954" s="5">
+        <v>101</v>
+      </c>
+      <c r="C954" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D954" s="8">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A955" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B955" s="5">
+        <v>101</v>
+      </c>
+      <c r="C955" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D955" s="5">
+        <v>-642.34</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A956" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B956" s="5">
+        <v>101</v>
+      </c>
+      <c r="C956" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D956" s="8">
+        <v>-4746.6000000000004</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A957" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B957" s="5">
+        <v>101</v>
+      </c>
+      <c r="C957" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D957" s="8">
+        <v>23280</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A958" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B958" s="5">
+        <v>101</v>
+      </c>
+      <c r="C958" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D958" s="8">
+        <v>10841.95</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A959" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B959" s="5">
+        <v>101</v>
+      </c>
+      <c r="C959" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D959" s="8">
+        <v>-1036</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A960" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B960" s="5">
+        <v>101</v>
+      </c>
+      <c r="C960" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D960" s="8">
+        <v>2924.4</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A961" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B961" s="5">
+        <v>101</v>
+      </c>
+      <c r="C961" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D961" s="8">
+        <v>15505.63</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A962" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B962" s="5">
+        <v>101</v>
+      </c>
+      <c r="C962" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D962" s="8">
+        <v>9934.01</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A963" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B963" s="5">
+        <v>101</v>
+      </c>
+      <c r="C963" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D963" s="8">
+        <v>1337.85</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A964" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B964" s="5">
+        <v>101</v>
+      </c>
+      <c r="C964" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D964" s="8">
+        <v>40166.03</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A965" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B965" s="5">
+        <v>101</v>
+      </c>
+      <c r="C965" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D965" s="8">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A966" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B966" s="5">
+        <v>101</v>
+      </c>
+      <c r="C966" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D966" s="8">
+        <v>28889.22</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A967" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B967" s="5">
+        <v>101</v>
+      </c>
+      <c r="C967" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D967" s="8">
+        <v>-2797.2</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A968" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B968" s="5">
+        <v>101</v>
+      </c>
+      <c r="C968" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D968" s="8">
+        <v>7270.12</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A969" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B969" s="5">
+        <v>101</v>
+      </c>
+      <c r="C969" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D969" s="8">
+        <v>1899.2</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A970" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B970" s="5">
+        <v>101</v>
+      </c>
+      <c r="C970" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D970" s="8">
+        <v>11332</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A971" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B971" s="5">
+        <v>101</v>
+      </c>
+      <c r="C971" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D971" s="8">
+        <v>3154.98</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A972" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B972" s="5">
+        <v>101</v>
+      </c>
+      <c r="C972" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D972" s="8">
+        <v>4590.1400000000003</v>
+      </c>
+    </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A973" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B973" s="5">
+        <v>101</v>
+      </c>
+      <c r="C973" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D973" s="8">
+        <v>8741.0300000000007</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A974" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B974" s="5">
+        <v>101</v>
+      </c>
+      <c r="C974" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D974" s="5">
+        <v>416.9</v>
+      </c>
+    </row>
+    <row r="975" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A975" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B975" s="5">
+        <v>101</v>
+      </c>
+      <c r="C975" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D975" s="8">
+        <v>1023.65</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A976" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B976" s="5">
+        <v>101</v>
+      </c>
+      <c r="C976" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D976" s="8">
+        <v>4587.47</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A977" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B977" s="5">
+        <v>101</v>
+      </c>
+      <c r="C977" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D977" s="8">
+        <v>1990.08</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A978" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B978" s="5">
+        <v>101</v>
+      </c>
+      <c r="C978" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D978" s="8">
+        <v>2023.32</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A979" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B979" s="5">
+        <v>101</v>
+      </c>
+      <c r="C979" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D979" s="8">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A980" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B980" s="5">
+        <v>101</v>
+      </c>
+      <c r="C980" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D980" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A981" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B981" s="5">
+        <v>101</v>
+      </c>
+      <c r="C981" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D981" s="5">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A982" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B982" s="5">
+        <v>101</v>
+      </c>
+      <c r="C982" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D982" s="8">
+        <v>27847.200000000001</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A983" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B983" s="5">
+        <v>101</v>
+      </c>
+      <c r="C983" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D983" s="8">
+        <v>-4320</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A984" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B984" s="5">
+        <v>101</v>
+      </c>
+      <c r="C984" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D984" s="8">
+        <v>1067.04</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A985" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B985" s="5">
+        <v>101</v>
+      </c>
+      <c r="C985" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D985" s="5">
+        <v>608.28</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A986" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B986" s="5">
+        <v>101</v>
+      </c>
+      <c r="C986" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D986" s="8">
+        <v>1689.5</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A987" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B987" s="5">
+        <v>101</v>
+      </c>
+      <c r="C987" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D987" s="5">
+        <v>710.41</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A988" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B988" s="5">
+        <v>101</v>
+      </c>
+      <c r="C988" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D988" s="5">
+        <v>457.8</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A989" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B989" s="5">
+        <v>101</v>
+      </c>
+      <c r="C989" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D989" s="5">
+        <v>-539.54999999999995</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A990" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B990" s="5">
+        <v>101</v>
+      </c>
+      <c r="C990" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D990" s="5">
+        <v>457.8</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A991" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B991" s="5">
+        <v>101</v>
+      </c>
+      <c r="C991" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D991" s="5">
+        <v>373.9</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A992" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B992" s="5">
+        <v>101</v>
+      </c>
+      <c r="C992" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D992" s="5">
+        <v>366.24</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A993" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B993" s="5">
+        <v>101</v>
+      </c>
+      <c r="C993" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D993" s="5">
+        <v>396.76</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A994" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B994" s="5">
+        <v>101</v>
+      </c>
+      <c r="C994" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D994" s="5">
+        <v>224.34</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A995" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B995" s="5">
+        <v>101</v>
+      </c>
+      <c r="C995" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D995" s="5">
+        <v>100.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9E092-B214-420C-9E40-CD84F2C211ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A4FC15-C52A-4F70-9FBF-C90ABE967B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="9">
-        <v>0</v>
+        <v>9789630.4499999993</v>
       </c>
     </row>
   </sheetData>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A4FC15-C52A-4F70-9FBF-C90ABE967B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D6FC34-69BE-420C-B4F6-814AC15640A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="252">
   <si>
     <t>Filial</t>
   </si>
@@ -777,34 +777,13 @@
   </si>
   <si>
     <t>TOT</t>
-  </si>
-  <si>
-    <t>qui</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>seg</t>
-  </si>
-  <si>
-    <t>ter</t>
-  </si>
-  <si>
-    <t>qua</t>
-  </si>
-  <si>
-    <t>sáb</t>
-  </si>
-  <si>
-    <t>dom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,6 +930,29 @@
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.6"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.6"/>
+      <color rgb="FF212529"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1146,7 +1148,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1293,15 +1295,54 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFDEE2E6"/>
+        <color rgb="FF808080"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF808080"/>
       </left>
       <right style="medium">
-        <color rgb="FFDEE2E6"/>
+        <color rgb="FF808080"/>
       </right>
       <top style="medium">
-        <color rgb="FFDEE2E6"/>
+        <color rgb="FF808080"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF808080"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF808080"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1309,9 +1350,11 @@
         <color rgb="FFDEE2E6"/>
       </left>
       <right style="medium">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="medium">
         <color rgb="FFDEE2E6"/>
-      </right>
-      <top/>
+      </top>
       <bottom style="medium">
         <color rgb="FFDEE2E6"/>
       </bottom>
@@ -1319,15 +1362,21 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFDEE2E6"/>
+        <color rgb="FF808080"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="medium">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1370,8 +1419,9 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="19" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1389,21 +1439,53 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="11" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1433,6 +1515,7 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Hiperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
@@ -1781,758 +1864,879 @@
   <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="19"/>
+      <c r="H1" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="I1" s="10"/>
-    </row>
-    <row r="2" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" t="s">
+      <c r="I1" s="19"/>
+      <c r="J1" s="20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="5">
+      <c r="J2" s="21"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>46296</v>
       </c>
-      <c r="C3" s="9">
+      <c r="B3" s="10">
         <v>271426.78000000003</v>
       </c>
-      <c r="D3">
+      <c r="C3" s="11">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="D3" s="11">
         <v>619.79999999999995</v>
       </c>
-      <c r="F3">
+      <c r="E3" s="11">
         <v>0</v>
       </c>
-      <c r="H3">
+      <c r="F3" s="8"/>
+      <c r="G3" s="11">
         <v>0</v>
       </c>
-      <c r="I3">
+      <c r="H3" s="8"/>
+      <c r="I3" s="11">
         <v>0</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="12">
         <v>272046.58</v>
       </c>
     </row>
     <row r="4" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="A4" s="9">
         <v>46297</v>
       </c>
-      <c r="C4" s="9">
+      <c r="B4" s="10">
         <v>423201.75</v>
       </c>
-      <c r="D4" s="9">
+      <c r="C4" s="10">
         <v>-26599.88</v>
       </c>
-      <c r="E4" s="9">
+      <c r="D4" s="10">
         <v>60744.65</v>
       </c>
-      <c r="F4">
+      <c r="E4" s="11">
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="F4" s="8"/>
+      <c r="G4" s="11">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="H4" s="8"/>
+      <c r="I4" s="11">
         <v>0</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="12">
         <v>457346.52</v>
       </c>
     </row>
     <row r="5" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="9">
         <v>46300</v>
       </c>
-      <c r="C5" s="9">
+      <c r="B5" s="10">
         <v>279190.96000000002</v>
       </c>
-      <c r="D5" s="9">
+      <c r="C5" s="10">
         <v>-7502.05</v>
       </c>
-      <c r="E5" s="9">
+      <c r="D5" s="10">
         <v>33687.550000000003</v>
       </c>
-      <c r="F5">
+      <c r="E5" s="11">
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="F5" s="8"/>
+      <c r="G5" s="11">
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="H5" s="8"/>
+      <c r="I5" s="11">
         <v>0</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="12">
         <v>305376.46000000002</v>
       </c>
     </row>
     <row r="6" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" s="9">
         <v>46301</v>
       </c>
-      <c r="C6" s="9">
+      <c r="B6" s="10">
         <v>425539.17</v>
       </c>
-      <c r="D6" s="9">
+      <c r="C6" s="10">
         <v>-15443.4</v>
       </c>
-      <c r="E6" s="9">
+      <c r="D6" s="10">
         <v>51272.05</v>
       </c>
-      <c r="F6">
+      <c r="E6" s="11">
         <v>-149.56</v>
       </c>
-      <c r="H6">
+      <c r="F6" s="8"/>
+      <c r="G6" s="11">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="H6" s="8"/>
+      <c r="I6" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="12">
         <v>461218.26</v>
       </c>
     </row>
     <row r="7" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="9">
         <v>46302</v>
       </c>
-      <c r="C7" s="9">
+      <c r="B7" s="10">
         <v>306641.53000000003</v>
       </c>
-      <c r="D7" s="9">
+      <c r="C7" s="10">
         <v>-12949.2</v>
       </c>
-      <c r="E7" s="9">
+      <c r="D7" s="10">
         <v>26119.68</v>
       </c>
-      <c r="F7">
+      <c r="E7" s="11">
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="F7" s="8"/>
+      <c r="G7" s="11">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="H7" s="8"/>
+      <c r="I7" s="11">
         <v>0</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="12">
         <v>319812.01</v>
       </c>
     </row>
     <row r="8" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="9">
         <v>46303</v>
       </c>
-      <c r="C8" s="9">
+      <c r="B8" s="10">
         <v>578381.43999999994</v>
       </c>
-      <c r="D8">
+      <c r="C8" s="11">
         <v>0</v>
       </c>
-      <c r="E8" s="9">
+      <c r="D8" s="10">
         <v>14425.52</v>
       </c>
-      <c r="F8">
+      <c r="E8" s="11">
         <v>0</v>
       </c>
-      <c r="H8">
+      <c r="F8" s="8"/>
+      <c r="G8" s="11">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="H8" s="8"/>
+      <c r="I8" s="11">
         <v>0</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="12">
         <v>592806.96</v>
       </c>
     </row>
     <row r="9" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="9">
         <v>46304</v>
       </c>
-      <c r="C9" s="9">
+      <c r="B9" s="10">
         <v>307842.78999999998</v>
       </c>
-      <c r="D9" s="9">
+      <c r="C9" s="10">
         <v>-70366.45</v>
       </c>
-      <c r="E9" s="9">
+      <c r="D9" s="10">
         <v>46378.81</v>
       </c>
-      <c r="F9">
+      <c r="E9" s="11">
         <v>-317</v>
       </c>
-      <c r="H9">
+      <c r="F9" s="8"/>
+      <c r="G9" s="11">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="H9" s="8"/>
+      <c r="I9" s="11">
         <v>0</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="12">
         <v>283538.15000000002</v>
       </c>
     </row>
     <row r="10" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="9">
         <v>46305</v>
       </c>
-      <c r="C10" s="9">
+      <c r="B10" s="10">
         <v>203772.98</v>
       </c>
-      <c r="D10">
+      <c r="C10" s="11">
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="D10" s="8"/>
+      <c r="E10" s="11">
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="F10" s="8"/>
+      <c r="G10" s="11">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="H10" s="8"/>
+      <c r="I10" s="11">
         <v>0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="12">
         <v>203772.98</v>
       </c>
     </row>
     <row r="11" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B11" s="5">
+      <c r="A11" s="9">
         <v>46306</v>
       </c>
-      <c r="C11" s="9">
+      <c r="B11" s="10">
         <v>169560.7</v>
       </c>
-      <c r="D11">
+      <c r="C11" s="11">
         <v>0</v>
       </c>
-      <c r="F11">
+      <c r="D11" s="8"/>
+      <c r="E11" s="11">
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="F11" s="8"/>
+      <c r="G11" s="11">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="H11" s="8"/>
+      <c r="I11" s="11">
         <v>0</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="12">
         <v>169560.7</v>
       </c>
     </row>
     <row r="12" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="A12" s="9">
         <v>46307</v>
       </c>
-      <c r="C12" s="9">
+      <c r="B12" s="10">
         <v>216275.07</v>
       </c>
-      <c r="D12">
+      <c r="C12" s="11">
         <v>0</v>
       </c>
-      <c r="F12">
+      <c r="D12" s="8"/>
+      <c r="E12" s="11">
         <v>0</v>
       </c>
-      <c r="H12">
+      <c r="F12" s="8"/>
+      <c r="G12" s="11">
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="H12" s="8"/>
+      <c r="I12" s="11">
         <v>0</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="12">
         <v>216275.07</v>
       </c>
     </row>
     <row r="13" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B13" s="5">
+      <c r="A13" s="9">
         <v>46308</v>
       </c>
-      <c r="C13" s="9">
+      <c r="B13" s="10">
         <v>476395.59</v>
       </c>
-      <c r="D13" s="9">
+      <c r="C13" s="10">
         <v>-29468.28</v>
       </c>
-      <c r="E13" s="9">
+      <c r="D13" s="10">
         <v>57788.11</v>
       </c>
-      <c r="F13">
+      <c r="E13" s="11">
         <v>0</v>
       </c>
-      <c r="H13">
+      <c r="F13" s="8"/>
+      <c r="G13" s="11">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="H13" s="8"/>
+      <c r="I13" s="11">
         <v>0</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="12">
         <v>504715.42</v>
       </c>
     </row>
     <row r="14" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B14" s="5">
+      <c r="A14" s="9">
         <v>46309</v>
       </c>
-      <c r="C14" s="9">
+      <c r="B14" s="10">
         <v>278778.15999999997</v>
       </c>
-      <c r="D14" s="9">
+      <c r="C14" s="10">
         <v>-14134.51</v>
       </c>
-      <c r="E14" s="9">
+      <c r="D14" s="10">
         <v>70986.45</v>
       </c>
-      <c r="F14">
+      <c r="E14" s="11">
         <v>0</v>
       </c>
-      <c r="H14">
+      <c r="F14" s="8"/>
+      <c r="G14" s="11">
         <v>0</v>
       </c>
-      <c r="I14">
+      <c r="H14" s="8"/>
+      <c r="I14" s="11">
         <v>0</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="12">
         <v>335630.1</v>
       </c>
     </row>
     <row r="15" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="A15" s="9">
         <v>46310</v>
       </c>
-      <c r="C15" s="9">
+      <c r="B15" s="10">
         <v>281419.15999999997</v>
       </c>
-      <c r="D15">
+      <c r="C15" s="11">
         <v>0</v>
       </c>
-      <c r="E15" s="9">
+      <c r="D15" s="10">
         <v>33803.629999999997</v>
       </c>
-      <c r="F15" s="9">
+      <c r="E15" s="10">
         <v>-11085.38</v>
       </c>
-      <c r="H15">
+      <c r="F15" s="8"/>
+      <c r="G15" s="11">
         <v>0</v>
       </c>
-      <c r="I15">
+      <c r="H15" s="8"/>
+      <c r="I15" s="11">
         <v>0</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="12">
         <v>304137.40999999997</v>
       </c>
     </row>
     <row r="16" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" s="5">
+      <c r="A16" s="9">
         <v>46311</v>
       </c>
-      <c r="C16" s="9">
+      <c r="B16" s="10">
         <v>1353057.37</v>
       </c>
-      <c r="D16">
+      <c r="C16" s="11">
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="D16" s="10">
         <v>29492.51</v>
       </c>
-      <c r="F16">
+      <c r="E16" s="11">
         <v>0</v>
       </c>
-      <c r="H16">
+      <c r="F16" s="8"/>
+      <c r="G16" s="11">
         <v>0</v>
       </c>
-      <c r="I16">
+      <c r="H16" s="8"/>
+      <c r="I16" s="11">
         <v>0</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="12">
         <v>1382549.88</v>
       </c>
     </row>
     <row r="17" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B17" s="5">
+      <c r="A17" s="9">
         <v>46314</v>
       </c>
-      <c r="C17" s="9">
+      <c r="B17" s="10">
         <v>336565.44</v>
       </c>
-      <c r="D17">
+      <c r="C17" s="11">
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="D17" s="8"/>
+      <c r="E17" s="11">
         <v>0</v>
       </c>
-      <c r="H17">
+      <c r="F17" s="8"/>
+      <c r="G17" s="11">
         <v>0</v>
       </c>
-      <c r="I17">
+      <c r="H17" s="8"/>
+      <c r="I17" s="11">
         <v>0</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="12">
         <v>336565.44</v>
       </c>
     </row>
     <row r="18" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="9">
         <v>46315</v>
       </c>
-      <c r="C18" s="9">
+      <c r="B18" s="10">
         <v>381768.26</v>
       </c>
-      <c r="D18" s="9">
+      <c r="C18" s="10">
         <v>-63152.34</v>
       </c>
-      <c r="E18" s="9">
+      <c r="D18" s="10">
         <v>51209.3</v>
       </c>
-      <c r="F18">
+      <c r="E18" s="11">
         <v>0</v>
       </c>
-      <c r="H18">
+      <c r="F18" s="8"/>
+      <c r="G18" s="11">
         <v>0</v>
       </c>
-      <c r="I18">
+      <c r="H18" s="8"/>
+      <c r="I18" s="11">
         <v>0</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="12">
         <v>369825.22</v>
       </c>
     </row>
     <row r="19" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B19" s="5">
+      <c r="A19" s="9">
         <v>46316</v>
       </c>
-      <c r="C19" s="9">
+      <c r="B19" s="10">
         <v>548968.22</v>
       </c>
-      <c r="D19" s="9">
+      <c r="C19" s="10">
         <v>-24640.94</v>
       </c>
-      <c r="E19" s="9">
+      <c r="D19" s="10">
         <v>43879.51</v>
       </c>
-      <c r="F19">
+      <c r="E19" s="11">
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="F19" s="8"/>
+      <c r="G19" s="11">
         <v>0</v>
       </c>
-      <c r="I19">
+      <c r="H19" s="8"/>
+      <c r="I19" s="11">
         <v>0</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="12">
         <v>568206.79</v>
       </c>
     </row>
     <row r="20" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B20" s="5">
+      <c r="A20" s="9">
         <v>46317</v>
       </c>
-      <c r="C20" s="9">
+      <c r="B20" s="10">
         <v>647160.07999999996</v>
       </c>
-      <c r="D20" s="9">
+      <c r="C20" s="10">
         <v>-26687.200000000001</v>
       </c>
-      <c r="E20" s="9">
+      <c r="D20" s="10">
         <v>50411.43</v>
       </c>
-      <c r="F20">
+      <c r="E20" s="11">
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="F20" s="8"/>
+      <c r="G20" s="11">
         <v>0</v>
       </c>
-      <c r="I20">
+      <c r="H20" s="8"/>
+      <c r="I20" s="11">
         <v>0</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="12">
         <v>670884.31000000006</v>
       </c>
     </row>
     <row r="21" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="5">
+      <c r="A21" s="9">
         <v>46318</v>
       </c>
-      <c r="C21" s="9">
+      <c r="B21" s="10">
         <v>380210.58</v>
       </c>
-      <c r="D21" s="9">
+      <c r="C21" s="10">
         <v>-19833.009999999998</v>
       </c>
-      <c r="E21" s="9">
+      <c r="D21" s="10">
         <v>22362.76</v>
       </c>
-      <c r="F21">
+      <c r="E21" s="11">
         <v>0</v>
       </c>
-      <c r="H21">
+      <c r="F21" s="8"/>
+      <c r="G21" s="11">
         <v>0</v>
       </c>
-      <c r="I21">
+      <c r="H21" s="8"/>
+      <c r="I21" s="11">
         <v>0</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="12">
         <v>382740.33</v>
       </c>
     </row>
     <row r="22" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="9">
         <v>46321</v>
       </c>
-      <c r="C22" s="9">
+      <c r="B22" s="10">
         <v>833062.77</v>
       </c>
-      <c r="D22" s="9">
+      <c r="C22" s="10">
         <v>-8601.89</v>
       </c>
-      <c r="E22" s="9">
+      <c r="D22" s="10">
         <v>30850.26</v>
       </c>
-      <c r="F22">
+      <c r="E22" s="11">
         <v>0</v>
       </c>
-      <c r="H22">
+      <c r="F22" s="8"/>
+      <c r="G22" s="11">
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="H22" s="8"/>
+      <c r="I22" s="11">
         <v>0</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="12">
         <v>855311.14</v>
       </c>
     </row>
     <row r="23" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B23" s="5">
+      <c r="A23" s="9">
         <v>46322</v>
       </c>
-      <c r="C23" s="9">
+      <c r="B23" s="10">
         <v>403142.18</v>
       </c>
-      <c r="D23">
+      <c r="C23" s="11">
         <v>-397.64</v>
       </c>
-      <c r="E23" s="9">
+      <c r="D23" s="10">
         <v>15633.35</v>
       </c>
-      <c r="F23" s="9">
+      <c r="E23" s="10">
         <v>-4776.72</v>
       </c>
-      <c r="H23">
+      <c r="F23" s="8"/>
+      <c r="G23" s="11">
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="H23" s="8"/>
+      <c r="I23" s="11">
         <v>0</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="12">
         <v>413601.17</v>
       </c>
     </row>
     <row r="24" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B24" s="5">
+      <c r="A24" s="9">
         <v>46323</v>
       </c>
-      <c r="C24" s="9">
+      <c r="B24" s="10">
         <v>367755.97</v>
       </c>
-      <c r="D24" s="9">
+      <c r="C24" s="10">
         <v>-14081.69</v>
       </c>
-      <c r="E24" s="9">
+      <c r="D24" s="10">
         <v>20991.67</v>
       </c>
-      <c r="F24">
+      <c r="E24" s="11">
         <v>0</v>
       </c>
-      <c r="H24">
+      <c r="F24" s="8"/>
+      <c r="G24" s="11">
         <v>0</v>
       </c>
-      <c r="I24">
+      <c r="H24" s="8"/>
+      <c r="I24" s="11">
         <v>0</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="12">
         <v>374665.95</v>
       </c>
     </row>
     <row r="25" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B25" s="5">
+      <c r="A25" s="9">
         <v>46324</v>
       </c>
-      <c r="C25" s="9">
+      <c r="B25" s="10">
         <v>39248.85</v>
       </c>
-      <c r="D25" s="9">
+      <c r="C25" s="10">
         <v>-30205.25</v>
       </c>
-      <c r="F25">
+      <c r="D25" s="8"/>
+      <c r="E25" s="11">
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="F25" s="8"/>
+      <c r="G25" s="11">
         <v>0</v>
       </c>
-      <c r="I25">
+      <c r="H25" s="8"/>
+      <c r="I25" s="11">
         <v>0</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="12">
+        <v>9043.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="14">
+        <v>9509365.8000000007</v>
+      </c>
+      <c r="C26" s="14">
+        <v>-364063.73</v>
+      </c>
+      <c r="D26" s="14">
+        <v>660657.04</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-16328.66</v>
+      </c>
+      <c r="F26" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="9">
-        <v>9509365.8000000007</v>
-      </c>
-      <c r="D26" s="9">
-        <v>-364063.73</v>
-      </c>
-      <c r="E26" s="9">
-        <v>660657.04</v>
-      </c>
-      <c r="F26" s="9">
-        <v>-16328.66</v>
-      </c>
-      <c r="G26">
+      <c r="G26" s="15">
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="15">
         <v>0</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="15">
         <v>0</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="14">
         <v>9789630.4499999993</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{687BB916-39E4-451A-9FD6-05CE7101E56A}"/>
+    <hyperlink ref="C3" r:id="rId2" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E5FBD46F-E11A-4D2A-B9FE-F8CBC1E01A94}"/>
+    <hyperlink ref="D3" r:id="rId3" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C706EFF1-19C6-43DB-BF1C-D774D72D3CE5}"/>
+    <hyperlink ref="E3" r:id="rId4" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{1315EF9F-1F25-4041-BC16-DE12039BA3CB}"/>
+    <hyperlink ref="G3" r:id="rId5" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A9A8307D-310D-45BF-BF45-B21473727FC3}"/>
+    <hyperlink ref="I3" r:id="rId6" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{4C2DAC39-BD81-43B0-8EA7-456B2BB9799B}"/>
+    <hyperlink ref="B4" r:id="rId7" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=02%2F10%2F2026&amp;wDT_FIM=02%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{9DAF6DFA-76E5-4514-A106-958279A2DC2C}"/>
+    <hyperlink ref="C4" r:id="rId8" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=02%2F10%2F2026&amp;wDT_FIM=02%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{097FE572-AFA1-47B0-90CE-FE32B44A7B66}"/>
+    <hyperlink ref="D4" r:id="rId9" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=02%2F10%2F2026&amp;wDT_FIM=02%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{1E17B66C-D739-4BCE-A5F7-04A6F0EE91BD}"/>
+    <hyperlink ref="E4" r:id="rId10" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=02%2F10%2F2026&amp;wDT_FIM=02%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{78ECE9C6-7AC3-45E1-ADED-A8ED3C9BB380}"/>
+    <hyperlink ref="G4" r:id="rId11" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=02%2F10%2F2026&amp;wDT_FIM=02%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6C7B5F4-DB18-4CBF-902E-8D08E939B9C0}"/>
+    <hyperlink ref="I4" r:id="rId12" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=02%2F10%2F2026&amp;wDT_FIM=02%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{070523A6-7BBA-45A0-91A1-DD10E096AC83}"/>
+    <hyperlink ref="B5" r:id="rId13" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=05%2F10%2F2026&amp;wDT_FIM=05%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A6FE5CE1-9AFF-43A0-A2F7-A5FA64AE1C82}"/>
+    <hyperlink ref="C5" r:id="rId14" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=05%2F10%2F2026&amp;wDT_FIM=05%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5F06682F-785F-48AF-A556-9CB62F556813}"/>
+    <hyperlink ref="D5" r:id="rId15" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=05%2F10%2F2026&amp;wDT_FIM=05%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{99AECBC6-376B-463D-ABB3-613E6F334936}"/>
+    <hyperlink ref="E5" r:id="rId16" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=05%2F10%2F2026&amp;wDT_FIM=05%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{27865420-50C6-4B05-A8F7-78B1FC151DB8}"/>
+    <hyperlink ref="G5" r:id="rId17" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=05%2F10%2F2026&amp;wDT_FIM=05%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{3C074977-FBF5-40B5-995F-3B3FBDF4D757}"/>
+    <hyperlink ref="I5" r:id="rId18" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=05%2F10%2F2026&amp;wDT_FIM=05%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{942165DF-39D9-4890-BC49-3DC9CF408E78}"/>
+    <hyperlink ref="B6" r:id="rId19" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=06%2F10%2F2026&amp;wDT_FIM=06%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{BCC79D74-CE54-4820-A276-F1F847F0E585}"/>
+    <hyperlink ref="C6" r:id="rId20" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=06%2F10%2F2026&amp;wDT_FIM=06%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F7217115-1ED7-4776-838B-2EBAC408CA87}"/>
+    <hyperlink ref="D6" r:id="rId21" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=06%2F10%2F2026&amp;wDT_FIM=06%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0C834F42-8441-4D44-A5F6-2E057DAA850C}"/>
+    <hyperlink ref="E6" r:id="rId22" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=06%2F10%2F2026&amp;wDT_FIM=06%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{82310EFD-5CCC-411D-AAD6-3D10203E31AE}"/>
+    <hyperlink ref="G6" r:id="rId23" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=06%2F10%2F2026&amp;wDT_FIM=06%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0FBB09BD-6B32-40FA-9B50-16465E596A73}"/>
+    <hyperlink ref="I6" r:id="rId24" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=06%2F10%2F2026&amp;wDT_FIM=06%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C015B2D3-473D-4B27-AA32-C1EB96A98E2F}"/>
+    <hyperlink ref="B7" r:id="rId25" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=07%2F10%2F2026&amp;wDT_FIM=07%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{D8B51840-FE95-4575-9F58-A14A89D1CC89}"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=07%2F10%2F2026&amp;wDT_FIM=07%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{913B7A06-A561-49D9-9054-6988583CE0CF}"/>
+    <hyperlink ref="D7" r:id="rId27" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=07%2F10%2F2026&amp;wDT_FIM=07%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5928DE69-8B49-4938-8BC0-2591C24A59DA}"/>
+    <hyperlink ref="E7" r:id="rId28" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=07%2F10%2F2026&amp;wDT_FIM=07%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6A64E255-EAEC-4015-92E3-718673D24F41}"/>
+    <hyperlink ref="G7" r:id="rId29" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=07%2F10%2F2026&amp;wDT_FIM=07%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{171A8010-629F-4FCF-A267-F8977772A919}"/>
+    <hyperlink ref="I7" r:id="rId30" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=07%2F10%2F2026&amp;wDT_FIM=07%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{84D00DCA-8910-488F-A8BE-CF00F1AA773D}"/>
+    <hyperlink ref="B8" r:id="rId31" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=08%2F10%2F2026&amp;wDT_FIM=08%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{8A4AF581-4EA9-4887-9BA9-7B71127B5BEE}"/>
+    <hyperlink ref="C8" r:id="rId32" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=08%2F10%2F2026&amp;wDT_FIM=08%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FA63E263-C6EB-47FB-BB42-744574F43B36}"/>
+    <hyperlink ref="D8" r:id="rId33" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=08%2F10%2F2026&amp;wDT_FIM=08%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{46A855A0-B703-4A32-855A-133544FFA78E}"/>
+    <hyperlink ref="E8" r:id="rId34" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=08%2F10%2F2026&amp;wDT_FIM=08%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{81269BBD-6466-47BA-8954-B99AB7E547FD}"/>
+    <hyperlink ref="G8" r:id="rId35" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=08%2F10%2F2026&amp;wDT_FIM=08%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{8D159887-6B6B-4CF0-B136-959762FC53E5}"/>
+    <hyperlink ref="I8" r:id="rId36" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=08%2F10%2F2026&amp;wDT_FIM=08%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{AC9BAAD9-DB01-4874-A326-3ECFFE2AB771}"/>
+    <hyperlink ref="B9" r:id="rId37" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=09%2F10%2F2026&amp;wDT_FIM=09%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{ADECEC3D-1503-432D-9CE7-1D303F2EDA65}"/>
+    <hyperlink ref="C9" r:id="rId38" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=09%2F10%2F2026&amp;wDT_FIM=09%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{3DDFFF8C-7C65-4049-8FB5-880E5FAD2015}"/>
+    <hyperlink ref="D9" r:id="rId39" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=09%2F10%2F2026&amp;wDT_FIM=09%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B6B2BAD8-9818-4A17-B2AF-5EB790564079}"/>
+    <hyperlink ref="E9" r:id="rId40" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=09%2F10%2F2026&amp;wDT_FIM=09%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C3B9EC01-61F5-4418-9557-82EDCF8B1547}"/>
+    <hyperlink ref="G9" r:id="rId41" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=09%2F10%2F2026&amp;wDT_FIM=09%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{910F2F42-170A-4154-95A4-D576BF7E7119}"/>
+    <hyperlink ref="I9" r:id="rId42" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=09%2F10%2F2026&amp;wDT_FIM=09%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{73B71715-8B25-4802-A48B-206FEAB99577}"/>
+    <hyperlink ref="B10" r:id="rId43" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=10%2F10%2F2026&amp;wDT_FIM=10%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{1FFD6E12-D3BE-4FA7-A788-72E75A84EE48}"/>
+    <hyperlink ref="C10" r:id="rId44" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=10%2F10%2F2026&amp;wDT_FIM=10%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{60F13880-8519-4548-9073-F64C0E729464}"/>
+    <hyperlink ref="E10" r:id="rId45" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=10%2F10%2F2026&amp;wDT_FIM=10%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F2031124-7203-4B15-9E34-960BD3FC4AB9}"/>
+    <hyperlink ref="G10" r:id="rId46" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=10%2F10%2F2026&amp;wDT_FIM=10%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{39CCCDF7-0082-4581-9A5C-D7A3626EF94A}"/>
+    <hyperlink ref="I10" r:id="rId47" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=10%2F10%2F2026&amp;wDT_FIM=10%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0389E5D8-2ECA-4149-A985-3C38E758D9A5}"/>
+    <hyperlink ref="B11" r:id="rId48" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=11%2F10%2F2026&amp;wDT_FIM=11%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{30B1B3A3-0004-4192-B744-3D6C29732962}"/>
+    <hyperlink ref="C11" r:id="rId49" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=11%2F10%2F2026&amp;wDT_FIM=11%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{8DD9D58B-DC7C-4DDE-B29B-1A191FCC27EC}"/>
+    <hyperlink ref="E11" r:id="rId50" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=11%2F10%2F2026&amp;wDT_FIM=11%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6DD58EF5-84D0-43E6-8308-38241B6F33A6}"/>
+    <hyperlink ref="G11" r:id="rId51" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=11%2F10%2F2026&amp;wDT_FIM=11%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{8FDEFA51-3826-4AC9-B413-AB809828CC27}"/>
+    <hyperlink ref="I11" r:id="rId52" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=11%2F10%2F2026&amp;wDT_FIM=11%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{29EAB79F-E12E-4CA1-B0A4-5371C4363F2E}"/>
+    <hyperlink ref="B12" r:id="rId53" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=12%2F10%2F2026&amp;wDT_FIM=12%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{CED61254-7A53-4676-8894-8527F0937B26}"/>
+    <hyperlink ref="C12" r:id="rId54" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=12%2F10%2F2026&amp;wDT_FIM=12%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FB0C6349-F7A9-44BE-8D7C-BC51053FCFA0}"/>
+    <hyperlink ref="E12" r:id="rId55" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=12%2F10%2F2026&amp;wDT_FIM=12%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{001031EB-4A3F-486C-B2E9-E90310B771B2}"/>
+    <hyperlink ref="G12" r:id="rId56" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=12%2F10%2F2026&amp;wDT_FIM=12%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{329980CD-A0C3-49B7-8A0F-151CBF8D346F}"/>
+    <hyperlink ref="I12" r:id="rId57" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=12%2F10%2F2026&amp;wDT_FIM=12%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{BA8C7164-B9AC-453C-AC13-390EF76C3CAA}"/>
+    <hyperlink ref="B13" r:id="rId58" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=13%2F10%2F2026&amp;wDT_FIM=13%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{04B51785-D512-4943-AE8C-0D8BE107D63D}"/>
+    <hyperlink ref="C13" r:id="rId59" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=13%2F10%2F2026&amp;wDT_FIM=13%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FD9277CC-07A3-444D-AA93-AE4686F3DDD2}"/>
+    <hyperlink ref="D13" r:id="rId60" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=13%2F10%2F2026&amp;wDT_FIM=13%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{82C93853-7B6E-4349-BEF6-D6743752A55B}"/>
+    <hyperlink ref="E13" r:id="rId61" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=13%2F10%2F2026&amp;wDT_FIM=13%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{BE630531-0E43-4541-9855-02D96EA186CF}"/>
+    <hyperlink ref="G13" r:id="rId62" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=13%2F10%2F2026&amp;wDT_FIM=13%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{780AD855-20EC-46E0-8309-4927B05D52C0}"/>
+    <hyperlink ref="I13" r:id="rId63" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=13%2F10%2F2026&amp;wDT_FIM=13%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0F397AE1-7108-4873-98AA-42DF29077EBA}"/>
+    <hyperlink ref="B14" r:id="rId64" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=14%2F10%2F2026&amp;wDT_FIM=14%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{69984AF0-BFBD-4576-AAB7-E720EB47AA23}"/>
+    <hyperlink ref="C14" r:id="rId65" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=14%2F10%2F2026&amp;wDT_FIM=14%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E741674C-9639-4284-85DA-2758B4B98186}"/>
+    <hyperlink ref="D14" r:id="rId66" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=14%2F10%2F2026&amp;wDT_FIM=14%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0EAB373F-90CB-4781-881A-18B44C5C67CE}"/>
+    <hyperlink ref="E14" r:id="rId67" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=14%2F10%2F2026&amp;wDT_FIM=14%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C9950F5F-F47E-4017-BD4C-CB6C5E1AD4EA}"/>
+    <hyperlink ref="G14" r:id="rId68" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=14%2F10%2F2026&amp;wDT_FIM=14%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{9ED67B91-146B-4BA0-89AF-12E3B525B057}"/>
+    <hyperlink ref="I14" r:id="rId69" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=14%2F10%2F2026&amp;wDT_FIM=14%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{75091688-CCD1-4148-8302-C16C62A3ECEB}"/>
+    <hyperlink ref="B15" r:id="rId70" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=15%2F10%2F2026&amp;wDT_FIM=15%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{51AB3956-06F7-42FF-92F7-87725F4628B9}"/>
+    <hyperlink ref="C15" r:id="rId71" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=15%2F10%2F2026&amp;wDT_FIM=15%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{D01B4EA1-DE0E-4C8E-9A83-0611A7BC37EE}"/>
+    <hyperlink ref="D15" r:id="rId72" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=15%2F10%2F2026&amp;wDT_FIM=15%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A9DE5639-D4AC-4A1B-B83A-DEFF954978CA}"/>
+    <hyperlink ref="E15" r:id="rId73" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=15%2F10%2F2026&amp;wDT_FIM=15%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5BBB9CFD-24F5-4F9B-8C3B-D385341FB79F}"/>
+    <hyperlink ref="G15" r:id="rId74" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=15%2F10%2F2026&amp;wDT_FIM=15%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E633D1D4-CA93-4115-B984-F66B88BF3416}"/>
+    <hyperlink ref="I15" r:id="rId75" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=15%2F10%2F2026&amp;wDT_FIM=15%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{13357E6C-BB30-484B-8400-F91EE2A7D07E}"/>
+    <hyperlink ref="B16" r:id="rId76" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=16%2F10%2F2026&amp;wDT_FIM=16%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{057E90F7-6A40-4EDE-9A3E-F30A859CF3BE}"/>
+    <hyperlink ref="C16" r:id="rId77" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=16%2F10%2F2026&amp;wDT_FIM=16%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F7DB2805-0CDB-484E-B723-B80837A45A7C}"/>
+    <hyperlink ref="D16" r:id="rId78" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=16%2F10%2F2026&amp;wDT_FIM=16%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{47E74C81-3114-45F2-986C-956A43348F2B}"/>
+    <hyperlink ref="E16" r:id="rId79" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=16%2F10%2F2026&amp;wDT_FIM=16%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{55782F92-7117-4BA1-BB3C-7206EDDCE433}"/>
+    <hyperlink ref="G16" r:id="rId80" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=16%2F10%2F2026&amp;wDT_FIM=16%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A2A6CF9B-8818-4C36-9182-BB4C1CD6E24D}"/>
+    <hyperlink ref="I16" r:id="rId81" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=16%2F10%2F2026&amp;wDT_FIM=16%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{4A7E4F9B-D384-4C96-9E21-EF9427F927A0}"/>
+    <hyperlink ref="B17" r:id="rId82" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=19%2F10%2F2026&amp;wDT_FIM=19%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93C9F410-EA82-4975-A9CA-E8E7C9E6E495}"/>
+    <hyperlink ref="C17" r:id="rId83" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=19%2F10%2F2026&amp;wDT_FIM=19%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A261D0F3-D257-498A-916F-FC902A0B02BA}"/>
+    <hyperlink ref="E17" r:id="rId84" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=19%2F10%2F2026&amp;wDT_FIM=19%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6F6EF0DF-0CDA-4824-B98D-C894AFE2F645}"/>
+    <hyperlink ref="G17" r:id="rId85" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=19%2F10%2F2026&amp;wDT_FIM=19%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A64E6B0D-5609-420E-A0F9-2CD8282DF21E}"/>
+    <hyperlink ref="I17" r:id="rId86" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=19%2F10%2F2026&amp;wDT_FIM=19%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F1155477-B7F0-421A-9F9F-26636A548949}"/>
+    <hyperlink ref="B18" r:id="rId87" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{63B925F4-B927-4D4B-AF30-932AEBEE9398}"/>
+    <hyperlink ref="C18" r:id="rId88" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{13B50C12-A016-4095-80AB-9C31F37F9631}"/>
+    <hyperlink ref="D18" r:id="rId89" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6CE45C78-33FF-409B-B7D1-55ED5243215C}"/>
+    <hyperlink ref="E18" r:id="rId90" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F81D7FAA-6209-4009-8307-F99F7A8A264B}"/>
+    <hyperlink ref="G18" r:id="rId91" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5E4EE0FA-B3A6-4483-8853-49B026528B1C}"/>
+    <hyperlink ref="I18" r:id="rId92" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=20%2F10%2F2026&amp;wDT_FIM=20%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{5805841B-46C8-4811-A12A-93F1DF772040}"/>
+    <hyperlink ref="B19" r:id="rId93" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{879CA852-48F7-47EA-8032-E11E92617195}"/>
+    <hyperlink ref="C19" r:id="rId94" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C341E091-4BE7-44D7-94C5-24322C9FB854}"/>
+    <hyperlink ref="D19" r:id="rId95" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{BD6A736D-E57D-4E62-8311-AD3B2D3789E1}"/>
+    <hyperlink ref="E19" r:id="rId96" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E8FA1758-0AB6-4D9C-970A-0EF3A77B867A}"/>
+    <hyperlink ref="G19" r:id="rId97" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F817A03E-2763-4E40-A607-DB36EDA79830}"/>
+    <hyperlink ref="I19" r:id="rId98" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=21%2F10%2F2026&amp;wDT_FIM=21%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{25CAEB8F-B63C-484E-BC45-F81165558C94}"/>
+    <hyperlink ref="B20" r:id="rId99" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=22%2F10%2F2026&amp;wDT_FIM=22%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{7DA6DE3B-61E7-4299-8BC4-FC2AF3E662F8}"/>
+    <hyperlink ref="C20" r:id="rId100" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=22%2F10%2F2026&amp;wDT_FIM=22%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{BD60FEF0-5474-46D6-A5F2-EF2DAFF8B99B}"/>
+    <hyperlink ref="D20" r:id="rId101" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=22%2F10%2F2026&amp;wDT_FIM=22%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{49D3EB46-3608-49B9-A55C-96E319E31E51}"/>
+    <hyperlink ref="E20" r:id="rId102" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=22%2F10%2F2026&amp;wDT_FIM=22%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F088F589-3D39-42DA-AF41-25DDB3728F24}"/>
+    <hyperlink ref="G20" r:id="rId103" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=22%2F10%2F2026&amp;wDT_FIM=22%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F3C47B57-3594-4D55-A617-FFDC13F5FB73}"/>
+    <hyperlink ref="I20" r:id="rId104" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=22%2F10%2F2026&amp;wDT_FIM=22%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{1FC47A20-9CE2-4784-B0BA-E38A9864DCE4}"/>
+    <hyperlink ref="B21" r:id="rId105" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E319463A-8363-4BBA-B1A3-39F493B7B6D9}"/>
+    <hyperlink ref="C21" r:id="rId106" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{57A685E2-9D7A-4021-822F-26463A7EEA54}"/>
+    <hyperlink ref="D21" r:id="rId107" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{4976344E-0814-4EFE-AB2F-EE2FE3AF2C2E}"/>
+    <hyperlink ref="E21" r:id="rId108" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{695CE89C-574C-4A69-B7B7-7FF03B4CD7B1}"/>
+    <hyperlink ref="G21" r:id="rId109" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F86D88F9-D317-461D-9C61-FF135999D175}"/>
+    <hyperlink ref="I21" r:id="rId110" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=23%2F10%2F2026&amp;wDT_FIM=23%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{D0326386-67B6-4488-A438-F8FBAC6A450F}"/>
+    <hyperlink ref="B22" r:id="rId111" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C7AF566F-9632-4AA4-8F34-0B970597D3BA}"/>
+    <hyperlink ref="C22" r:id="rId112" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{169EAA2C-A6AC-4FCE-93BB-ACEF1B3F8EBC}"/>
+    <hyperlink ref="D22" r:id="rId113" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{7676174D-27EF-49A8-A14E-D7BC7E0216B1}"/>
+    <hyperlink ref="E22" r:id="rId114" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{24DB1586-F850-47B7-9679-1296B90D21FF}"/>
+    <hyperlink ref="G22" r:id="rId115" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F6EE7820-E235-40AE-9EE0-D9FF248828DF}"/>
+    <hyperlink ref="I22" r:id="rId116" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=26%2F10%2F2026&amp;wDT_FIM=26%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{59D0B290-8208-4530-9196-E059E3EFB104}"/>
+    <hyperlink ref="B23" r:id="rId117" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{8A006336-1515-4366-BB60-0F379AB25E3D}"/>
+    <hyperlink ref="C23" r:id="rId118" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B27C3982-31D4-4CAD-A4BF-03134A481775}"/>
+    <hyperlink ref="D23" r:id="rId119" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{7A7748FF-DCEF-4FE1-9493-4A90724AD4B8}"/>
+    <hyperlink ref="E23" r:id="rId120" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93532439-7A0E-4DEA-B3D9-0784C51E7BE7}"/>
+    <hyperlink ref="G23" r:id="rId121" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0DC2FEC9-B20A-401A-8D11-AC1D2F0DC61B}"/>
+    <hyperlink ref="I23" r:id="rId122" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=27%2F10%2F2026&amp;wDT_FIM=27%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{0FD5E040-B03A-455A-9204-5AAD0A2AED19}"/>
+    <hyperlink ref="B24" r:id="rId123" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{D44FD28B-EBF8-471F-BB31-1BEFD1F43233}"/>
+    <hyperlink ref="C24" r:id="rId124" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{9EAB19A3-BECE-4184-930C-6A15ED9A29D6}"/>
+    <hyperlink ref="D24" r:id="rId125" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{9D649A28-9791-4AAC-B0A1-F2C3CA303F0C}"/>
+    <hyperlink ref="E24" r:id="rId126" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{21823261-B4F4-47FA-86BC-5F7CEE4685B2}"/>
+    <hyperlink ref="G24" r:id="rId127" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FB38D098-8B1C-43C1-AD3A-C194FB3E3C7F}"/>
+    <hyperlink ref="I24" r:id="rId128" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{14A793E0-75A1-4F59-9C35-B1536EC89BEF}"/>
+    <hyperlink ref="B25" r:id="rId129" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{26C339CF-03A2-4044-B71F-1B100CC059A9}"/>
+    <hyperlink ref="C25" r:id="rId130" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{02C307C1-145D-41B7-B1AE-A8080C58C1BE}"/>
+    <hyperlink ref="E25" r:id="rId131" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{18C8549A-2C10-4784-8559-867EC840A426}"/>
+    <hyperlink ref="G25" r:id="rId132" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{42E3BB6E-E58A-4D99-B8A0-A7FED1A97F48}"/>
+    <hyperlink ref="I25" r:id="rId133" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93DD70DD-B00E-43A1-98BC-B520BE0CEE83}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId134"/>
 </worksheet>
 </file>
 

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D6FC34-69BE-420C-B4F6-814AC15640A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984F8F84-D9C0-49F4-B5AE-75BA115EA04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
     <sheet name="Faturamento por cliente" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="253">
   <si>
     <t>Filial</t>
   </si>
@@ -777,6 +790,9 @@
   </si>
   <si>
     <t>TOT</t>
+  </si>
+  <si>
+    <t>DEV</t>
   </si>
 </sst>
 </file>
@@ -1467,10 +1483,10 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1479,10 +1495,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1860,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19101EBF-008C-4E37-90C0-CF2D419D5300}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1871,10 +1887,11 @@
     <col min="7" max="7" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="18" t="s">
@@ -1893,12 +1910,15 @@
         <v>250</v>
       </c>
       <c r="I1" s="19"/>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="16" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
+      <c r="K1" s="16" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21"/>
       <c r="B2" s="7" t="s">
         <v>78</v>
       </c>
@@ -1923,9 +1943,10 @@
       <c r="I2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="21"/>
-    </row>
-    <row r="3" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>46296</v>
       </c>
@@ -1952,8 +1973,12 @@
       <c r="J3" s="12">
         <v>272046.58</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="12">
+        <f>SUM(C3+E3+G3+I3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>46297</v>
       </c>
@@ -1980,8 +2005,12 @@
       <c r="J4" s="12">
         <v>457346.52</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="12">
+        <f t="shared" ref="K4:K26" si="0">SUM(C4+E4+G4+I4)</f>
+        <v>-26599.88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>46300</v>
       </c>
@@ -2008,8 +2037,12 @@
       <c r="J5" s="12">
         <v>305376.46000000002</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="12">
+        <f t="shared" si="0"/>
+        <v>-7502.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>46301</v>
       </c>
@@ -2036,8 +2069,12 @@
       <c r="J6" s="12">
         <v>461218.26</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="12">
+        <f t="shared" si="0"/>
+        <v>-15592.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>46302</v>
       </c>
@@ -2064,8 +2101,12 @@
       <c r="J7" s="12">
         <v>319812.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="12">
+        <f t="shared" si="0"/>
+        <v>-12949.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>46303</v>
       </c>
@@ -2092,8 +2133,12 @@
       <c r="J8" s="12">
         <v>592806.96</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>46304</v>
       </c>
@@ -2120,8 +2165,12 @@
       <c r="J9" s="12">
         <v>283538.15000000002</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="12">
+        <f t="shared" si="0"/>
+        <v>-70683.45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>46305</v>
       </c>
@@ -2146,8 +2195,12 @@
       <c r="J10" s="12">
         <v>203772.98</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>46306</v>
       </c>
@@ -2172,8 +2225,12 @@
       <c r="J11" s="12">
         <v>169560.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>46307</v>
       </c>
@@ -2198,8 +2255,12 @@
       <c r="J12" s="12">
         <v>216275.07</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>46308</v>
       </c>
@@ -2226,8 +2287,12 @@
       <c r="J13" s="12">
         <v>504715.42</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="12">
+        <f t="shared" si="0"/>
+        <v>-29468.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>46309</v>
       </c>
@@ -2254,8 +2319,12 @@
       <c r="J14" s="12">
         <v>335630.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="12">
+        <f t="shared" si="0"/>
+        <v>-14134.51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>46310</v>
       </c>
@@ -2282,8 +2351,12 @@
       <c r="J15" s="12">
         <v>304137.40999999997</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="12">
+        <f t="shared" si="0"/>
+        <v>-11085.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>46311</v>
       </c>
@@ -2310,8 +2383,12 @@
       <c r="J16" s="12">
         <v>1382549.88</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>46314</v>
       </c>
@@ -2336,8 +2413,12 @@
       <c r="J17" s="12">
         <v>336565.44</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>46315</v>
       </c>
@@ -2364,8 +2445,12 @@
       <c r="J18" s="12">
         <v>369825.22</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="12">
+        <f t="shared" si="0"/>
+        <v>-63152.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>46316</v>
       </c>
@@ -2392,8 +2477,12 @@
       <c r="J19" s="12">
         <v>568206.79</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="12">
+        <f t="shared" si="0"/>
+        <v>-24640.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>46317</v>
       </c>
@@ -2420,8 +2509,12 @@
       <c r="J20" s="12">
         <v>670884.31000000006</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="12">
+        <f t="shared" si="0"/>
+        <v>-26687.200000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>46318</v>
       </c>
@@ -2448,8 +2541,12 @@
       <c r="J21" s="12">
         <v>382740.33</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="12">
+        <f t="shared" si="0"/>
+        <v>-19833.009999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>46321</v>
       </c>
@@ -2476,8 +2573,12 @@
       <c r="J22" s="12">
         <v>855311.14</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="12">
+        <f t="shared" si="0"/>
+        <v>-8601.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>46322</v>
       </c>
@@ -2504,8 +2605,12 @@
       <c r="J23" s="12">
         <v>413601.17</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="12">
+        <f t="shared" si="0"/>
+        <v>-5174.3600000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>46323</v>
       </c>
@@ -2532,8 +2637,12 @@
       <c r="J24" s="12">
         <v>374665.95</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="12">
+        <f t="shared" si="0"/>
+        <v>-14081.69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>46324</v>
       </c>
@@ -2558,8 +2667,12 @@
       <c r="J25" s="12">
         <v>9043.6</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="12">
+        <f t="shared" si="0"/>
+        <v>-30205.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>75</v>
       </c>
@@ -2590,15 +2703,20 @@
       <c r="J26" s="14">
         <v>9789630.4499999993</v>
       </c>
+      <c r="K26" s="14">
+        <f>SUM(K3:K25)</f>
+        <v>-380392.39</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="K1:K2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=01%2F10%2F2026&amp;wDT_FIM=01%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{687BB916-39E4-451A-9FD6-05CE7101E56A}"/>

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984F8F84-D9C0-49F4-B5AE-75BA115EA04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9A479B-2D61-46ED-8C2B-F459B239B014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
@@ -1164,7 +1164,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1391,6 +1391,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1437,7 +1482,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="19" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1473,14 +1518,14 @@
     <xf numFmtId="4" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="21" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1494,11 +1539,29 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="33" borderId="19" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="19" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="18" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1886,12 +1949,12 @@
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="18" t="s">
@@ -1918,7 +1981,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
+      <c r="A2" s="15"/>
       <c r="B2" s="7" t="s">
         <v>78</v>
       </c>
@@ -2006,7 +2069,7 @@
         <v>457346.52</v>
       </c>
       <c r="K4" s="12">
-        <f t="shared" ref="K4:K26" si="0">SUM(C4+E4+G4+I4)</f>
+        <f t="shared" ref="K4:K25" si="0">SUM(C4+E4+G4+I4)</f>
         <v>-26599.88</v>
       </c>
     </row>
@@ -2643,69 +2706,71 @@
       </c>
     </row>
     <row r="25" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9">
+      <c r="A25" s="20">
         <v>46324</v>
       </c>
-      <c r="B25" s="10">
-        <v>39248.85</v>
-      </c>
-      <c r="C25" s="10">
-        <v>-30205.25</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="11">
+      <c r="B25" s="21">
+        <v>50832.02</v>
+      </c>
+      <c r="C25" s="21">
+        <v>-32762.45</v>
+      </c>
+      <c r="D25" s="21">
+        <v>11640.48</v>
+      </c>
+      <c r="E25" s="22">
         <v>0</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="11">
+      <c r="F25" s="23"/>
+      <c r="G25" s="22">
         <v>0</v>
       </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="11">
+      <c r="H25" s="23"/>
+      <c r="I25" s="22">
         <v>0</v>
       </c>
-      <c r="J25" s="12">
-        <v>9043.6</v>
+      <c r="J25" s="24">
+        <v>29710.05</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="0"/>
-        <v>-30205.25</v>
+        <v>-32762.45</v>
       </c>
     </row>
     <row r="26" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="14">
-        <v>9509365.8000000007</v>
-      </c>
-      <c r="C26" s="14">
-        <v>-364063.73</v>
-      </c>
-      <c r="D26" s="14">
-        <v>660657.04</v>
-      </c>
-      <c r="E26" s="14">
+      <c r="B26" s="26">
+        <v>9520948.9700000007</v>
+      </c>
+      <c r="C26" s="26">
+        <v>-366620.93</v>
+      </c>
+      <c r="D26" s="26">
+        <v>672297.52</v>
+      </c>
+      <c r="E26" s="26">
         <v>-16328.66</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="27">
         <v>0</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="27">
         <v>0</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="27">
         <v>0</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="27">
         <v>0</v>
       </c>
-      <c r="J26" s="14">
-        <v>9789630.4499999993</v>
-      </c>
-      <c r="K26" s="14">
+      <c r="J26" s="26">
+        <v>9810296.9000000004</v>
+      </c>
+      <c r="K26" s="13">
         <f>SUM(K3:K25)</f>
-        <v>-380392.39</v>
+        <v>-382949.59</v>
       </c>
     </row>
   </sheetData>
@@ -2847,14 +2912,15 @@
     <hyperlink ref="E24" r:id="rId126" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{21823261-B4F4-47FA-86BC-5F7CEE4685B2}"/>
     <hyperlink ref="G24" r:id="rId127" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FB38D098-8B1C-43C1-AD3A-C194FB3E3C7F}"/>
     <hyperlink ref="I24" r:id="rId128" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{14A793E0-75A1-4F59-9C35-B1536EC89BEF}"/>
-    <hyperlink ref="B25" r:id="rId129" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{26C339CF-03A2-4044-B71F-1B100CC059A9}"/>
-    <hyperlink ref="C25" r:id="rId130" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{02C307C1-145D-41B7-B1AE-A8080C58C1BE}"/>
-    <hyperlink ref="E25" r:id="rId131" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{18C8549A-2C10-4784-8559-867EC840A426}"/>
-    <hyperlink ref="G25" r:id="rId132" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{42E3BB6E-E58A-4D99-B8A0-A7FED1A97F48}"/>
-    <hyperlink ref="I25" r:id="rId133" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93DD70DD-B00E-43A1-98BC-B520BE0CEE83}"/>
+    <hyperlink ref="B25" r:id="rId129" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6F9D287F-5B13-4F5E-B9A9-FAE3F21A9F05}"/>
+    <hyperlink ref="C25" r:id="rId130" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E20DED4D-CA1D-4234-932E-9D0B5BFD88AA}"/>
+    <hyperlink ref="D25" r:id="rId131" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93988AEF-44D8-440D-A3F9-80D13FDE9B8D}"/>
+    <hyperlink ref="E25" r:id="rId132" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F30E50C5-74FA-474A-B0A5-1A1DA6C88237}"/>
+    <hyperlink ref="G25" r:id="rId133" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B642C56F-47C6-4274-AB89-8D8203E0CC13}"/>
+    <hyperlink ref="I25" r:id="rId134" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C2C51E8D-EDDC-46DF-8B51-DB8FE9F897B0}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId134"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId135"/>
 </worksheet>
 </file>
 

--- a/DadosFaturamento.xlsx
+++ b/DadosFaturamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9A479B-2D61-46ED-8C2B-F459B239B014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E022D271-6EDB-4958-8A3A-BC82A908C2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CBC36103-499F-47D2-920C-CE20E86CCBE2}"/>
   </bookViews>
   <sheets>
     <sheet name="FaturamentoBruto" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="258">
   <si>
     <t>Filial</t>
   </si>
@@ -793,6 +793,21 @@
   </si>
   <si>
     <t>DEV</t>
+  </si>
+  <si>
+    <t>WURTH SW INDUSTRY</t>
+  </si>
+  <si>
+    <t>UNIMED ARACATUBA 51.</t>
+  </si>
+  <si>
+    <t>DASA RAPOSO</t>
+  </si>
+  <si>
+    <t>AME RIO CLARO</t>
+  </si>
+  <si>
+    <t>AME PARIQUERA-ACU</t>
   </si>
 </sst>
 </file>
@@ -1521,24 +1536,6 @@
     <xf numFmtId="4" fontId="21" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="19" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1562,6 +1559,24 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1949,39 +1964,39 @@
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="18" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="27"/>
+      <c r="H1" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="16" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="24" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="7" t="s">
         <v>78</v>
       </c>
@@ -2006,8 +2021,8 @@
       <c r="I2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -2706,71 +2721,71 @@
       </c>
     </row>
     <row r="25" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20">
+      <c r="A25" s="14">
         <v>46324</v>
       </c>
-      <c r="B25" s="21">
-        <v>50832.02</v>
-      </c>
-      <c r="C25" s="21">
-        <v>-32762.45</v>
-      </c>
-      <c r="D25" s="21">
-        <v>11640.48</v>
-      </c>
-      <c r="E25" s="22">
+      <c r="B25" s="15">
+        <v>377725.62</v>
+      </c>
+      <c r="C25" s="15">
+        <v>-39009.949999999997</v>
+      </c>
+      <c r="D25" s="15">
+        <v>108814.98</v>
+      </c>
+      <c r="E25" s="16">
         <v>0</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="22">
+      <c r="F25" s="17"/>
+      <c r="G25" s="16">
         <v>0</v>
       </c>
-      <c r="H25" s="23"/>
-      <c r="I25" s="22">
+      <c r="H25" s="17"/>
+      <c r="I25" s="16">
         <v>0</v>
       </c>
-      <c r="J25" s="24">
-        <v>29710.05</v>
+      <c r="J25" s="18">
+        <v>447530.65</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="0"/>
-        <v>-32762.45</v>
+        <v>-39009.949999999997</v>
       </c>
     </row>
     <row r="26" spans="1:11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="26">
-        <v>9520948.9700000007</v>
-      </c>
-      <c r="C26" s="26">
-        <v>-366620.93</v>
-      </c>
-      <c r="D26" s="26">
-        <v>672297.52</v>
-      </c>
-      <c r="E26" s="26">
+      <c r="B26" s="20">
+        <v>9847842.5700000003</v>
+      </c>
+      <c r="C26" s="20">
+        <v>-372868.43</v>
+      </c>
+      <c r="D26" s="20">
+        <v>769472.02</v>
+      </c>
+      <c r="E26" s="20">
         <v>-16328.66</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="21">
         <v>0</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="21">
         <v>0</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="21">
         <v>0</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="21">
         <v>0</v>
       </c>
-      <c r="J26" s="26">
-        <v>9810296.9000000004</v>
+      <c r="J26" s="20">
+        <v>10228117.5</v>
       </c>
       <c r="K26" s="13">
         <f>SUM(K3:K25)</f>
-        <v>-382949.59</v>
+        <v>-389197.09</v>
       </c>
     </row>
   </sheetData>
@@ -2912,12 +2927,12 @@
     <hyperlink ref="E24" r:id="rId126" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{21823261-B4F4-47FA-86BC-5F7CEE4685B2}"/>
     <hyperlink ref="G24" r:id="rId127" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{FB38D098-8B1C-43C1-AD3A-C194FB3E3C7F}"/>
     <hyperlink ref="I24" r:id="rId128" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=28%2F10%2F2026&amp;wDT_FIM=28%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{14A793E0-75A1-4F59-9C35-B1536EC89BEF}"/>
-    <hyperlink ref="B25" r:id="rId129" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{6F9D287F-5B13-4F5E-B9A9-FAE3F21A9F05}"/>
-    <hyperlink ref="C25" r:id="rId130" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E20DED4D-CA1D-4234-932E-9D0B5BFD88AA}"/>
-    <hyperlink ref="D25" r:id="rId131" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93988AEF-44D8-440D-A3F9-80D13FDE9B8D}"/>
-    <hyperlink ref="E25" r:id="rId132" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{F30E50C5-74FA-474A-B0A5-1A1DA6C88237}"/>
-    <hyperlink ref="G25" r:id="rId133" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{B642C56F-47C6-4274-AB89-8D8203E0CC13}"/>
-    <hyperlink ref="I25" r:id="rId134" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{C2C51E8D-EDDC-46DF-8B51-DB8FE9F897B0}"/>
+    <hyperlink ref="B25" r:id="rId129" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{25B910CD-9280-4CC7-A8A2-3716EB8EF00A}"/>
+    <hyperlink ref="C25" r:id="rId130" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{93804283-6680-4372-A3C0-560A55CC5F86}"/>
+    <hyperlink ref="D25" r:id="rId131" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0102&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{A7E82148-BE68-4D9B-9D31-B0C90CDF1CFA}"/>
+    <hyperlink ref="E25" r:id="rId132" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{E7729466-911D-4795-B4DC-094721E8D966}"/>
+    <hyperlink ref="G25" r:id="rId133" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{BE69B926-E970-4614-84AA-B59FBA79C25F}"/>
+    <hyperlink ref="I25" r:id="rId134" tooltip="por Cliente" display="https://qubex-higimed.integraerp.com.br/ViewCockpit001/Cp01Cli?wFIL_DD=0101&amp;wDT_INI=29%2F10%2F2026&amp;wDT_FIM=29%2F10%2F2026&amp;wACY_DD=%5B%22%2A%2A%2A%2A%2A%2A%22%5D" xr:uid="{EED94229-FFDA-41CC-8856-1FBCA489E980}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId135"/>
@@ -2926,7 +2941,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2872C95-5BBD-470F-BA44-E40722CF8AA3}">
-  <dimension ref="A1:D995"/>
+  <dimension ref="A1:D1042"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -16866,6 +16881,664 @@
         <v>100.8</v>
       </c>
     </row>
+    <row r="996" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A996" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B996" s="3">
+        <v>101</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D996" s="6">
+        <v>8499.5</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A997" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B997" s="3">
+        <v>101</v>
+      </c>
+      <c r="C997" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D997" s="6">
+        <v>4270.3599999999997</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A998" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B998" s="3">
+        <v>101</v>
+      </c>
+      <c r="C998" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D998" s="6">
+        <v>2858.4</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A999" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B999" s="3">
+        <v>101</v>
+      </c>
+      <c r="C999" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D999" s="6">
+        <v>82188.320000000007</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1000" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1000" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1000" s="6">
+        <v>1075.3</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1001" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1001" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1001" s="6">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1002" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1002" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1002" s="6">
+        <v>4344.82</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1003" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1003" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1003" s="6">
+        <v>7885.5</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1004" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1004" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1004" s="3">
+        <v>740.5</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1005" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1005" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1005" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1005" s="6">
+        <v>-5722.17</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1006" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1006" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1006" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1006" s="6">
+        <v>30653.4</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1007" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1007" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1007" s="3">
+        <v>639.84</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1008" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1008" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1008" s="6">
+        <v>3217.52</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1009" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1009" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1009" s="6">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1010" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1010" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1010" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1011" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1011" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1011" s="6">
+        <v>11571.3</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1012" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1012" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1012" s="6">
+        <v>6690.63</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1013" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1013" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1013" s="6">
+        <v>57554.76</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1014" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1014" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1014" s="6">
+        <v>25243.08</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1015" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1015" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1015" s="6">
+        <v>2623.54</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1016" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1016" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1016" s="3">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1017" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1017" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1017" s="3">
+        <v>981.82</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1018" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1018" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1018" s="6">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1019" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1019" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1019" s="6">
+        <v>6467.38</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1020" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1020" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1020" s="6">
+        <v>5265.95</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1021" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1021" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1021" s="6">
+        <v>6967.6</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1022" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1022" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1022" s="3">
+        <v>272.16000000000003</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1023" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1023" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1023" s="6">
+        <v>1415.82</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1024" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1024" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1024" s="3">
+        <v>814.12</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1025" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1025" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1025" s="3">
+        <v>-525.33000000000004</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1026" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1026" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1026" s="6">
+        <v>1385.08</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1027" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1027" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1027" s="6">
+        <v>2128.17</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1028" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1028" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1028" s="6">
+        <v>4451.55</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1029" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1029" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1029" s="6">
+        <v>5926.43</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1030" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1030" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1030" s="6">
+        <v>5663.4</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1031" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1031" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1031" s="6">
+        <v>2188.4299999999998</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1032" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1032" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1032" s="6">
+        <v>2124.34</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1033" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1033" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1033" s="6">
+        <v>12750</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1034" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1034" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1034" s="6">
+        <v>38872.5</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1035" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1035" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1035" s="6">
+        <v>2374.13</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1036" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1036" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1036" s="6">
+        <v>1191.54</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1037" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1037" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1037" s="6">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1038" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1038" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1038" s="6">
+        <v>13672.64</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1039" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1039" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1039" s="6">
+        <v>-32762.45</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1040" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1040" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1040" s="3">
+        <v>249.61</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1041" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1041" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1041" s="3">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1042" s="4">
+        <v>46324</v>
+      </c>
+      <c r="B1042" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1042" s="6">
+        <v>2640.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
